--- a/Fechas_CARS.xlsx
+++ b/Fechas_CARS.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MiguelAndresBeltranG\Documents\UNERGY\Automatizacion\App CARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDC9487-2DE5-4166-A1F3-81DCDB176E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D875E87B-B879-4273-9394-EDF71E50D93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="556" xr2:uid="{360465FD-DB33-40A4-B804-83F77FD168BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="556" xr2:uid="{360465FD-DB33-40A4-B804-83F77FD168BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$O$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$P$177</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,8 +42,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="321">
   <si>
     <t>Tipo</t>
   </si>
@@ -143,9 +166,6 @@
     <t>AUTOPISTA DEL RIO GRANDE S.A.S</t>
   </si>
   <si>
-    <t>CENIT TRANSPORTE Y, LOGISTICA DE HIDROCARBUROS S.A.S.</t>
-  </si>
-  <si>
     <t>Archivo</t>
   </si>
   <si>
@@ -198,18 +218,12 @@
   </si>
   <si>
     <t>BORIS ANTONIO ANDRADE MOVILLA</t>
-  </si>
-  <si>
-    <t>AUTO-0053-11-02-2026-RN.pdf</t>
   </si>
   <si>
     <t>CONSORCIO
 CONSTRUCTOR AUTOPISTA DEL RIO GRANDE</t>
   </si>
   <si>
-    <t>AUTO-0052-11-02-2026-RN.pdf</t>
-  </si>
-  <si>
     <t>AUTO-0050-11-02-2026-RN.pdf</t>
   </si>
   <si>
@@ -282,9 +296,6 @@
     <t>AUTO-0073-02-03-2026-RN.pdf</t>
   </si>
   <si>
-    <t>AUTO-0074-02-03-2026-RN.pdf</t>
-  </si>
-  <si>
     <t>AUTO-0102-18-03-2026-RN.pdf</t>
   </si>
   <si>
@@ -331,9 +342,6 @@
     <t>Empresa / Entidad</t>
   </si>
   <si>
-    <t>Dirección General (Valledupar)</t>
-  </si>
-  <si>
     <t>RESOLUCION-0607-23-12-2025-DG.pdf</t>
   </si>
   <si>
@@ -371,9 +379,6 @@
   </si>
   <si>
     <t>RESOLUCION-0046-10-12-2025-RN.pdf</t>
-  </si>
-  <si>
-    <t>AUTO-0250-12-12-2025-RN.pdf</t>
   </si>
   <si>
     <t>CESAR AUGUSTO SIERRA
@@ -434,10 +439,6 @@
     <t>AUTO-0165-06-10-2025-JA.pdf</t>
   </si>
   <si>
-    <t>CENIT
-TRANSPORTE Y LOGISTICA DE HIDROCARBUROS S.A.S.</t>
-  </si>
-  <si>
     <t>AUTO-0160-15-10-2025-JA.pdf</t>
   </si>
   <si>
@@ -478,9 +479,6 @@
     <t>RESOLUCION-0051-08-07-2026-RN.pdf</t>
   </si>
   <si>
-    <t>RESOLUCION-0371-16-07-2026-DG.pdf</t>
-  </si>
-  <si>
     <t>CONSORCIO CONSTRUCTOR
 PISTA DEL RIO GRANDE</t>
   </si>
@@ -571,10 +569,6 @@
     <t>AUTO-0242-24-11-2025-RN.pdf</t>
   </si>
   <si>
-    <t>CONSORCIO CONSTRUCTOR
-AUTOPISTA DEL RIO GRANDE</t>
-  </si>
-  <si>
     <t>AUTO-0241-24-11-2025-RN.pdf</t>
   </si>
   <si>
@@ -695,9 +689,6 @@
     <t>AUTO-0182-28-05-2026-RN.pdf</t>
   </si>
   <si>
-    <t>AUTO-0159-21-05-2026-RN.pdf</t>
-  </si>
-  <si>
     <t>LA ESTACIÓN SOLAR S.A.S E.S.P</t>
   </si>
   <si>
@@ -946,9 +937,6 @@
     <t>LIZANDRO JOSE VEGA ARAUJO</t>
   </si>
   <si>
-    <t>CENIT TRANSPORTE Y LOGÍSTICA DE HIDROCARBUROS.S.A.S</t>
-  </si>
-  <si>
     <t>Calcularon carbono/biomasa</t>
   </si>
   <si>
@@ -1049,6 +1037,15 @@
   </si>
   <si>
     <t>RESOLUCION-0037-05-09-2025-RN.pdfa</t>
+  </si>
+  <si>
+    <t>CONSORCIO CONSTRUCTOR AUTOPISTA DEL RIO GRANDE</t>
+  </si>
+  <si>
+    <t>Resolucion</t>
+  </si>
+  <si>
+    <t>ERCO ENERGIA S.A.S</t>
   </si>
 </sst>
 </file>
@@ -1084,10 +1081,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1422,8 +1420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7620F5B7-47DE-4BC5-A97E-98454B0A0CF4}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:P172"/>
+  <dimension ref="A1:P178"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1431,9 +1428,9 @@
     <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.21875" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="112.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.77734375" customWidth="1"/>
+    <col min="8" max="8" width="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.21875" bestFit="1" customWidth="1"/>
@@ -1445,7 +1442,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
@@ -1457,7 +1454,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -1475,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L1" t="s">
         <v>27</v>
       </c>
       <c r="M1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N1" t="s">
         <v>6</v>
@@ -1492,7 +1489,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -1504,10 +1501,10 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="G2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2">
@@ -1520,18 +1517,18 @@
         <v>46062</v>
       </c>
       <c r="L2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -1546,10 +1543,10 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="G3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H3" s="2">
         <v>45602</v>
@@ -1574,9 +1571,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -1591,10 +1588,10 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H4" s="2">
         <v>45954</v>
@@ -1613,24 +1610,24 @@
         <v>579.298</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
       <c r="G5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2">
         <v>46051</v>
@@ -1641,9 +1638,9 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -1658,7 +1655,7 @@
         <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H6" s="2">
         <v>45939</v>
@@ -1669,9 +1666,9 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -1686,7 +1683,7 @@
         <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H7" s="2">
         <v>45982</v>
@@ -1697,9 +1694,9 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -1714,7 +1711,7 @@
         <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H8" s="2">
         <v>45986</v>
@@ -1725,9 +1722,9 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -1742,7 +1739,7 @@
         <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2">
         <v>45988</v>
@@ -1753,24 +1750,24 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
         <v>50</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
       <c r="G10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2">
@@ -1779,7 +1776,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -1793,45 +1790,51 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>318</v>
       </c>
       <c r="G11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2">
-        <v>46064</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>45392</v>
+      </c>
+      <c r="J11" s="2">
+        <v>45402</v>
+      </c>
+      <c r="K11" s="2">
+        <v>45604</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
         <v>54</v>
       </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
       <c r="G12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H12" s="2">
+        <v>45974</v>
+      </c>
       <c r="I12" s="2">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -1844,20 +1847,28 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>290</v>
       </c>
       <c r="G13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H13" s="2">
+        <v>46042</v>
+      </c>
       <c r="I13" s="2">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -1871,55 +1882,45 @@
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="2">
-        <v>45974</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H14" s="2"/>
       <c r="I14" s="2">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
         <v>58</v>
       </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
       <c r="G15" t="s">
-        <v>93</v>
-      </c>
-      <c r="H15" s="2">
-        <v>46042</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="H15" s="2"/>
       <c r="I15" s="2">
         <v>46062</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="N15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>59</v>
       </c>
@@ -1933,10 +1934,10 @@
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2">
@@ -1945,7 +1946,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -1959,10 +1960,10 @@
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2">
@@ -1971,9 +1972,9 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -1985,45 +1986,49 @@
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>93</v>
-      </c>
-      <c r="H18" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H18" s="2">
+        <v>46041</v>
+      </c>
       <c r="I18" s="2">
-        <v>46062</v>
+        <v>46059</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
         <v>63</v>
       </c>
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>20</v>
-      </c>
       <c r="G19" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H19" s="2">
+        <v>46020</v>
+      </c>
       <c r="I19" s="2">
-        <v>46062</v>
+        <v>46076</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -2037,23 +2042,23 @@
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="G20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H20" s="2">
-        <v>46041</v>
+        <v>45975</v>
       </c>
       <c r="I20" s="2">
-        <v>46059</v>
+        <v>46028</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -2065,21 +2070,27 @@
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>269</v>
       </c>
       <c r="G21" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H21" s="2">
-        <v>46020</v>
+        <v>46001</v>
       </c>
       <c r="I21" s="2">
-        <v>46076</v>
+        <v>46050</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="N21" t="s">
+        <v>12</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -2093,55 +2104,55 @@
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="G22" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H22" s="2">
-        <v>45975</v>
+        <v>46013</v>
       </c>
       <c r="I22" s="2">
-        <v>46028</v>
+        <v>46051</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
         <v>69</v>
       </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>279</v>
-      </c>
       <c r="G23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H23" s="2">
-        <v>46001</v>
-      </c>
-      <c r="I23" s="2">
+        <v>46037</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2">
         <v>46050</v>
       </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="N23" t="s">
-        <v>12</v>
-      </c>
-      <c r="O23">
+      <c r="L23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="M23">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -2149,61 +2160,64 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="G24" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2">
-        <v>46013</v>
-      </c>
-      <c r="I24" s="2">
-        <v>46051</v>
-      </c>
+        <v>45953</v>
+      </c>
+      <c r="I24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K24" s="2">
+        <v>46050</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
       </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="G25" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2">
-        <v>46037</v>
-      </c>
-      <c r="I25" s="2"/>
+        <v>46043</v>
+      </c>
+      <c r="I25" s="2">
+        <v>46083</v>
+      </c>
       <c r="J25" s="2"/>
-      <c r="K25" s="2">
-        <v>46050</v>
-      </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -2214,182 +2228,224 @@
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2">
+        <v>45874</v>
+      </c>
+      <c r="J26" s="2">
+        <v>45891</v>
+      </c>
+      <c r="K26" s="2">
+        <v>46097</v>
+      </c>
+      <c r="L26" t="s">
+        <v>37</v>
+      </c>
+      <c r="M26" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>74</v>
       </c>
-      <c r="G26" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" s="2">
-        <v>45953</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2">
-        <v>46050</v>
-      </c>
-      <c r="L26">
-        <v>2</v>
-      </c>
-      <c r="M26">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>75</v>
-      </c>
       <c r="B27" t="s">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2">
-        <v>46043</v>
+        <v>46009</v>
       </c>
       <c r="I27" s="2">
         <v>46083</v>
       </c>
       <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
+      <c r="K27" s="2">
+        <v>46248</v>
+      </c>
+      <c r="L27">
+        <v>557</v>
+      </c>
+      <c r="M27">
+        <v>301.72000000000003</v>
+      </c>
+      <c r="N27" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" t="s">
+        <v>89</v>
+      </c>
+      <c r="H28" s="2">
+        <v>46085</v>
+      </c>
+      <c r="I28" s="2">
+        <v>46099</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>76</v>
       </c>
-      <c r="B28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
         <v>17</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H29" s="2">
+        <v>46008</v>
+      </c>
+      <c r="I29" s="2">
+        <v>46062</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2">
+        <v>46090</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>29.981999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
         <v>4</v>
       </c>
-      <c r="F28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G28" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2">
-        <v>45874</v>
-      </c>
-      <c r="J28" s="2">
-        <v>45891</v>
-      </c>
-      <c r="K28" s="2">
-        <v>46097</v>
-      </c>
-      <c r="L28" t="s">
-        <v>38</v>
-      </c>
-      <c r="M28" t="s">
-        <v>38</v>
-      </c>
-      <c r="N28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>77</v>
-      </c>
-      <c r="B29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>30</v>
-      </c>
-      <c r="G29" t="s">
-        <v>93</v>
-      </c>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2">
-        <v>46083</v>
-      </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
       <c r="F30" t="s">
-        <v>30</v>
+        <v>270</v>
       </c>
       <c r="G30" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2">
-        <v>46083</v>
-      </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>45520</v>
+      </c>
+      <c r="J30" s="2">
+        <v>45546</v>
+      </c>
+      <c r="K30" s="2">
+        <v>46100</v>
+      </c>
+      <c r="L30" t="s">
+        <v>37</v>
+      </c>
+      <c r="M30" t="s">
+        <v>37</v>
+      </c>
+      <c r="N30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" s="2">
+        <v>45938</v>
+      </c>
+      <c r="I31" s="2">
+        <v>46062</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2">
+        <v>46097</v>
+      </c>
+      <c r="L31">
+        <v>15</v>
+      </c>
+      <c r="M31">
+        <v>82.825000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>79</v>
-      </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>28</v>
-      </c>
-      <c r="G31" t="s">
-        <v>93</v>
-      </c>
-      <c r="H31" s="2">
-        <v>46085</v>
-      </c>
-      <c r="I31" s="2">
-        <v>46099</v>
-      </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>80</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -2398,37 +2454,33 @@
         <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G32" t="s">
-        <v>93</v>
-      </c>
-      <c r="H32" s="2">
-        <v>46008</v>
-      </c>
-      <c r="I32" s="2">
-        <v>46062</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2">
-        <v>46090</v>
-      </c>
-      <c r="L32">
-        <v>1</v>
-      </c>
-      <c r="M32">
-        <v>29.981999999999999</v>
+        <v>46100</v>
+      </c>
+      <c r="L32" t="s">
+        <v>37</v>
+      </c>
+      <c r="M32" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -2440,34 +2492,34 @@
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>280</v>
+        <v>24</v>
       </c>
       <c r="G33" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2">
-        <v>45520</v>
+        <v>45874</v>
       </c>
       <c r="J33" s="2">
-        <v>45546</v>
+        <v>45903</v>
       </c>
       <c r="K33" s="2">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="L33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N33" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -2479,34 +2531,34 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G34" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H34" s="2">
-        <v>45938</v>
+        <v>45754</v>
       </c>
       <c r="I34" s="2">
-        <v>46062</v>
+        <v>45883</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2">
-        <v>46097</v>
-      </c>
-      <c r="L34">
-        <v>15</v>
+        <v>46105</v>
+      </c>
+      <c r="L34" s="1">
+        <v>239</v>
       </c>
       <c r="M34">
-        <v>82.825000000000003</v>
+        <v>5558.38</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
@@ -2518,22 +2570,26 @@
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>271</v>
       </c>
       <c r="G35" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
+      <c r="I35" s="2">
+        <v>45946</v>
+      </c>
+      <c r="J35" s="2">
+        <v>45971</v>
+      </c>
       <c r="K35" s="2">
         <v>46100</v>
       </c>
       <c r="L35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N35" t="s">
         <v>12</v>
@@ -2541,7 +2597,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
@@ -2553,34 +2609,34 @@
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="G36" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2">
-        <v>45874</v>
+        <v>45520</v>
       </c>
       <c r="J36" s="2">
-        <v>45903</v>
+        <v>45574</v>
       </c>
       <c r="K36" s="2">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="L36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N36" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -2589,32 +2645,28 @@
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="G37" t="s">
-        <v>93</v>
-      </c>
-      <c r="H37" s="2">
-        <v>45754</v>
-      </c>
-      <c r="I37" s="2">
-        <v>45883</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2">
         <v>46105</v>
       </c>
-      <c r="L37" s="1">
-        <v>239</v>
-      </c>
-      <c r="M37">
-        <v>5558.38</v>
+      <c r="L37" t="s">
+        <v>37</v>
+      </c>
+      <c r="M37" t="s">
+        <v>37</v>
+      </c>
+      <c r="N37" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
@@ -2631,26 +2683,26 @@
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="G38" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2">
-        <v>45946</v>
+        <v>45821</v>
       </c>
       <c r="J38" s="2">
-        <v>45971</v>
+        <v>45861</v>
       </c>
       <c r="K38" s="2">
-        <v>46100</v>
+        <v>46105</v>
       </c>
       <c r="L38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N38" t="s">
         <v>12</v>
@@ -2667,29 +2719,27 @@
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E39" t="s">
+        <v>13</v>
       </c>
       <c r="F39" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="G39" t="s">
-        <v>93</v>
-      </c>
-      <c r="H39" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H39" s="2">
+        <v>46118</v>
+      </c>
       <c r="I39" s="2">
-        <v>45520</v>
-      </c>
-      <c r="J39" s="2">
-        <v>45574</v>
-      </c>
-      <c r="K39" s="2">
-        <v>46100</v>
-      </c>
-      <c r="L39" t="s">
-        <v>38</v>
-      </c>
+        <v>46150</v>
+      </c>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
       <c r="M39" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="N39" t="s">
         <v>12</v>
@@ -2706,28 +2756,35 @@
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="G40" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
+      <c r="I40" s="2">
+        <v>45692</v>
+      </c>
+      <c r="J40" s="2">
+        <v>45713</v>
+      </c>
       <c r="K40" s="2">
-        <v>46105</v>
+        <v>46014</v>
       </c>
       <c r="L40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N40" t="s">
         <v>12</v>
+      </c>
+      <c r="O40">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
@@ -2744,32 +2801,32 @@
         <v>4</v>
       </c>
       <c r="F41" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="G41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2">
-        <v>45821</v>
+        <v>45967</v>
       </c>
       <c r="J41" s="2">
-        <v>45861</v>
+        <v>45980</v>
       </c>
       <c r="K41" s="2">
-        <v>46105</v>
+        <v>46014</v>
       </c>
       <c r="L41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -2780,30 +2837,32 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F42" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="G42" t="s">
-        <v>93</v>
-      </c>
-      <c r="H42" s="2">
-        <v>46118</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H42" s="2"/>
       <c r="I42" s="2">
-        <v>46150</v>
-      </c>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
+        <v>45952</v>
+      </c>
+      <c r="J42" s="2">
+        <v>45966</v>
+      </c>
+      <c r="K42" s="2">
+        <v>46014</v>
+      </c>
+      <c r="L42" t="s">
+        <v>37</v>
+      </c>
       <c r="M42" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N42" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
@@ -2823,34 +2882,31 @@
         <v>274</v>
       </c>
       <c r="G43" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2">
-        <v>45692</v>
+        <v>45776</v>
       </c>
       <c r="J43" s="2">
-        <v>45713</v>
+        <v>45800</v>
       </c>
       <c r="K43" s="2">
-        <v>46014</v>
+        <v>46003</v>
       </c>
       <c r="L43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N43" t="s">
         <v>12</v>
-      </c>
-      <c r="O43">
-        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -2859,29 +2915,32 @@
         <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E44" t="s">
+        <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>283</v>
+        <v>94</v>
       </c>
       <c r="G44" t="s">
-        <v>93</v>
-      </c>
-      <c r="H44" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H44" s="2">
+        <v>45674</v>
+      </c>
       <c r="I44" s="2">
-        <v>45967</v>
-      </c>
-      <c r="J44" s="2">
-        <v>45980</v>
-      </c>
+        <v>45677</v>
+      </c>
+      <c r="J44" s="2"/>
       <c r="K44" s="2">
         <v>46014</v>
       </c>
-      <c r="L44" t="s">
-        <v>38</v>
-      </c>
-      <c r="M44" t="s">
-        <v>38</v>
+      <c r="L44">
+        <v>126</v>
+      </c>
+      <c r="M44">
+        <v>1052.8</v>
       </c>
       <c r="N44" t="s">
         <v>12</v>
@@ -2898,29 +2957,32 @@
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E45" t="s">
+        <v>13</v>
       </c>
       <c r="F45" t="s">
-        <v>284</v>
+        <v>97</v>
       </c>
       <c r="G45" t="s">
-        <v>93</v>
-      </c>
-      <c r="H45" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H45" s="2">
+        <v>45814</v>
+      </c>
       <c r="I45" s="2">
-        <v>45952</v>
-      </c>
-      <c r="J45" s="2">
-        <v>45966</v>
-      </c>
+        <v>45846</v>
+      </c>
+      <c r="J45" s="2"/>
       <c r="K45" s="2">
-        <v>46014</v>
-      </c>
-      <c r="L45" t="s">
-        <v>38</v>
-      </c>
-      <c r="M45" t="s">
-        <v>38</v>
+        <v>46009</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>4.37</v>
       </c>
       <c r="N45" t="s">
         <v>12</v>
@@ -2928,7 +2990,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
@@ -2937,37 +2999,40 @@
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E46" t="s">
+        <v>13</v>
       </c>
       <c r="F46" t="s">
-        <v>284</v>
+        <v>99</v>
       </c>
       <c r="G46" t="s">
-        <v>93</v>
-      </c>
-      <c r="H46" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H46" s="2">
+        <v>45967</v>
+      </c>
       <c r="I46" s="2">
-        <v>45776</v>
-      </c>
-      <c r="J46" s="2">
-        <v>45800</v>
-      </c>
+        <v>45974</v>
+      </c>
+      <c r="J46" s="2"/>
       <c r="K46" s="2">
-        <v>46003</v>
-      </c>
-      <c r="L46" t="s">
-        <v>38</v>
-      </c>
-      <c r="M46" t="s">
-        <v>38</v>
+        <v>46007</v>
+      </c>
+      <c r="L46">
+        <v>9</v>
+      </c>
+      <c r="M46">
+        <v>51.7</v>
       </c>
       <c r="N46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -2982,34 +3047,34 @@
         <v>13</v>
       </c>
       <c r="F47" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H47" s="2">
-        <v>45674</v>
+        <v>45811</v>
       </c>
       <c r="I47" s="2">
-        <v>45677</v>
+        <v>45959</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2">
-        <v>46014</v>
+        <v>45996</v>
       </c>
       <c r="L47">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="M47">
-        <v>1052.8</v>
+        <v>1.2450000000000001</v>
       </c>
       <c r="N47" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -3024,94 +3089,84 @@
         <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="G48" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H48" s="2">
-        <v>45814</v>
+        <v>45937</v>
       </c>
       <c r="I48" s="2">
-        <v>45846</v>
+        <v>45966</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2">
-        <v>46009</v>
+        <v>46001</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M48">
-        <v>4.37</v>
+        <v>10.949</v>
       </c>
       <c r="N48" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49" t="s">
         <v>9</v>
       </c>
-      <c r="E49" t="s">
-        <v>13</v>
-      </c>
       <c r="F49" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G49" t="s">
-        <v>93</v>
-      </c>
-      <c r="H49" s="2">
-        <v>45967</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="H49" s="2"/>
       <c r="I49" s="2">
-        <v>45974</v>
+        <v>45994</v>
       </c>
       <c r="J49" s="2"/>
-      <c r="K49" s="2">
-        <v>46007</v>
-      </c>
-      <c r="L49">
-        <v>9</v>
-      </c>
-      <c r="M49">
-        <v>51.7</v>
+      <c r="K49" s="2"/>
+      <c r="L49" t="s">
+        <v>37</v>
+      </c>
+      <c r="M49" t="s">
+        <v>37</v>
       </c>
       <c r="N49" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B50" t="s">
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D50" t="s">
         <v>9</v>
       </c>
-      <c r="E50" t="s">
-        <v>13</v>
-      </c>
       <c r="F50" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G50" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H50" s="2">
         <v>45811</v>
@@ -3120,20 +3175,18 @@
         <v>45959</v>
       </c>
       <c r="J50" s="2"/>
-      <c r="K50" s="2">
-        <v>45996</v>
-      </c>
-      <c r="L50">
-        <v>1</v>
-      </c>
-      <c r="M50">
-        <v>1.2450000000000001</v>
+      <c r="K50" s="2"/>
+      <c r="L50" t="s">
+        <v>37</v>
+      </c>
+      <c r="M50" t="s">
+        <v>37</v>
       </c>
       <c r="N50" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>107</v>
       </c>
@@ -3141,7 +3194,7 @@
         <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D51" t="s">
         <v>9</v>
@@ -3150,29 +3203,27 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="G51" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H51" s="2">
-        <v>45937</v>
+        <v>45881</v>
       </c>
       <c r="I51" s="2">
-        <v>45966</v>
+        <v>45959</v>
       </c>
       <c r="J51" s="2"/>
-      <c r="K51" s="2">
-        <v>46001</v>
-      </c>
-      <c r="L51">
-        <v>10</v>
-      </c>
-      <c r="M51">
-        <v>10.949</v>
+      <c r="K51" s="2"/>
+      <c r="L51" t="s">
+        <v>37</v>
+      </c>
+      <c r="M51" t="s">
+        <v>37</v>
       </c>
       <c r="N51" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
@@ -3192,21 +3243,21 @@
         <v>109</v>
       </c>
       <c r="G52" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H52" s="2">
-        <v>45674</v>
+        <v>45922</v>
       </c>
       <c r="I52" s="2">
-        <v>46003</v>
+        <v>45951</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N52" t="s">
         <v>12</v>
@@ -3226,22 +3277,22 @@
         <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="G53" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2">
-        <v>45994</v>
+        <v>45951</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N53" t="s">
         <v>12</v>
@@ -3249,7 +3300,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B54" t="s">
         <v>8</v>
@@ -3261,24 +3312,24 @@
         <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="G54" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H54" s="2">
-        <v>45811</v>
+        <v>45833</v>
       </c>
       <c r="I54" s="2">
-        <v>45959</v>
+        <v>45939</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N54" t="s">
         <v>12</v>
@@ -3297,28 +3348,25 @@
       <c r="D55" t="s">
         <v>9</v>
       </c>
-      <c r="E55" t="s">
-        <v>13</v>
-      </c>
       <c r="F55" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="G55" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H55" s="2">
-        <v>45881</v>
+        <v>45925</v>
       </c>
       <c r="I55" s="2">
-        <v>45959</v>
+        <v>45939</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N55" t="s">
         <v>12</v>
@@ -3332,110 +3380,129 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>278</v>
       </c>
       <c r="G56" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H56" s="2">
-        <v>45922</v>
+        <v>45485</v>
       </c>
       <c r="I56" s="2">
-        <v>45951</v>
-      </c>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
+        <v>45583</v>
+      </c>
+      <c r="J56" s="2">
+        <v>45603</v>
+      </c>
+      <c r="K56" s="2">
+        <v>45933</v>
+      </c>
       <c r="L56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N56" t="s">
         <v>12</v>
+      </c>
+      <c r="O56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B57" t="s">
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F57" t="s">
-        <v>22</v>
+        <v>279</v>
       </c>
       <c r="G57" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2">
-        <v>45951</v>
-      </c>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
+        <v>45786</v>
+      </c>
+      <c r="J57" s="2">
+        <v>45811</v>
+      </c>
+      <c r="K57" s="2">
+        <v>45933</v>
+      </c>
       <c r="L57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N57" t="s">
         <v>12</v>
+      </c>
+      <c r="O57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B58" t="s">
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>118</v>
+        <v>279</v>
       </c>
       <c r="G58" t="s">
-        <v>93</v>
-      </c>
-      <c r="H58" s="2">
-        <v>45833</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H58" s="2"/>
       <c r="I58" s="2">
-        <v>45939</v>
-      </c>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
+        <v>45786</v>
+      </c>
+      <c r="J58" s="2">
+        <v>45813</v>
+      </c>
+      <c r="K58" s="2">
+        <v>45932</v>
+      </c>
       <c r="L58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N58" t="s">
         <v>12</v>
+      </c>
+      <c r="O58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
         <v>8</v>
@@ -3444,27 +3511,25 @@
         <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F59" t="s">
-        <v>287</v>
+        <v>118</v>
       </c>
       <c r="G59" t="s">
-        <v>93</v>
-      </c>
-      <c r="H59" s="2">
-        <v>45925</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H59" s="2"/>
       <c r="I59" s="2">
-        <v>45939</v>
+        <v>45954</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N59" t="s">
         <v>12</v>
@@ -3472,46 +3537,37 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B60" t="s">
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D60" t="s">
         <v>4</v>
       </c>
       <c r="F60" t="s">
-        <v>288</v>
+        <v>118</v>
       </c>
       <c r="G60" t="s">
-        <v>93</v>
-      </c>
-      <c r="H60" s="2">
-        <v>45485</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H60" s="2"/>
       <c r="I60" s="2">
-        <v>45583</v>
-      </c>
-      <c r="J60" s="2">
-        <v>45603</v>
-      </c>
-      <c r="K60" s="2">
-        <v>45933</v>
-      </c>
+        <v>45954</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
       <c r="L60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N60" t="s">
         <v>12</v>
-      </c>
-      <c r="O60">
-        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
@@ -3522,38 +3578,31 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D61" t="s">
         <v>4</v>
       </c>
       <c r="F61" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="G61" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2">
-        <v>45786</v>
-      </c>
-      <c r="J61" s="2">
-        <v>45811</v>
-      </c>
-      <c r="K61" s="2">
-        <v>45933</v>
-      </c>
+        <v>45936</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
       <c r="L61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N61" t="s">
         <v>12</v>
-      </c>
-      <c r="O61">
-        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
@@ -3564,43 +3613,36 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D62" t="s">
         <v>4</v>
       </c>
       <c r="F62" t="s">
-        <v>290</v>
+        <v>123</v>
       </c>
       <c r="G62" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2">
-        <v>45786</v>
-      </c>
-      <c r="J62" s="2">
-        <v>45813</v>
-      </c>
-      <c r="K62" s="2">
-        <v>45932</v>
-      </c>
+        <v>45945</v>
+      </c>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
       <c r="L62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N62" t="s">
         <v>12</v>
-      </c>
-      <c r="O62">
-        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B63" t="s">
         <v>8</v>
@@ -3612,22 +3654,22 @@
         <v>4</v>
       </c>
       <c r="F63" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G63" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2">
-        <v>45954</v>
+        <v>45944</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
       <c r="L63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N63" t="s">
         <v>12</v>
@@ -3635,7 +3677,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B64" t="s">
         <v>8</v>
@@ -3647,22 +3689,22 @@
         <v>4</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>270</v>
       </c>
       <c r="G64" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2">
-        <v>45954</v>
+        <v>46224</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
       <c r="L64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N64" t="s">
         <v>12</v>
@@ -3685,19 +3727,19 @@
         <v>128</v>
       </c>
       <c r="G65" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2">
-        <v>45936</v>
+        <v>46218</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
       <c r="L65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N65" t="s">
         <v>12</v>
@@ -3717,22 +3759,22 @@
         <v>4</v>
       </c>
       <c r="F66" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G66" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2">
-        <v>45945</v>
+        <v>46218</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
       <c r="L66" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M66" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N66" t="s">
         <v>12</v>
@@ -3740,69 +3782,86 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
         <v>131</v>
       </c>
-      <c r="B67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" t="s">
-        <v>16</v>
-      </c>
-      <c r="D67" t="s">
-        <v>4</v>
-      </c>
-      <c r="F67" t="s">
-        <v>132</v>
-      </c>
       <c r="G67" t="s">
-        <v>37</v>
-      </c>
-      <c r="H67" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H67" s="2">
+        <v>46149</v>
+      </c>
       <c r="I67" s="2">
-        <v>45944</v>
+        <v>46189</v>
       </c>
       <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" t="s">
-        <v>38</v>
-      </c>
-      <c r="M67" t="s">
-        <v>38</v>
+      <c r="K67" s="2">
+        <v>46233</v>
+      </c>
+      <c r="L67">
+        <v>18</v>
+      </c>
+      <c r="M67">
+        <v>33.58</v>
       </c>
       <c r="N67" t="s">
         <v>12</v>
+      </c>
+      <c r="O67">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B68" t="s">
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E68" t="s">
+        <v>13</v>
       </c>
       <c r="F68" t="s">
-        <v>128</v>
+        <v>281</v>
       </c>
       <c r="G68" t="s">
-        <v>93</v>
-      </c>
-      <c r="H68" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H68" s="2">
+        <v>46176</v>
+      </c>
       <c r="I68" s="2">
-        <v>46224</v>
+        <v>46195</v>
       </c>
       <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" t="s">
-        <v>38</v>
-      </c>
-      <c r="M68" t="s">
-        <v>38</v>
+      <c r="K68" s="2">
+        <v>46227</v>
+      </c>
+      <c r="L68">
+        <v>12</v>
+      </c>
+      <c r="M68">
+        <v>35.67</v>
       </c>
       <c r="N68" t="s">
         <v>12</v>
@@ -3810,34 +3869,43 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B69" t="s">
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E69" t="s">
+        <v>13</v>
       </c>
       <c r="F69" t="s">
-        <v>135</v>
+        <v>282</v>
       </c>
       <c r="G69" t="s">
-        <v>93</v>
-      </c>
-      <c r="H69" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H69" s="2">
+        <v>46049</v>
+      </c>
       <c r="I69" s="2">
-        <v>46218</v>
-      </c>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" t="s">
-        <v>38</v>
-      </c>
-      <c r="M69" t="s">
-        <v>38</v>
+        <v>46198</v>
+      </c>
+      <c r="J69" s="2">
+        <v>46204</v>
+      </c>
+      <c r="K69" s="2">
+        <v>46220</v>
+      </c>
+      <c r="L69">
+        <v>102</v>
+      </c>
+      <c r="M69">
+        <v>1096.1410000000001</v>
       </c>
       <c r="N69" t="s">
         <v>12</v>
@@ -3845,42 +3913,49 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>134</v>
+      </c>
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" t="s">
+        <v>283</v>
+      </c>
+      <c r="G70" t="s">
+        <v>95</v>
+      </c>
+      <c r="H70" s="2">
+        <v>46224</v>
+      </c>
+      <c r="I70" s="2">
+        <v>46162</v>
+      </c>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2">
+        <v>46211</v>
+      </c>
+      <c r="L70">
+        <v>152</v>
+      </c>
+      <c r="M70">
+        <v>380.57100000000003</v>
+      </c>
+      <c r="N70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>136</v>
-      </c>
-      <c r="B70" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" t="s">
-        <v>16</v>
-      </c>
-      <c r="D70" t="s">
-        <v>4</v>
-      </c>
-      <c r="F70" t="s">
-        <v>135</v>
-      </c>
-      <c r="G70" t="s">
-        <v>93</v>
-      </c>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2">
-        <v>46218</v>
-      </c>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-      <c r="L70" t="s">
-        <v>38</v>
-      </c>
-      <c r="M70" t="s">
-        <v>38</v>
-      </c>
-      <c r="N70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>137</v>
       </c>
       <c r="B71" t="s">
         <v>8</v>
@@ -3892,40 +3967,37 @@
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F71" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="G71" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H71" s="2">
-        <v>46149</v>
+        <v>45873</v>
       </c>
       <c r="I71" s="2">
-        <v>46189</v>
+        <v>45901</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2">
-        <v>46233</v>
+        <v>46206</v>
       </c>
       <c r="L71">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M71">
-        <v>33.58</v>
+        <v>4.58</v>
       </c>
       <c r="N71" t="s">
-        <v>94</v>
-      </c>
-      <c r="O71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B72" t="s">
         <v>8</v>
@@ -3937,37 +4009,40 @@
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F72" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="G72" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H72" s="2">
-        <v>46176</v>
+        <v>45448</v>
       </c>
       <c r="I72" s="2">
-        <v>46195</v>
+        <v>45527</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2">
-        <v>46227</v>
+        <v>46184</v>
       </c>
       <c r="L72">
-        <v>12</v>
+        <v>142</v>
       </c>
       <c r="M72">
-        <v>35.67</v>
+        <v>294.24</v>
       </c>
       <c r="N72" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="O72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B73" t="s">
         <v>8</v>
@@ -3979,39 +4054,43 @@
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F73" t="s">
-        <v>292</v>
+        <v>43</v>
       </c>
       <c r="G73" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H73" s="2">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="I73" s="2">
-        <v>46198</v>
-      </c>
-      <c r="J73" s="2">
-        <v>46204</v>
-      </c>
+        <v>46080</v>
+      </c>
+      <c r="J73" s="2"/>
       <c r="K73" s="2">
-        <v>46220</v>
+        <v>46184</v>
       </c>
       <c r="L73">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="M73">
-        <v>1096.1410000000001</v>
+        <v>12.025</v>
       </c>
       <c r="N73" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="O73">
+        <v>1</v>
+      </c>
+      <c r="P73" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B74" t="s">
         <v>8</v>
@@ -4023,37 +4102,39 @@
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F74" t="s">
-        <v>293</v>
+        <v>28</v>
       </c>
       <c r="G74" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H74" s="2">
-        <v>46224</v>
+        <v>45833</v>
       </c>
       <c r="I74" s="2">
-        <v>46162</v>
-      </c>
-      <c r="J74" s="2"/>
+        <v>45868</v>
+      </c>
+      <c r="J74" s="2">
+        <v>45939</v>
+      </c>
       <c r="K74" s="2">
-        <v>46211</v>
+        <v>46175</v>
       </c>
       <c r="L74">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="M74">
-        <v>380.57100000000003</v>
+        <v>23.67</v>
       </c>
       <c r="N74" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B75" t="s">
         <v>8</v>
@@ -4064,23 +4145,30 @@
       <c r="D75" t="s">
         <v>9</v>
       </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
       <c r="F75" t="s">
-        <v>143</v>
+        <v>285</v>
       </c>
       <c r="G75" t="s">
-        <v>93</v>
-      </c>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H75" s="2">
+        <v>46049</v>
+      </c>
+      <c r="I75" s="2">
+        <v>46170</v>
+      </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2">
-        <v>46219</v>
-      </c>
-      <c r="L75" t="s">
-        <v>38</v>
-      </c>
-      <c r="M75" t="s">
-        <v>38</v>
+        <v>46183</v>
+      </c>
+      <c r="L75">
+        <v>109</v>
+      </c>
+      <c r="M75">
+        <v>1172.77</v>
       </c>
       <c r="N75" t="s">
         <v>12</v>
@@ -4088,187 +4176,173 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>142</v>
+      </c>
+      <c r="B76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76" t="s">
+        <v>89</v>
+      </c>
+      <c r="H76" s="2">
+        <v>46149</v>
+      </c>
+      <c r="I76" s="2">
+        <v>46203</v>
+      </c>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" t="s">
+        <v>37</v>
+      </c>
+      <c r="M76" t="s">
+        <v>37</v>
+      </c>
+      <c r="N76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>144</v>
       </c>
-      <c r="B76" t="s">
-        <v>8</v>
-      </c>
-      <c r="C76" t="s">
-        <v>17</v>
-      </c>
-      <c r="D76" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="B77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" t="s">
+        <v>286</v>
+      </c>
+      <c r="G77" t="s">
+        <v>95</v>
+      </c>
+      <c r="H77" s="2">
+        <v>46174</v>
+      </c>
+      <c r="I77" s="2">
+        <v>46199</v>
+      </c>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" t="s">
+        <v>37</v>
+      </c>
+      <c r="M77" t="s">
+        <v>37</v>
+      </c>
+      <c r="N77" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>145</v>
       </c>
-      <c r="G76" t="s">
-        <v>93</v>
-      </c>
-      <c r="H76" s="2">
-        <v>45873</v>
-      </c>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2">
-        <v>46206</v>
-      </c>
-      <c r="L76" t="s">
-        <v>38</v>
-      </c>
-      <c r="M76" t="s">
-        <v>38</v>
-      </c>
-      <c r="N76" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>146</v>
-      </c>
-      <c r="B77" t="s">
-        <v>8</v>
-      </c>
-      <c r="C77" t="s">
-        <v>17</v>
-      </c>
-      <c r="D77" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" t="s">
-        <v>294</v>
-      </c>
-      <c r="G77" t="s">
-        <v>93</v>
-      </c>
-      <c r="H77" s="2">
-        <v>45448</v>
-      </c>
-      <c r="I77" s="2">
-        <v>45527</v>
-      </c>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2">
-        <v>46184</v>
-      </c>
-      <c r="L77">
-        <v>142</v>
-      </c>
-      <c r="M77">
-        <v>294.24</v>
-      </c>
-      <c r="N77" t="s">
-        <v>94</v>
-      </c>
-      <c r="O77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>147</v>
-      </c>
       <c r="B78" t="s">
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D78" t="s">
         <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>44</v>
+        <v>288</v>
       </c>
       <c r="G78" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H78" s="2">
-        <v>46051</v>
+        <v>46161</v>
       </c>
       <c r="I78" s="2">
-        <v>46080</v>
+        <v>46199</v>
       </c>
       <c r="J78" s="2"/>
-      <c r="K78" s="2">
-        <v>46184</v>
-      </c>
-      <c r="L78">
-        <v>16</v>
-      </c>
-      <c r="M78">
-        <v>12.025</v>
+      <c r="K78" s="2"/>
+      <c r="L78" t="s">
+        <v>37</v>
+      </c>
+      <c r="M78" t="s">
+        <v>37</v>
       </c>
       <c r="N78" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="O78">
         <v>1</v>
       </c>
-      <c r="P78" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B79" t="s">
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D79" t="s">
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F79" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="G79" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H79" s="2">
-        <v>45833</v>
+        <v>46049</v>
       </c>
       <c r="I79" s="2">
-        <v>45868</v>
-      </c>
-      <c r="J79" s="2">
-        <v>45939</v>
-      </c>
-      <c r="K79" s="2">
-        <v>46175</v>
-      </c>
-      <c r="L79">
-        <v>73</v>
-      </c>
-      <c r="M79">
-        <v>23.67</v>
+        <v>46198</v>
+      </c>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" t="s">
+        <v>37</v>
+      </c>
+      <c r="M79" t="s">
+        <v>37</v>
       </c>
       <c r="N79" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B80" t="s">
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
@@ -4277,34 +4351,32 @@
         <v>13</v>
       </c>
       <c r="F80" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="G80" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H80" s="2">
-        <v>46049</v>
+        <v>46176</v>
       </c>
       <c r="I80" s="2">
-        <v>46170</v>
+        <v>46197</v>
       </c>
       <c r="J80" s="2"/>
-      <c r="K80" s="2">
-        <v>46183</v>
-      </c>
-      <c r="L80">
-        <v>109</v>
-      </c>
-      <c r="M80">
-        <v>1172.77</v>
+      <c r="K80" s="2"/>
+      <c r="L80" t="s">
+        <v>37</v>
+      </c>
+      <c r="M80" t="s">
+        <v>37</v>
       </c>
       <c r="N80" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B81" t="s">
         <v>8</v>
@@ -4315,25 +4387,28 @@
       <c r="D81" t="s">
         <v>9</v>
       </c>
+      <c r="E81" t="s">
+        <v>13</v>
+      </c>
       <c r="F81" t="s">
-        <v>151</v>
+        <v>289</v>
       </c>
       <c r="G81" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H81" s="2">
-        <v>46149</v>
+        <v>46135</v>
       </c>
       <c r="I81" s="2">
-        <v>46203</v>
+        <v>46195</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
       <c r="L81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N81" t="s">
         <v>12</v>
@@ -4341,7 +4416,7 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B82" t="s">
         <v>8</v>
@@ -4352,28 +4427,25 @@
       <c r="D82" t="s">
         <v>9</v>
       </c>
-      <c r="E82" t="s">
-        <v>13</v>
-      </c>
       <c r="F82" t="s">
-        <v>297</v>
+        <v>150</v>
       </c>
       <c r="G82" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H82" s="2">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="I82" s="2">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
       <c r="L82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N82" t="s">
         <v>12</v>
@@ -4381,7 +4453,7 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B83" t="s">
         <v>8</v>
@@ -4392,39 +4464,33 @@
       <c r="D83" t="s">
         <v>9</v>
       </c>
-      <c r="E83" t="s">
-        <v>13</v>
-      </c>
       <c r="F83" t="s">
-        <v>299</v>
+        <v>131</v>
       </c>
       <c r="G83" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H83" s="2">
-        <v>46161</v>
+        <v>46169</v>
       </c>
       <c r="I83" s="2">
-        <v>46199</v>
+        <v>46189</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
       <c r="L83" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M83" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N83" t="s">
         <v>12</v>
-      </c>
-      <c r="O83">
-        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B84" t="s">
         <v>8</v>
@@ -4436,27 +4502,27 @@
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F84" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G84" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H84" s="2">
-        <v>46049</v>
+        <v>46120</v>
       </c>
       <c r="I84" s="2">
-        <v>46198</v>
+        <v>46183</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
       <c r="L84" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M84" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N84" t="s">
         <v>12</v>
@@ -4464,7 +4530,7 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B85" t="s">
         <v>8</v>
@@ -4476,27 +4542,27 @@
         <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F85" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G85" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H85" s="2">
-        <v>46176</v>
+        <v>46120</v>
       </c>
       <c r="I85" s="2">
-        <v>46197</v>
+        <v>46183</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
       <c r="L85" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M85" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N85" t="s">
         <v>12</v>
@@ -4504,7 +4570,7 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B86" t="s">
         <v>8</v>
@@ -4515,28 +4581,23 @@
       <c r="D86" t="s">
         <v>9</v>
       </c>
-      <c r="E86" t="s">
-        <v>13</v>
-      </c>
       <c r="F86" t="s">
-        <v>300</v>
+        <v>155</v>
       </c>
       <c r="G86" t="s">
-        <v>93</v>
-      </c>
-      <c r="H86" s="2">
-        <v>46135</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H86" s="2"/>
       <c r="I86" s="2">
-        <v>46195</v>
+        <v>46182</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
       <c r="L86" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M86" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N86" t="s">
         <v>12</v>
@@ -4544,36 +4605,34 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>156</v>
+      </c>
+      <c r="B87" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" t="s">
         <v>157</v>
       </c>
-      <c r="B87" t="s">
-        <v>8</v>
-      </c>
-      <c r="C87" t="s">
-        <v>16</v>
-      </c>
-      <c r="D87" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" t="s">
-        <v>158</v>
-      </c>
       <c r="G87" t="s">
-        <v>93</v>
-      </c>
-      <c r="H87" s="2">
-        <v>46171</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="H87" s="2"/>
       <c r="I87" s="2">
-        <v>46195</v>
+        <v>46177</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
       <c r="L87" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M87" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N87" t="s">
         <v>12</v>
@@ -4581,36 +4640,36 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>158</v>
+      </c>
+      <c r="B88" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" t="s">
         <v>159</v>
       </c>
-      <c r="B88" t="s">
-        <v>8</v>
-      </c>
-      <c r="C88" t="s">
-        <v>16</v>
-      </c>
-      <c r="D88" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" t="s">
-        <v>138</v>
-      </c>
       <c r="G88" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H88" s="2">
-        <v>46169</v>
+        <v>46059</v>
       </c>
       <c r="I88" s="2">
-        <v>46189</v>
+        <v>46175</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
       <c r="L88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N88" t="s">
         <v>12</v>
@@ -4624,36 +4683,41 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D89" t="s">
         <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>15</v>
+        <v>291</v>
       </c>
       <c r="F89" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="G89" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H89" s="2">
-        <v>46120</v>
+        <v>45881</v>
       </c>
       <c r="I89" s="2">
-        <v>46183</v>
+        <v>45959</v>
       </c>
       <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="L89" t="s">
-        <v>38</v>
-      </c>
-      <c r="M89" t="s">
-        <v>38</v>
+      <c r="K89" s="2">
+        <v>45988</v>
+      </c>
+      <c r="L89">
+        <v>27</v>
+      </c>
+      <c r="M89">
+        <v>3.5209999999999999</v>
       </c>
       <c r="N89" t="s">
         <v>12</v>
+      </c>
+      <c r="O89">
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
@@ -4664,36 +4728,43 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D90" t="s">
         <v>9</v>
       </c>
       <c r="E90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F90" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="G90" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H90" s="2">
-        <v>46120</v>
+        <v>45959</v>
       </c>
       <c r="I90" s="2">
-        <v>46183</v>
-      </c>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" t="s">
-        <v>38</v>
-      </c>
-      <c r="M90" t="s">
-        <v>38</v>
+        <v>45971</v>
+      </c>
+      <c r="J90" s="2">
+        <v>45974</v>
+      </c>
+      <c r="K90" s="2">
+        <v>45980</v>
+      </c>
+      <c r="L90">
+        <v>3</v>
+      </c>
+      <c r="M90">
+        <v>0.69899999999999995</v>
       </c>
       <c r="N90" t="s">
         <v>12</v>
+      </c>
+      <c r="P90" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
@@ -4709,31 +4780,39 @@
       <c r="D91" t="s">
         <v>9</v>
       </c>
+      <c r="E91" t="s">
+        <v>13</v>
+      </c>
       <c r="F91" t="s">
-        <v>163</v>
+        <v>294</v>
       </c>
       <c r="G91" t="s">
-        <v>93</v>
-      </c>
-      <c r="H91" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H91" s="2">
+        <v>45911</v>
+      </c>
       <c r="I91" s="2">
-        <v>46182</v>
+        <v>45986</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
       <c r="L91" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M91" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N91" t="s">
         <v>12</v>
+      </c>
+      <c r="O91">
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B92" t="s">
         <v>8</v>
@@ -4745,22 +4824,22 @@
         <v>9</v>
       </c>
       <c r="F92" t="s">
-        <v>165</v>
+        <v>318</v>
       </c>
       <c r="G92" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H92" s="2"/>
       <c r="I92" s="2">
-        <v>46177</v>
+        <v>45985</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
       <c r="L92" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M92" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N92" t="s">
         <v>12</v>
@@ -4768,7 +4847,7 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B93" t="s">
         <v>8</v>
@@ -4780,124 +4859,104 @@
         <v>9</v>
       </c>
       <c r="F93" t="s">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="G93" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H93" s="2">
-        <v>46059</v>
+        <v>45852</v>
       </c>
       <c r="I93" s="2">
-        <v>46175</v>
+        <v>45985</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
       <c r="L93" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M93" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B94" t="s">
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
         <v>9</v>
       </c>
-      <c r="E94" t="s">
-        <v>302</v>
-      </c>
       <c r="F94" t="s">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="G94" t="s">
-        <v>100</v>
-      </c>
-      <c r="H94" s="2">
-        <v>45881</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H94" s="2"/>
       <c r="I94" s="2">
-        <v>45959</v>
+        <v>45985</v>
       </c>
       <c r="J94" s="2"/>
-      <c r="K94" s="2">
-        <v>45988</v>
-      </c>
-      <c r="L94">
-        <v>27</v>
-      </c>
-      <c r="M94">
-        <v>3.5209999999999999</v>
+      <c r="K94" s="2"/>
+      <c r="L94" t="s">
+        <v>37</v>
+      </c>
+      <c r="M94" t="s">
+        <v>37</v>
       </c>
       <c r="N94" t="s">
-        <v>94</v>
-      </c>
-      <c r="O94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B95" t="s">
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D95" t="s">
         <v>9</v>
       </c>
-      <c r="E95" t="s">
-        <v>13</v>
-      </c>
       <c r="F95" t="s">
-        <v>303</v>
+        <v>31</v>
       </c>
       <c r="G95" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H95" s="2">
-        <v>45959</v>
+        <v>45953</v>
       </c>
       <c r="I95" s="2">
-        <v>45971</v>
-      </c>
-      <c r="J95" s="2">
-        <v>45974</v>
-      </c>
-      <c r="K95" s="2">
         <v>45980</v>
       </c>
-      <c r="L95">
-        <v>3</v>
-      </c>
-      <c r="M95">
-        <v>0.69899999999999995</v>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" t="s">
+        <v>37</v>
+      </c>
+      <c r="M95" t="s">
+        <v>37</v>
       </c>
       <c r="N95" t="s">
-        <v>94</v>
-      </c>
-      <c r="P95" t="s">
-        <v>304</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B96" t="s">
         <v>8</v>
@@ -4912,35 +4971,32 @@
         <v>13</v>
       </c>
       <c r="F96" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="G96" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H96" s="2">
-        <v>45911</v>
+        <v>45980</v>
       </c>
       <c r="I96" s="2">
-        <v>45986</v>
+        <v>45982</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
       <c r="L96" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M96" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N96" t="s">
         <v>12</v>
       </c>
-      <c r="O96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B97" t="s">
         <v>8</v>
@@ -4952,30 +5008,32 @@
         <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="G97" t="s">
-        <v>93</v>
-      </c>
-      <c r="H97" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H97" s="2">
+        <v>45967</v>
+      </c>
       <c r="I97" s="2">
-        <v>45985</v>
+        <v>45974</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
       <c r="L97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N97" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B98" t="s">
         <v>8</v>
@@ -4986,33 +5044,36 @@
       <c r="D98" t="s">
         <v>9</v>
       </c>
+      <c r="E98" t="s">
+        <v>13</v>
+      </c>
       <c r="F98" t="s">
-        <v>28</v>
+        <v>292</v>
       </c>
       <c r="G98" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H98" s="2">
-        <v>45852</v>
+        <v>45959</v>
       </c>
       <c r="I98" s="2">
-        <v>45985</v>
+        <v>45971</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
       <c r="L98" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M98" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N98" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B99" t="s">
         <v>8</v>
@@ -5024,30 +5085,32 @@
         <v>9</v>
       </c>
       <c r="F99" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="G99" t="s">
-        <v>93</v>
-      </c>
-      <c r="H99" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H99" s="2">
+        <v>45954</v>
+      </c>
       <c r="I99" s="2">
-        <v>45985</v>
+        <v>45973</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
       <c r="L99" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M99" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N99" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B100" t="s">
         <v>8</v>
@@ -5059,32 +5122,32 @@
         <v>9</v>
       </c>
       <c r="F100" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G100" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H100" s="2">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="I100" s="2">
-        <v>45980</v>
+        <v>45973</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
       <c r="L100" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M100" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N100" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B101" t="s">
         <v>8</v>
@@ -5095,36 +5158,33 @@
       <c r="D101" t="s">
         <v>9</v>
       </c>
-      <c r="E101" t="s">
-        <v>13</v>
-      </c>
       <c r="F101" t="s">
-        <v>306</v>
+        <v>28</v>
       </c>
       <c r="G101" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H101" s="2">
-        <v>45980</v>
+        <v>45799</v>
       </c>
       <c r="I101" s="2">
-        <v>45982</v>
+        <v>45971</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
       <c r="L101" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M101" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N101" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B102" t="s">
         <v>8</v>
@@ -5136,32 +5196,32 @@
         <v>9</v>
       </c>
       <c r="F102" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="G102" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H102" s="2">
-        <v>45967</v>
+        <v>45852</v>
       </c>
       <c r="I102" s="2">
-        <v>45974</v>
+        <v>45971</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
       <c r="L102" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M102" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N102" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B103" t="s">
         <v>8</v>
@@ -5176,69 +5236,71 @@
         <v>13</v>
       </c>
       <c r="F103" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G103" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H103" s="2">
-        <v>45959</v>
+        <v>45937</v>
       </c>
       <c r="I103" s="2">
-        <v>45971</v>
+        <v>45966</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
       <c r="L103" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M103" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N103" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B104" t="s">
         <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D104" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F104" t="s">
-        <v>42</v>
+        <v>274</v>
       </c>
       <c r="G104" t="s">
-        <v>100</v>
-      </c>
-      <c r="H104" s="2">
-        <v>45954</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H104" s="2"/>
       <c r="I104" s="2">
-        <v>45973</v>
-      </c>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
+        <v>45776</v>
+      </c>
+      <c r="J104" s="2">
+        <v>45798</v>
+      </c>
+      <c r="K104" s="2">
+        <v>45972</v>
+      </c>
       <c r="L104" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M104" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N104" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B105" t="s">
         <v>8</v>
@@ -5247,115 +5309,120 @@
         <v>16</v>
       </c>
       <c r="D105" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F105" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="G105" t="s">
-        <v>100</v>
-      </c>
-      <c r="H105" s="2">
-        <v>45954</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H105" s="2"/>
       <c r="I105" s="2">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
       <c r="L105" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M105" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N105" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B106" t="s">
         <v>8</v>
       </c>
       <c r="C106" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D106" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F106" t="s">
-        <v>28</v>
+        <v>270</v>
       </c>
       <c r="G106" t="s">
-        <v>93</v>
-      </c>
-      <c r="H106" s="2">
-        <v>45799</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H106" s="2"/>
       <c r="I106" s="2">
-        <v>45971</v>
-      </c>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
+        <v>45936</v>
+      </c>
+      <c r="J106" s="2">
+        <v>45972</v>
+      </c>
+      <c r="K106" s="2">
+        <v>46140</v>
+      </c>
       <c r="L106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N106" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B107" t="s">
         <v>8</v>
       </c>
       <c r="C107" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D107" t="s">
         <v>9</v>
+      </c>
+      <c r="E107" t="s">
+        <v>15</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
       </c>
       <c r="G107" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H107" s="2">
-        <v>45852</v>
+        <v>45873</v>
       </c>
       <c r="I107" s="2">
-        <v>45971</v>
+        <v>45901</v>
       </c>
       <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
+      <c r="K107" s="2">
+        <v>46129</v>
+      </c>
       <c r="L107" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M107" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N107" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B108" t="s">
         <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D108" t="s">
         <v>9</v>
@@ -5364,71 +5431,74 @@
         <v>13</v>
       </c>
       <c r="F108" t="s">
-        <v>307</v>
+        <v>50</v>
       </c>
       <c r="G108" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H108" s="2">
-        <v>45937</v>
+        <v>46030</v>
       </c>
       <c r="I108" s="2">
-        <v>45966</v>
+        <v>46069</v>
       </c>
       <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
-      <c r="L108" t="s">
-        <v>38</v>
-      </c>
-      <c r="M108" t="s">
-        <v>38</v>
+      <c r="K108" s="2">
+        <v>46125</v>
+      </c>
+      <c r="L108">
+        <v>80</v>
+      </c>
+      <c r="M108">
+        <v>1211.4269999999999</v>
       </c>
       <c r="N108" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B109" t="s">
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D109" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E109" t="s">
+        <v>13</v>
       </c>
       <c r="F109" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="G109" t="s">
-        <v>93</v>
-      </c>
-      <c r="H109" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H109" s="2">
+        <v>46106</v>
+      </c>
       <c r="I109" s="2">
-        <v>45776</v>
-      </c>
-      <c r="J109" s="2">
-        <v>45798</v>
-      </c>
-      <c r="K109" s="2">
-        <v>45972</v>
-      </c>
+        <v>46140</v>
+      </c>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
       <c r="L109" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M109" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N109" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B110" t="s">
         <v>8</v>
@@ -5437,156 +5507,151 @@
         <v>16</v>
       </c>
       <c r="D110" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E110" t="s">
+        <v>13</v>
       </c>
       <c r="F110" t="s">
-        <v>186</v>
+        <v>299</v>
       </c>
       <c r="G110" t="s">
-        <v>93</v>
-      </c>
-      <c r="H110" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H110" s="2">
+        <v>46076</v>
+      </c>
       <c r="I110" s="2">
-        <v>45975</v>
+        <v>46133</v>
       </c>
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
       <c r="L110" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M110" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N110" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B111" t="s">
         <v>8</v>
       </c>
       <c r="C111" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D111" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E111" t="s">
+        <v>13</v>
       </c>
       <c r="F111" t="s">
-        <v>33</v>
+        <v>300</v>
       </c>
       <c r="G111" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H111" s="2"/>
       <c r="I111" s="2">
-        <v>45936</v>
-      </c>
-      <c r="J111" s="2">
-        <v>45972</v>
-      </c>
-      <c r="K111" s="2">
-        <v>46140</v>
-      </c>
+        <v>46126</v>
+      </c>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
       <c r="L111" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M111" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N111" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B112" t="s">
         <v>8</v>
       </c>
       <c r="C112" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D112" t="s">
         <v>9</v>
       </c>
-      <c r="E112" t="s">
-        <v>15</v>
-      </c>
       <c r="F112" t="s">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="G112" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H112" s="2">
-        <v>45873</v>
+        <v>46080</v>
       </c>
       <c r="I112" s="2">
-        <v>45901</v>
+        <v>46126</v>
       </c>
       <c r="J112" s="2"/>
-      <c r="K112" s="2">
-        <v>46129</v>
-      </c>
+      <c r="K112" s="2"/>
       <c r="L112" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M112" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N112" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B113" t="s">
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D113" t="s">
         <v>9</v>
       </c>
-      <c r="E113" t="s">
-        <v>13</v>
-      </c>
       <c r="F113" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G113" t="s">
-        <v>100</v>
-      </c>
-      <c r="H113" s="2">
-        <v>46030</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H113" s="2"/>
       <c r="I113" s="2">
-        <v>46069</v>
+        <v>46125</v>
       </c>
       <c r="J113" s="2"/>
-      <c r="K113" s="2">
-        <v>46125</v>
-      </c>
-      <c r="L113">
-        <v>80</v>
-      </c>
-      <c r="M113">
-        <v>1211.4269999999999</v>
+      <c r="K113" s="2"/>
+      <c r="L113" t="s">
+        <v>37</v>
+      </c>
+      <c r="M113" t="s">
+        <v>37</v>
       </c>
       <c r="N113" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B114" t="s">
         <v>8</v>
@@ -5597,28 +5662,25 @@
       <c r="D114" t="s">
         <v>9</v>
       </c>
-      <c r="E114" t="s">
-        <v>13</v>
-      </c>
       <c r="F114" t="s">
-        <v>309</v>
+        <v>28</v>
       </c>
       <c r="G114" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H114" s="2">
-        <v>46106</v>
+        <v>45932</v>
       </c>
       <c r="I114" s="2">
-        <v>46140</v>
+        <v>46125</v>
       </c>
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
       <c r="L114" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M114" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N114" t="s">
         <v>12</v>
@@ -5626,7 +5688,7 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B115" t="s">
         <v>8</v>
@@ -5637,39 +5699,33 @@
       <c r="D115" t="s">
         <v>9</v>
       </c>
-      <c r="E115" t="s">
-        <v>13</v>
-      </c>
       <c r="F115" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="G115" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H115" s="2">
-        <v>46076</v>
+        <v>46091</v>
       </c>
       <c r="I115" s="2">
-        <v>46133</v>
+        <v>46121</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
       <c r="L115" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M115" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N115" t="s">
         <v>12</v>
-      </c>
-      <c r="O115">
-        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B116" t="s">
         <v>8</v>
@@ -5680,26 +5736,23 @@
       <c r="D116" t="s">
         <v>9</v>
       </c>
-      <c r="E116" t="s">
-        <v>13</v>
-      </c>
       <c r="F116" t="s">
-        <v>311</v>
+        <v>189</v>
       </c>
       <c r="G116" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H116" s="2"/>
       <c r="I116" s="2">
-        <v>46126</v>
+        <v>46121</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
       <c r="L116" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M116" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N116" t="s">
         <v>12</v>
@@ -5707,7 +5760,7 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B117" t="s">
         <v>8</v>
@@ -5719,24 +5772,24 @@
         <v>9</v>
       </c>
       <c r="F117" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G117" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H117" s="2">
-        <v>46080</v>
+        <v>46063</v>
       </c>
       <c r="I117" s="2">
-        <v>46126</v>
+        <v>46120</v>
       </c>
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
       <c r="L117" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M117" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N117" t="s">
         <v>12</v>
@@ -5744,7 +5797,7 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B118" t="s">
         <v>8</v>
@@ -5755,23 +5808,28 @@
       <c r="D118" t="s">
         <v>9</v>
       </c>
+      <c r="E118" t="s">
+        <v>13</v>
+      </c>
       <c r="F118" t="s">
-        <v>32</v>
+        <v>303</v>
       </c>
       <c r="G118" t="s">
-        <v>93</v>
-      </c>
-      <c r="H118" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H118" s="2">
+        <v>46043</v>
+      </c>
       <c r="I118" s="2">
-        <v>46125</v>
+        <v>46119</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
       <c r="L118" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M118" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N118" t="s">
         <v>12</v>
@@ -5779,7 +5837,7 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B119" t="s">
         <v>8</v>
@@ -5794,21 +5852,21 @@
         <v>28</v>
       </c>
       <c r="G119" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H119" s="2">
         <v>45932</v>
       </c>
       <c r="I119" s="2">
-        <v>46125</v>
+        <v>46118</v>
       </c>
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
       <c r="L119" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M119" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N119" t="s">
         <v>12</v>
@@ -5816,7 +5874,7 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B120" t="s">
         <v>8</v>
@@ -5828,24 +5886,22 @@
         <v>9</v>
       </c>
       <c r="F120" t="s">
-        <v>312</v>
+        <v>32</v>
       </c>
       <c r="G120" t="s">
-        <v>100</v>
-      </c>
-      <c r="H120" s="2">
-        <v>46091</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H120" s="2"/>
       <c r="I120" s="2">
-        <v>46121</v>
+        <v>46118</v>
       </c>
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
       <c r="L120" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M120" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N120" t="s">
         <v>12</v>
@@ -5853,7 +5909,7 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B121" t="s">
         <v>8</v>
@@ -5864,23 +5920,28 @@
       <c r="D121" t="s">
         <v>9</v>
       </c>
+      <c r="E121" t="s">
+        <v>15</v>
+      </c>
       <c r="F121" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="G121" t="s">
-        <v>100</v>
-      </c>
-      <c r="H121" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H121" s="2">
+        <v>46027</v>
+      </c>
       <c r="I121" s="2">
-        <v>46121</v>
+        <v>46118</v>
       </c>
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
       <c r="L121" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M121" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N121" t="s">
         <v>12</v>
@@ -5888,36 +5949,41 @@
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B122" t="s">
         <v>8</v>
       </c>
       <c r="C122" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D122" t="s">
         <v>9</v>
       </c>
+      <c r="E122" t="s">
+        <v>13</v>
+      </c>
       <c r="F122" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="G122" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H122" s="2">
-        <v>46063</v>
+        <v>45845</v>
       </c>
       <c r="I122" s="2">
-        <v>46120</v>
+        <v>46224</v>
       </c>
       <c r="J122" s="2"/>
-      <c r="K122" s="2"/>
-      <c r="L122" t="s">
-        <v>38</v>
-      </c>
-      <c r="M122" t="s">
-        <v>38</v>
+      <c r="K122" s="2">
+        <v>46157</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>1.1000000000000001</v>
       </c>
       <c r="N122" t="s">
         <v>12</v>
@@ -5925,39 +5991,36 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B123" t="s">
         <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D123" t="s">
         <v>9</v>
       </c>
-      <c r="E123" t="s">
-        <v>13</v>
-      </c>
       <c r="F123" t="s">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="G123" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H123" s="2">
-        <v>46043</v>
-      </c>
-      <c r="I123" s="2">
-        <v>46119</v>
-      </c>
+        <v>45954</v>
+      </c>
+      <c r="I123" s="2"/>
       <c r="J123" s="2"/>
-      <c r="K123" s="2"/>
+      <c r="K123" s="2">
+        <v>46157</v>
+      </c>
       <c r="L123" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M123" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N123" t="s">
         <v>12</v>
@@ -5965,44 +6028,52 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B124" t="s">
         <v>8</v>
       </c>
       <c r="C124" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D124" t="s">
         <v>9</v>
       </c>
+      <c r="E124" t="s">
+        <v>13</v>
+      </c>
       <c r="F124" t="s">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="G124" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H124" s="2">
-        <v>45932</v>
+        <v>46001</v>
       </c>
       <c r="I124" s="2">
-        <v>46118</v>
+        <v>46050</v>
       </c>
       <c r="J124" s="2"/>
-      <c r="K124" s="2"/>
-      <c r="L124" t="s">
-        <v>38</v>
-      </c>
-      <c r="M124" t="s">
-        <v>38</v>
+      <c r="K124" s="2">
+        <v>46150</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>0.74</v>
       </c>
       <c r="N124" t="s">
         <v>12</v>
+      </c>
+      <c r="O124">
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B125" t="s">
         <v>8</v>
@@ -6013,31 +6084,39 @@
       <c r="D125" t="s">
         <v>9</v>
       </c>
+      <c r="E125" t="s">
+        <v>13</v>
+      </c>
       <c r="F125" t="s">
-        <v>203</v>
+        <v>302</v>
       </c>
       <c r="G125" t="s">
-        <v>93</v>
-      </c>
-      <c r="H125" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H125" s="2">
+        <v>45760</v>
+      </c>
       <c r="I125" s="2">
-        <v>46118</v>
+        <v>46170</v>
       </c>
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
       <c r="L125" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M125" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N125" t="s">
         <v>12</v>
+      </c>
+      <c r="O125">
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B126" t="s">
         <v>8</v>
@@ -6049,120 +6128,116 @@
         <v>9</v>
       </c>
       <c r="E126" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F126" t="s">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="G126" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H126" s="2">
-        <v>46027</v>
+        <v>46049</v>
       </c>
       <c r="I126" s="2">
-        <v>46118</v>
+        <v>46170</v>
       </c>
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
       <c r="L126" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M126" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N126" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>204</v>
+      </c>
+      <c r="B127" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" t="s">
+        <v>16</v>
+      </c>
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" t="s">
         <v>205</v>
       </c>
-      <c r="B127" t="s">
-        <v>8</v>
-      </c>
-      <c r="C127" t="s">
-        <v>17</v>
-      </c>
-      <c r="D127" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" t="s">
-        <v>13</v>
-      </c>
-      <c r="F127" t="s">
-        <v>206</v>
-      </c>
       <c r="G127" t="s">
-        <v>100</v>
-      </c>
-      <c r="H127" s="2">
-        <v>45845</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H127" s="2"/>
       <c r="I127" s="2">
-        <v>46224</v>
+        <v>46163</v>
       </c>
       <c r="J127" s="2"/>
-      <c r="K127" s="2">
-        <v>46157</v>
-      </c>
-      <c r="L127">
-        <v>1</v>
-      </c>
-      <c r="M127">
-        <v>1.1000000000000001</v>
+      <c r="K127" s="2"/>
+      <c r="L127" t="s">
+        <v>37</v>
+      </c>
+      <c r="M127" t="s">
+        <v>37</v>
       </c>
       <c r="N127" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>206</v>
+      </c>
+      <c r="B128" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" t="s">
+        <v>16</v>
+      </c>
+      <c r="D128" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" t="s">
+        <v>290</v>
+      </c>
+      <c r="G128" t="s">
+        <v>89</v>
+      </c>
+      <c r="H128" s="2">
+        <v>46140</v>
+      </c>
+      <c r="I128" s="2">
+        <v>46163</v>
+      </c>
+      <c r="J128" s="2"/>
+      <c r="K128" s="2"/>
+      <c r="L128" t="s">
+        <v>37</v>
+      </c>
+      <c r="M128" t="s">
+        <v>37</v>
+      </c>
+      <c r="N128" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>207</v>
       </c>
-      <c r="B128" t="s">
-        <v>8</v>
-      </c>
-      <c r="C128" t="s">
-        <v>17</v>
-      </c>
-      <c r="D128" t="s">
-        <v>9</v>
-      </c>
-      <c r="F128" t="s">
-        <v>42</v>
-      </c>
-      <c r="G128" t="s">
-        <v>100</v>
-      </c>
-      <c r="H128" s="2">
-        <v>45954</v>
-      </c>
-      <c r="I128" s="2"/>
-      <c r="J128" s="2"/>
-      <c r="K128" s="2">
-        <v>46157</v>
-      </c>
-      <c r="L128" t="s">
-        <v>38</v>
-      </c>
-      <c r="M128" t="s">
-        <v>38</v>
-      </c>
-      <c r="N128" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>208</v>
-      </c>
       <c r="B129" t="s">
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D129" t="s">
         <v>9</v>
@@ -6171,37 +6246,32 @@
         <v>13</v>
       </c>
       <c r="F129" t="s">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="G129" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H129" s="2">
-        <v>46001</v>
+        <v>46133</v>
       </c>
       <c r="I129" s="2">
-        <v>46050</v>
+        <v>46162</v>
       </c>
       <c r="J129" s="2"/>
-      <c r="K129" s="2">
-        <v>46150</v>
-      </c>
-      <c r="L129">
-        <v>1</v>
-      </c>
-      <c r="M129">
-        <v>0.74</v>
+      <c r="K129" s="2"/>
+      <c r="L129" t="s">
+        <v>37</v>
+      </c>
+      <c r="M129" t="s">
+        <v>37</v>
       </c>
       <c r="N129" t="s">
-        <v>94</v>
-      </c>
-      <c r="O129">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B130" t="s">
         <v>8</v>
@@ -6212,39 +6282,31 @@
       <c r="D130" t="s">
         <v>9</v>
       </c>
-      <c r="E130" t="s">
-        <v>13</v>
-      </c>
       <c r="F130" t="s">
-        <v>313</v>
+        <v>209</v>
       </c>
       <c r="G130" t="s">
-        <v>100</v>
-      </c>
-      <c r="H130" s="2">
-        <v>45760</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H130" s="2"/>
       <c r="I130" s="2">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
       <c r="L130" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M130" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N130" t="s">
         <v>12</v>
-      </c>
-      <c r="O130">
-        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B131" t="s">
         <v>8</v>
@@ -6259,24 +6321,24 @@
         <v>13</v>
       </c>
       <c r="F131" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="G131" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H131" s="2">
-        <v>46049</v>
+        <v>46118</v>
       </c>
       <c r="I131" s="2">
-        <v>46170</v>
+        <v>46150</v>
       </c>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
       <c r="L131" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M131" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N131" t="s">
         <v>12</v>
@@ -6284,7 +6346,7 @@
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B132" t="s">
         <v>8</v>
@@ -6295,25 +6357,28 @@
       <c r="D132" t="s">
         <v>9</v>
       </c>
+      <c r="E132" t="s">
+        <v>13</v>
+      </c>
       <c r="F132" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="G132" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H132" s="2">
-        <v>46100</v>
+        <v>46079</v>
       </c>
       <c r="I132" s="2">
-        <v>46163</v>
+        <v>46148</v>
       </c>
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
       <c r="L132" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M132" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N132" t="s">
         <v>12</v>
@@ -6321,77 +6386,91 @@
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B133" t="s">
         <v>8</v>
       </c>
       <c r="C133" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D133" t="s">
         <v>9</v>
       </c>
+      <c r="E133" t="s">
+        <v>13</v>
+      </c>
       <c r="F133" t="s">
-        <v>215</v>
+        <v>306</v>
       </c>
       <c r="G133" t="s">
-        <v>93</v>
-      </c>
-      <c r="H133" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H133" s="2">
+        <v>46071</v>
+      </c>
       <c r="I133" s="2">
-        <v>46163</v>
-      </c>
-      <c r="J133" s="2"/>
-      <c r="K133" s="2"/>
-      <c r="L133" t="s">
-        <v>38</v>
-      </c>
-      <c r="M133" t="s">
-        <v>38</v>
+        <v>46072</v>
+      </c>
+      <c r="J133" s="2">
+        <v>46073</v>
+      </c>
+      <c r="K133" s="2">
+        <v>46076</v>
+      </c>
+      <c r="L133">
+        <v>6</v>
+      </c>
+      <c r="M133">
+        <v>8.44</v>
       </c>
       <c r="N133" t="s">
-        <v>12</v>
+        <v>213</v>
+      </c>
+      <c r="P133" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
+        <v>215</v>
+      </c>
+      <c r="B134" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" t="s">
         <v>216</v>
       </c>
-      <c r="B134" t="s">
-        <v>8</v>
-      </c>
-      <c r="C134" t="s">
-        <v>16</v>
-      </c>
-      <c r="D134" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" t="s">
-        <v>15</v>
-      </c>
-      <c r="F134" t="s">
-        <v>301</v>
-      </c>
       <c r="G134" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H134" s="2">
-        <v>46140</v>
+        <v>45994</v>
       </c>
       <c r="I134" s="2">
-        <v>46163</v>
+        <v>45994</v>
       </c>
       <c r="J134" s="2"/>
-      <c r="K134" s="2"/>
-      <c r="L134" t="s">
-        <v>38</v>
-      </c>
-      <c r="M134" t="s">
-        <v>38</v>
+      <c r="K134" s="2">
+        <v>46038</v>
+      </c>
+      <c r="L134">
+        <v>100</v>
+      </c>
+      <c r="M134">
+        <v>1176.6099999999999</v>
       </c>
       <c r="N134" t="s">
-        <v>12</v>
+        <v>213</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.3">
@@ -6402,7 +6481,7 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D135" t="s">
         <v>9</v>
@@ -6411,32 +6490,34 @@
         <v>13</v>
       </c>
       <c r="F135" t="s">
-        <v>293</v>
+        <v>218</v>
       </c>
       <c r="G135" t="s">
+        <v>95</v>
+      </c>
+      <c r="H135" s="2">
+        <v>46000</v>
+      </c>
+      <c r="I135" s="2">
+        <v>46002</v>
+      </c>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2">
+        <v>46036</v>
+      </c>
+      <c r="L135">
         <v>100</v>
       </c>
-      <c r="H135" s="2">
-        <v>46133</v>
-      </c>
-      <c r="I135" s="2">
-        <v>46162</v>
-      </c>
-      <c r="J135" s="2"/>
-      <c r="K135" s="2"/>
-      <c r="L135" t="s">
-        <v>38</v>
-      </c>
-      <c r="M135" t="s">
-        <v>38</v>
+      <c r="M135">
+        <v>942.49</v>
       </c>
       <c r="N135" t="s">
-        <v>12</v>
+        <v>213</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B136" t="s">
         <v>8</v>
@@ -6448,30 +6529,30 @@
         <v>9</v>
       </c>
       <c r="F136" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G136" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H136" s="2"/>
       <c r="I136" s="2">
-        <v>46161</v>
+        <v>46259</v>
       </c>
       <c r="J136" s="2"/>
       <c r="K136" s="2"/>
       <c r="L136" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M136" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N136" t="s">
-        <v>12</v>
+        <v>213</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B137" t="s">
         <v>8</v>
@@ -6482,42 +6563,37 @@
       <c r="D137" t="s">
         <v>9</v>
       </c>
-      <c r="E137" t="s">
-        <v>13</v>
-      </c>
       <c r="F137" t="s">
-        <v>282</v>
+        <v>214</v>
       </c>
       <c r="G137" t="s">
-        <v>93</v>
-      </c>
-      <c r="H137" s="2">
-        <v>46118</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="H137" s="2"/>
       <c r="I137" s="2">
-        <v>46150</v>
+        <v>46058</v>
       </c>
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
       <c r="L137" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M137" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N137" t="s">
-        <v>12</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B138" t="s">
         <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D138" t="s">
         <v>9</v>
@@ -6526,32 +6602,36 @@
         <v>13</v>
       </c>
       <c r="F138" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="G138" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H138" s="2">
-        <v>46079</v>
+        <v>46191</v>
       </c>
       <c r="I138" s="2">
-        <v>46148</v>
-      </c>
-      <c r="J138" s="2"/>
-      <c r="K138" s="2"/>
-      <c r="L138" t="s">
-        <v>38</v>
-      </c>
-      <c r="M138" t="s">
-        <v>38</v>
+        <v>46217</v>
+      </c>
+      <c r="J138" s="2">
+        <v>37454</v>
+      </c>
+      <c r="K138" s="2">
+        <v>46227</v>
+      </c>
+      <c r="L138">
+        <v>24</v>
+      </c>
+      <c r="M138">
+        <v>97.3</v>
       </c>
       <c r="N138" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B139" t="s">
         <v>8</v>
@@ -6563,42 +6643,37 @@
         <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>13</v>
+        <v>314</v>
       </c>
       <c r="F139" t="s">
-        <v>317</v>
+        <v>225</v>
       </c>
       <c r="G139" t="s">
-        <v>93</v>
-      </c>
-      <c r="H139" s="2">
-        <v>46071</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H139" s="2"/>
       <c r="I139" s="2">
-        <v>46072</v>
+        <v>46119</v>
       </c>
       <c r="J139" s="2">
-        <v>46073</v>
+        <v>46122</v>
       </c>
       <c r="K139" s="2">
-        <v>46076</v>
+        <v>46147</v>
       </c>
       <c r="L139">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="M139">
-        <v>8.44</v>
+        <v>3.61</v>
       </c>
       <c r="N139" t="s">
         <v>223</v>
       </c>
-      <c r="P139" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B140" t="s">
         <v>8</v>
@@ -6613,32 +6688,30 @@
         <v>13</v>
       </c>
       <c r="F140" t="s">
-        <v>226</v>
+        <v>315</v>
       </c>
       <c r="G140" t="s">
-        <v>100</v>
-      </c>
-      <c r="H140" s="2">
-        <v>45994</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H140" s="2"/>
       <c r="I140" s="2">
-        <v>45994</v>
+        <v>46106</v>
       </c>
       <c r="J140" s="2"/>
       <c r="K140" s="2">
-        <v>46038</v>
+        <v>46132</v>
       </c>
       <c r="L140">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="M140">
-        <v>1176.6099999999999</v>
+        <v>101.23</v>
       </c>
       <c r="N140" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>227</v>
       </c>
@@ -6646,7 +6719,7 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
       <c r="D141" t="s">
         <v>9</v>
@@ -6655,102 +6728,102 @@
         <v>13</v>
       </c>
       <c r="F141" t="s">
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="G141" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H141" s="2">
-        <v>46000</v>
+        <v>46209</v>
       </c>
       <c r="I141" s="2">
-        <v>46002</v>
+        <v>46260</v>
       </c>
       <c r="J141" s="2"/>
       <c r="K141" s="2">
-        <v>46036</v>
+        <v>46279</v>
       </c>
       <c r="L141">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="M141">
-        <v>942.49</v>
+        <v>2.161</v>
       </c>
       <c r="N141" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>228</v>
+      </c>
+      <c r="B142" t="s">
+        <v>8</v>
+      </c>
+      <c r="C142" t="s">
+        <v>16</v>
+      </c>
+      <c r="D142" t="s">
+        <v>9</v>
+      </c>
+      <c r="F142" t="s">
         <v>229</v>
       </c>
-      <c r="B142" t="s">
-        <v>8</v>
-      </c>
-      <c r="C142" t="s">
-        <v>16</v>
-      </c>
-      <c r="D142" t="s">
-        <v>9</v>
-      </c>
-      <c r="F142" t="s">
-        <v>230</v>
-      </c>
       <c r="G142" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="2">
-        <v>46259</v>
+        <v>46247</v>
       </c>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
       <c r="L142" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M142" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N142" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>230</v>
+      </c>
+      <c r="B143" t="s">
+        <v>8</v>
+      </c>
+      <c r="C143" t="s">
+        <v>16</v>
+      </c>
+      <c r="D143" t="s">
+        <v>4</v>
+      </c>
+      <c r="F143" t="s">
         <v>231</v>
       </c>
-      <c r="B143" t="s">
-        <v>8</v>
-      </c>
-      <c r="C143" t="s">
-        <v>16</v>
-      </c>
-      <c r="D143" t="s">
-        <v>9</v>
-      </c>
-      <c r="F143" t="s">
-        <v>224</v>
-      </c>
       <c r="G143" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H143" s="2"/>
       <c r="I143" s="2">
-        <v>46058</v>
+        <v>46237</v>
       </c>
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
       <c r="L143" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M143" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N143" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>232</v>
       </c>
@@ -6764,37 +6837,38 @@
         <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F144" t="s">
-        <v>319</v>
+        <v>30</v>
       </c>
       <c r="G144" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H144" s="2">
-        <v>46191</v>
+        <v>46009</v>
       </c>
       <c r="I144" s="2">
-        <v>46217</v>
-      </c>
-      <c r="J144" s="2">
-        <v>37454</v>
-      </c>
+        <v>46083</v>
+      </c>
+      <c r="J144" s="2"/>
       <c r="K144" s="2">
-        <v>46227</v>
+        <v>46248</v>
       </c>
       <c r="L144">
-        <v>24</v>
+        <v>339</v>
       </c>
       <c r="M144">
-        <v>97.3</v>
+        <v>67.849999999999994</v>
       </c>
       <c r="N144" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="O144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>234</v>
       </c>
@@ -6808,37 +6882,37 @@
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>325</v>
+        <v>13</v>
       </c>
       <c r="F145" t="s">
+        <v>316</v>
+      </c>
+      <c r="G145" t="s">
+        <v>89</v>
+      </c>
+      <c r="H145" s="2">
+        <v>46217</v>
+      </c>
+      <c r="I145" s="2">
+        <v>46247</v>
+      </c>
+      <c r="J145" s="2"/>
+      <c r="K145" s="2">
+        <v>46253</v>
+      </c>
+      <c r="L145">
+        <v>10</v>
+      </c>
+      <c r="M145">
+        <v>10.949</v>
+      </c>
+      <c r="N145" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
         <v>235</v>
-      </c>
-      <c r="G145" t="s">
-        <v>93</v>
-      </c>
-      <c r="H145" s="2"/>
-      <c r="I145" s="2">
-        <v>46119</v>
-      </c>
-      <c r="J145" s="2">
-        <v>46122</v>
-      </c>
-      <c r="K145" s="2">
-        <v>46147</v>
-      </c>
-      <c r="L145">
-        <v>122</v>
-      </c>
-      <c r="M145">
-        <v>3.61</v>
-      </c>
-      <c r="N145" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>236</v>
       </c>
       <c r="B146" t="s">
         <v>8</v>
@@ -6853,27 +6927,29 @@
         <v>13</v>
       </c>
       <c r="F146" t="s">
-        <v>326</v>
+        <v>236</v>
       </c>
       <c r="G146" t="s">
-        <v>93</v>
-      </c>
-      <c r="H146" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H146" s="2">
+        <v>45826</v>
+      </c>
       <c r="I146" s="2">
-        <v>46106</v>
+        <v>46228</v>
       </c>
       <c r="J146" s="2"/>
       <c r="K146" s="2">
-        <v>46132</v>
+        <v>45910</v>
       </c>
       <c r="L146">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M146">
-        <v>101.23</v>
+        <v>1210.6400000000001</v>
       </c>
       <c r="N146" t="s">
-        <v>233</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
@@ -6884,7 +6960,7 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D147" t="s">
         <v>9</v>
@@ -6893,24 +6969,26 @@
         <v>13</v>
       </c>
       <c r="F147" t="s">
-        <v>320</v>
+        <v>238</v>
       </c>
       <c r="G147" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H147" s="2">
-        <v>46209</v>
+        <v>45866</v>
       </c>
       <c r="I147" s="2">
-        <v>46260</v>
+        <v>45884</v>
       </c>
       <c r="J147" s="2"/>
-      <c r="K147" s="2"/>
-      <c r="L147" t="s">
-        <v>38</v>
-      </c>
-      <c r="M147" t="s">
-        <v>38</v>
+      <c r="K147" s="2">
+        <v>45905</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="M147">
+        <v>6.7350000000000003</v>
       </c>
       <c r="N147" t="s">
         <v>12</v>
@@ -6918,34 +6996,41 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="B148" t="s">
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D148" t="s">
         <v>9</v>
+      </c>
+      <c r="E148" t="s">
+        <v>13</v>
       </c>
       <c r="F148" t="s">
         <v>239</v>
       </c>
       <c r="G148" t="s">
-        <v>37</v>
-      </c>
-      <c r="H148" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H148" s="2">
+        <v>45856</v>
+      </c>
       <c r="I148" s="2">
-        <v>46247</v>
+        <v>45880</v>
       </c>
       <c r="J148" s="2"/>
-      <c r="K148" s="2"/>
-      <c r="L148" t="s">
-        <v>38</v>
-      </c>
-      <c r="M148" t="s">
-        <v>38</v>
+      <c r="K148" s="2">
+        <v>45905</v>
+      </c>
+      <c r="L148">
+        <v>1</v>
+      </c>
+      <c r="M148">
+        <v>16.376999999999999</v>
       </c>
       <c r="N148" t="s">
         <v>12</v>
@@ -6959,28 +7044,35 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E149" t="s">
+        <v>13</v>
       </c>
       <c r="F149" t="s">
         <v>241</v>
       </c>
       <c r="G149" t="s">
-        <v>93</v>
-      </c>
-      <c r="H149" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H149" s="2">
+        <v>45758</v>
+      </c>
       <c r="I149" s="2">
-        <v>46237</v>
+        <v>45817</v>
       </c>
       <c r="J149" s="2"/>
-      <c r="K149" s="2"/>
-      <c r="L149" t="s">
-        <v>38</v>
-      </c>
-      <c r="M149" t="s">
-        <v>38</v>
+      <c r="K149" s="2">
+        <v>45905</v>
+      </c>
+      <c r="L149">
+        <v>15</v>
+      </c>
+      <c r="M149">
+        <v>1.83</v>
       </c>
       <c r="N149" t="s">
         <v>12</v>
@@ -6999,29 +7091,36 @@
       <c r="D150" t="s">
         <v>9</v>
       </c>
+      <c r="E150" t="s">
+        <v>13</v>
+      </c>
       <c r="F150" t="s">
         <v>243</v>
       </c>
       <c r="G150" t="s">
-        <v>93</v>
-      </c>
-      <c r="H150" s="2"/>
-      <c r="I150" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H150" s="2">
+        <v>45854</v>
+      </c>
+      <c r="I150" s="2">
+        <v>45868</v>
+      </c>
       <c r="J150" s="2"/>
       <c r="K150" s="2">
-        <v>46248</v>
-      </c>
-      <c r="L150" t="s">
-        <v>38</v>
-      </c>
-      <c r="M150" t="s">
-        <v>38</v>
+        <v>45902</v>
+      </c>
+      <c r="L150">
+        <v>2</v>
+      </c>
+      <c r="M150">
+        <v>54.24</v>
       </c>
       <c r="N150" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>244</v>
       </c>
@@ -7038,208 +7137,180 @@
         <v>13</v>
       </c>
       <c r="F151" t="s">
-        <v>327</v>
+        <v>245</v>
       </c>
       <c r="G151" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H151" s="2">
-        <v>46217</v>
+        <v>45804</v>
       </c>
       <c r="I151" s="2">
-        <v>46247</v>
+        <v>45817</v>
       </c>
       <c r="J151" s="2"/>
       <c r="K151" s="2">
-        <v>46253</v>
+        <v>45908</v>
       </c>
       <c r="L151">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M151">
-        <v>10.949</v>
+        <v>13.68</v>
       </c>
       <c r="N151" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B152" t="s">
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D152" t="s">
         <v>9</v>
       </c>
-      <c r="E152" t="s">
-        <v>13</v>
-      </c>
       <c r="F152" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G152" t="s">
-        <v>100</v>
-      </c>
-      <c r="H152" s="2">
-        <v>45826</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="H152" s="2"/>
       <c r="I152" s="2">
-        <v>46228</v>
+        <v>45912</v>
       </c>
       <c r="J152" s="2"/>
-      <c r="K152" s="2">
-        <v>45910</v>
-      </c>
-      <c r="L152">
-        <v>68</v>
-      </c>
-      <c r="M152">
-        <v>1210.6400000000001</v>
+      <c r="K152" s="2"/>
+      <c r="L152" t="s">
+        <v>37</v>
+      </c>
+      <c r="M152" t="s">
+        <v>37</v>
       </c>
       <c r="N152" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B153" t="s">
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D153" t="s">
         <v>9</v>
       </c>
-      <c r="E153" t="s">
-        <v>13</v>
-      </c>
       <c r="F153" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G153" t="s">
-        <v>100</v>
-      </c>
-      <c r="H153" s="2">
-        <v>45866</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="H153" s="2"/>
       <c r="I153" s="2">
-        <v>45884</v>
+        <v>45912</v>
       </c>
       <c r="J153" s="2"/>
-      <c r="K153" s="2">
-        <v>45905</v>
-      </c>
-      <c r="L153">
-        <v>1</v>
-      </c>
-      <c r="M153">
-        <v>6.7350000000000003</v>
+      <c r="K153" s="2"/>
+      <c r="L153" t="s">
+        <v>37</v>
+      </c>
+      <c r="M153" t="s">
+        <v>37</v>
       </c>
       <c r="N153" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>328</v>
+        <v>250</v>
       </c>
       <c r="B154" t="s">
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D154" t="s">
         <v>9</v>
-      </c>
-      <c r="E154" t="s">
-        <v>13</v>
       </c>
       <c r="F154" t="s">
         <v>249</v>
       </c>
       <c r="G154" t="s">
-        <v>100</v>
-      </c>
-      <c r="H154" s="2">
-        <v>45856</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="H154" s="2"/>
       <c r="I154" s="2">
-        <v>45880</v>
+        <v>45912</v>
       </c>
       <c r="J154" s="2"/>
-      <c r="K154" s="2">
-        <v>45905</v>
-      </c>
-      <c r="L154">
-        <v>1</v>
-      </c>
-      <c r="M154">
-        <v>16.376999999999999</v>
+      <c r="K154" s="2"/>
+      <c r="L154" t="s">
+        <v>37</v>
+      </c>
+      <c r="M154" t="s">
+        <v>37</v>
       </c>
       <c r="N154" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B155" t="s">
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D155" t="s">
         <v>9</v>
       </c>
-      <c r="E155" t="s">
-        <v>13</v>
-      </c>
       <c r="F155" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G155" t="s">
-        <v>93</v>
-      </c>
-      <c r="H155" s="2">
-        <v>45758</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="H155" s="2"/>
       <c r="I155" s="2">
-        <v>45817</v>
+        <v>45912</v>
       </c>
       <c r="J155" s="2"/>
-      <c r="K155" s="2">
-        <v>45905</v>
-      </c>
-      <c r="L155">
-        <v>15</v>
-      </c>
-      <c r="M155">
-        <v>1.83</v>
+      <c r="K155" s="2"/>
+      <c r="L155" t="s">
+        <v>37</v>
+      </c>
+      <c r="M155" t="s">
+        <v>37</v>
       </c>
       <c r="N155" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B156" t="s">
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D156" t="s">
         <v>9</v>
@@ -7248,32 +7319,30 @@
         <v>13</v>
       </c>
       <c r="F156" t="s">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="G156" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H156" s="2">
-        <v>45854</v>
+        <v>45860</v>
       </c>
       <c r="I156" s="2">
-        <v>45868</v>
+        <v>45908</v>
       </c>
       <c r="J156" s="2"/>
-      <c r="K156" s="2">
-        <v>45902</v>
-      </c>
+      <c r="K156" s="2"/>
       <c r="L156">
-        <v>2</v>
-      </c>
-      <c r="M156">
-        <v>54.24</v>
+        <v>82</v>
+      </c>
+      <c r="M156" t="s">
+        <v>37</v>
       </c>
       <c r="N156" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>254</v>
       </c>
@@ -7281,7 +7350,7 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D157" t="s">
         <v>9</v>
@@ -7290,34 +7359,32 @@
         <v>13</v>
       </c>
       <c r="F157" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="G157" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H157" s="2">
-        <v>45804</v>
+        <v>45866</v>
       </c>
       <c r="I157" s="2">
-        <v>45817</v>
+        <v>45908</v>
       </c>
       <c r="J157" s="2"/>
-      <c r="K157" s="2">
-        <v>45908</v>
-      </c>
+      <c r="K157" s="2"/>
       <c r="L157">
-        <v>1</v>
-      </c>
-      <c r="M157">
-        <v>13.68</v>
+        <v>93</v>
+      </c>
+      <c r="M157" t="s">
+        <v>37</v>
       </c>
       <c r="N157" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B158" t="s">
         <v>8</v>
@@ -7328,23 +7395,28 @@
       <c r="D158" t="s">
         <v>9</v>
       </c>
+      <c r="E158" t="s">
+        <v>13</v>
+      </c>
       <c r="F158" t="s">
-        <v>257</v>
+        <v>312</v>
       </c>
       <c r="G158" t="s">
-        <v>100</v>
-      </c>
-      <c r="H158" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H158" s="2">
+        <v>45866</v>
+      </c>
       <c r="I158" s="2">
-        <v>45912</v>
+        <v>45908</v>
       </c>
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
-      <c r="L158" t="s">
-        <v>38</v>
+      <c r="L158">
+        <v>77</v>
       </c>
       <c r="M158" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N158" t="s">
         <v>12</v>
@@ -7352,7 +7424,7 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B159" t="s">
         <v>8</v>
@@ -7363,23 +7435,28 @@
       <c r="D159" t="s">
         <v>9</v>
       </c>
+      <c r="E159" t="s">
+        <v>13</v>
+      </c>
       <c r="F159" t="s">
-        <v>259</v>
+        <v>313</v>
       </c>
       <c r="G159" t="s">
-        <v>100</v>
-      </c>
-      <c r="H159" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="H159" s="2">
+        <v>45860</v>
+      </c>
       <c r="I159" s="2">
-        <v>45912</v>
+        <v>45908</v>
       </c>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
-      <c r="L159" t="s">
-        <v>38</v>
+      <c r="L159">
+        <v>73</v>
       </c>
       <c r="M159" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N159" t="s">
         <v>12</v>
@@ -7387,7 +7464,7 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B160" t="s">
         <v>8</v>
@@ -7399,22 +7476,24 @@
         <v>9</v>
       </c>
       <c r="F160" t="s">
-        <v>259</v>
+        <v>28</v>
       </c>
       <c r="G160" t="s">
-        <v>100</v>
-      </c>
-      <c r="H160" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H160" s="2">
+        <v>45873</v>
+      </c>
       <c r="I160" s="2">
-        <v>45912</v>
+        <v>45901</v>
       </c>
       <c r="J160" s="2"/>
       <c r="K160" s="2"/>
       <c r="L160" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M160" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N160" t="s">
         <v>12</v>
@@ -7422,7 +7501,7 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B161" t="s">
         <v>8</v>
@@ -7434,30 +7513,32 @@
         <v>9</v>
       </c>
       <c r="F161" t="s">
-        <v>262</v>
+        <v>28</v>
       </c>
       <c r="G161" t="s">
-        <v>100</v>
-      </c>
-      <c r="H161" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H161" s="2">
+        <v>45873</v>
+      </c>
       <c r="I161" s="2">
-        <v>45912</v>
+        <v>45901</v>
       </c>
       <c r="J161" s="2"/>
       <c r="K161" s="2"/>
       <c r="L161" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M161" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N161" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B162" t="s">
         <v>8</v>
@@ -7468,36 +7549,33 @@
       <c r="D162" t="s">
         <v>9</v>
       </c>
-      <c r="E162" t="s">
-        <v>13</v>
-      </c>
       <c r="F162" t="s">
-        <v>321</v>
+        <v>28</v>
       </c>
       <c r="G162" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H162" s="2">
-        <v>45860</v>
+        <v>45873</v>
       </c>
       <c r="I162" s="2">
-        <v>45908</v>
+        <v>45901</v>
       </c>
       <c r="J162" s="2"/>
       <c r="K162" s="2"/>
-      <c r="L162">
-        <v>82</v>
+      <c r="L162" t="s">
+        <v>37</v>
       </c>
       <c r="M162" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N162" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B163" t="s">
         <v>8</v>
@@ -7508,36 +7586,33 @@
       <c r="D163" t="s">
         <v>9</v>
       </c>
-      <c r="E163" t="s">
-        <v>13</v>
-      </c>
       <c r="F163" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="G163" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H163" s="2">
-        <v>45866</v>
+        <v>45894</v>
       </c>
       <c r="I163" s="2">
-        <v>45908</v>
+        <v>45901</v>
       </c>
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
-      <c r="L163">
-        <v>93</v>
+      <c r="L163" t="s">
+        <v>37</v>
       </c>
       <c r="M163" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N163" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B164" t="s">
         <v>8</v>
@@ -7548,36 +7623,33 @@
       <c r="D164" t="s">
         <v>9</v>
       </c>
-      <c r="E164" t="s">
-        <v>13</v>
-      </c>
       <c r="F164" t="s">
-        <v>323</v>
+        <v>262</v>
       </c>
       <c r="G164" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H164" s="2">
-        <v>45866</v>
+        <v>45351</v>
       </c>
       <c r="I164" s="2">
-        <v>45908</v>
+        <v>45901</v>
       </c>
       <c r="J164" s="2"/>
       <c r="K164" s="2"/>
-      <c r="L164">
-        <v>77</v>
+      <c r="L164" t="s">
+        <v>37</v>
       </c>
       <c r="M164" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N164" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B165" t="s">
         <v>8</v>
@@ -7588,36 +7660,33 @@
       <c r="D165" t="s">
         <v>9</v>
       </c>
-      <c r="E165" t="s">
-        <v>13</v>
-      </c>
       <c r="F165" t="s">
-        <v>324</v>
+        <v>264</v>
       </c>
       <c r="G165" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H165" s="2">
-        <v>45860</v>
+        <v>45849</v>
       </c>
       <c r="I165" s="2">
-        <v>45908</v>
+        <v>45901</v>
       </c>
       <c r="J165" s="2"/>
       <c r="K165" s="2"/>
-      <c r="L165">
-        <v>73</v>
+      <c r="L165" t="s">
+        <v>37</v>
       </c>
       <c r="M165" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N165" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B166" t="s">
         <v>8</v>
@@ -7626,266 +7695,1381 @@
         <v>16</v>
       </c>
       <c r="D166" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F166" t="s">
-        <v>28</v>
+        <v>266</v>
       </c>
       <c r="G166" t="s">
-        <v>93</v>
-      </c>
-      <c r="H166" s="2">
-        <v>45873</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H166" s="2"/>
       <c r="I166" s="2">
-        <v>45901</v>
+        <v>45909</v>
       </c>
       <c r="J166" s="2"/>
       <c r="K166" s="2"/>
       <c r="L166" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M166" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N166" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>268</v>
-      </c>
       <c r="B167" t="s">
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D167" t="s">
         <v>9</v>
       </c>
+      <c r="E167" t="s">
+        <v>15</v>
+      </c>
       <c r="F167" t="s">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="G167" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H167" s="2">
-        <v>45873</v>
+        <v>45146</v>
       </c>
       <c r="I167" s="2">
-        <v>45901</v>
-      </c>
-      <c r="J167" s="2"/>
-      <c r="K167" s="2"/>
-      <c r="L167" t="s">
-        <v>38</v>
-      </c>
-      <c r="M167" t="s">
-        <v>38</v>
-      </c>
-      <c r="N167" t="s">
-        <v>12</v>
+        <v>45160</v>
+      </c>
+      <c r="J167" s="2">
+        <v>45167</v>
+      </c>
+      <c r="K167" s="2">
+        <v>45251</v>
+      </c>
+      <c r="L167" s="3">
+        <v>979</v>
+      </c>
+      <c r="M167" s="1">
+        <v>335.5</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>269</v>
-      </c>
       <c r="B168" t="s">
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D168" t="s">
         <v>9</v>
       </c>
+      <c r="E168" t="s">
+        <v>15</v>
+      </c>
       <c r="F168" t="s">
-        <v>28</v>
-      </c>
-      <c r="G168" t="s">
-        <v>93</v>
+        <v>203</v>
       </c>
       <c r="H168" s="2">
-        <v>45873</v>
+        <v>46100</v>
       </c>
       <c r="I168" s="2">
-        <v>45901</v>
+        <v>46163</v>
       </c>
       <c r="J168" s="2"/>
-      <c r="K168" s="2"/>
-      <c r="L168" t="s">
-        <v>38</v>
-      </c>
-      <c r="M168" t="s">
-        <v>38</v>
-      </c>
-      <c r="N168" t="s">
-        <v>12</v>
+      <c r="K168" s="2">
+        <v>46272</v>
+      </c>
+      <c r="L168" s="1">
+        <f>469+404</f>
+        <v>873</v>
+      </c>
+      <c r="M168" s="1">
+        <v>22.440999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>270</v>
-      </c>
       <c r="B169" t="s">
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D169" t="s">
         <v>9</v>
       </c>
+      <c r="E169" t="s">
+        <v>15</v>
+      </c>
       <c r="F169" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="G169" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H169" s="2">
-        <v>45894</v>
+        <v>46027</v>
       </c>
       <c r="I169" s="2">
-        <v>45901</v>
+        <v>46118</v>
       </c>
       <c r="J169" s="2"/>
-      <c r="K169" s="2"/>
-      <c r="L169" t="s">
-        <v>38</v>
-      </c>
-      <c r="M169" t="s">
-        <v>38</v>
-      </c>
-      <c r="N169" t="s">
-        <v>12</v>
+      <c r="K169" s="2">
+        <v>46272</v>
+      </c>
+      <c r="L169" s="3">
+        <v>94</v>
+      </c>
+      <c r="M169" s="1">
+        <v>287.91000000000003</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>271</v>
-      </c>
       <c r="B170" t="s">
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D170" t="s">
         <v>9</v>
       </c>
+      <c r="E170" t="s">
+        <v>15</v>
+      </c>
       <c r="F170" t="s">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="G170" t="s">
-        <v>93</v>
-      </c>
-      <c r="H170" s="2">
-        <v>45351</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H170" s="2"/>
       <c r="I170" s="2">
-        <v>45901</v>
-      </c>
-      <c r="J170" s="2"/>
-      <c r="K170" s="2"/>
-      <c r="L170" t="s">
-        <v>38</v>
-      </c>
-      <c r="M170" t="s">
-        <v>38</v>
+        <v>45392</v>
+      </c>
+      <c r="J170" s="2">
+        <v>45402</v>
+      </c>
+      <c r="K170" s="2">
+        <v>45609</v>
+      </c>
+      <c r="L170" s="1">
+        <v>11</v>
+      </c>
+      <c r="M170" s="1">
+        <v>24.26</v>
       </c>
       <c r="N170" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>273</v>
-      </c>
       <c r="B171" t="s">
         <v>8</v>
       </c>
       <c r="C171" t="s">
-        <v>16</v>
+        <v>319</v>
       </c>
       <c r="D171" t="s">
         <v>9</v>
       </c>
+      <c r="E171" t="s">
+        <v>13</v>
+      </c>
       <c r="F171" t="s">
-        <v>274</v>
+        <v>209</v>
       </c>
       <c r="G171" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H171" s="2">
-        <v>45849</v>
+        <v>45166</v>
       </c>
       <c r="I171" s="2">
-        <v>45901</v>
+        <v>45253</v>
       </c>
       <c r="J171" s="2"/>
-      <c r="K171" s="2"/>
-      <c r="L171" t="s">
-        <v>38</v>
-      </c>
-      <c r="M171" t="s">
-        <v>38</v>
+      <c r="K171" s="2">
+        <v>45271</v>
+      </c>
+      <c r="L171" s="1">
+        <v>42</v>
+      </c>
+      <c r="M171" s="1">
+        <v>443.39400000000001</v>
       </c>
       <c r="N171" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>275</v>
-      </c>
       <c r="B172" t="s">
         <v>8</v>
       </c>
       <c r="C172" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D172" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E172" t="s">
+        <v>15</v>
       </c>
       <c r="F172" t="s">
-        <v>276</v>
+        <v>43</v>
       </c>
       <c r="G172" t="s">
-        <v>93</v>
-      </c>
-      <c r="H172" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="H172" s="2">
+        <v>46149</v>
+      </c>
       <c r="I172" s="2">
-        <v>45909</v>
+        <v>46269</v>
       </c>
       <c r="J172" s="2"/>
       <c r="K172" s="2"/>
-      <c r="L172" t="s">
-        <v>38</v>
-      </c>
-      <c r="M172" t="s">
-        <v>38</v>
-      </c>
-      <c r="N172" t="s">
-        <v>12</v>
-      </c>
+      <c r="L172" s="1"/>
+      <c r="M172" s="1"/>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B173" t="s">
+        <v>8</v>
+      </c>
+      <c r="C173" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" t="s">
+        <v>15</v>
+      </c>
+      <c r="F173" t="s">
+        <v>318</v>
+      </c>
+      <c r="G173" t="s">
+        <v>89</v>
+      </c>
+      <c r="H173" s="2"/>
+      <c r="I173" s="2">
+        <v>45392</v>
+      </c>
+      <c r="J173" s="2">
+        <v>45400</v>
+      </c>
+      <c r="K173" s="2">
+        <v>45609</v>
+      </c>
+      <c r="L173" s="1">
+        <v>117</v>
+      </c>
+      <c r="M173" s="1">
+        <v>10.36</v>
+      </c>
+      <c r="N173" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B174" t="s">
+        <v>8</v>
+      </c>
+      <c r="C174" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" t="s">
+        <v>15</v>
+      </c>
+      <c r="F174" t="s">
+        <v>318</v>
+      </c>
+      <c r="G174" t="s">
+        <v>89</v>
+      </c>
+      <c r="H174" s="2"/>
+      <c r="I174" s="2">
+        <v>45392</v>
+      </c>
+      <c r="J174" s="2">
+        <v>45392</v>
+      </c>
+      <c r="K174" s="2">
+        <v>45609</v>
+      </c>
+      <c r="L174" s="1"/>
+      <c r="M174" s="1"/>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B175" t="s">
+        <v>8</v>
+      </c>
+      <c r="C175" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" t="s">
+        <v>15</v>
+      </c>
+      <c r="F175" t="s">
+        <v>28</v>
+      </c>
+      <c r="G175" t="s">
+        <v>89</v>
+      </c>
+      <c r="H175" s="2">
+        <v>45643</v>
+      </c>
+      <c r="I175" s="2">
+        <v>45800</v>
+      </c>
+      <c r="J175" s="2"/>
+      <c r="K175" s="2">
+        <v>45994</v>
+      </c>
+      <c r="L175" s="1">
+        <v>152</v>
+      </c>
+      <c r="M175" s="1">
+        <v>100.06</v>
+      </c>
+      <c r="N175" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B176" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" t="s">
+        <v>15</v>
+      </c>
+      <c r="F176" t="s">
+        <v>28</v>
+      </c>
+      <c r="G176" t="s">
+        <v>89</v>
+      </c>
+      <c r="H176" s="2">
+        <v>45750</v>
+      </c>
+      <c r="I176" s="2">
+        <v>45868</v>
+      </c>
+      <c r="J176" s="2"/>
+      <c r="K176" s="2">
+        <v>46129</v>
+      </c>
+      <c r="L176" s="1">
+        <v>25</v>
+      </c>
+      <c r="M176" s="1">
+        <v>3.54</v>
+      </c>
+      <c r="N176" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B177" t="s">
+        <v>8</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" t="s">
+        <v>15</v>
+      </c>
+      <c r="F177" t="s">
+        <v>28</v>
+      </c>
+      <c r="G177" t="s">
+        <v>89</v>
+      </c>
+      <c r="H177" s="2">
+        <v>45812</v>
+      </c>
+      <c r="I177" s="2">
+        <v>45868</v>
+      </c>
+      <c r="J177" s="2"/>
+      <c r="K177" s="2">
+        <v>46129</v>
+      </c>
+      <c r="L177" s="1">
+        <v>1</v>
+      </c>
+      <c r="M177" s="1">
+        <v>1.99</v>
+      </c>
+      <c r="N177" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="178" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="L178" s="1"/>
+      <c r="M178" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O172" xr:uid="{7620F5B7-47DE-4BC5-A97E-98454B0A0CF4}">
-    <filterColumn colId="11">
-      <filters>
-        <filter val="No aplica"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="13">
-      <filters>
-        <filter val="Dirección General (Valledupar)"/>
-        <filter val="Valledupar"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:P177" xr:uid="{7620F5B7-47DE-4BC5-A97E-98454B0A0CF4}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3266ACC9-7D8C-4C1E-89D4-194B1C06F8B7}">
+  <dimension ref="B2:F120"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="105.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="105.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" t="str" cm="1">
+        <f t="array" ref="B2:B107">+_xlfn.UNIQUE(Hoja2!F2:F172)</f>
+        <v>JUNTA DE ACCION COMUNAL DE LA VEREDA LA PALIZÁ DEL CORREGIMIENTO DE NUEVAS FLORES DEL MUNICIPIO DE SAN DIEGO</v>
+      </c>
+      <c r="F2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" t="str">
+        <v>CLUB VALLEDUPAR S.A</v>
+      </c>
+      <c r="F3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" t="str">
+        <v>OLIVERIO CARDENAS QUINTERO</v>
+      </c>
+      <c r="F4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" t="str">
+        <v>ERCO ENERGÍA S.A.S</v>
+      </c>
+      <c r="F5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="str">
+        <v>UNERGY ENERGÍA DIGITAL S.A.S ESP</v>
+      </c>
+      <c r="F6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" t="str">
+        <v>BORIS ANTONIO ANDRADE MOVILLA</v>
+      </c>
+      <c r="F7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" t="str">
+        <v>CONSORCIO CONSTRUCTOR AUTOPISTA DEL RIO GRANDE</v>
+      </c>
+      <c r="F8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" t="str">
+        <v>CARMEN DOLORES BERRIO MAESTRE</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" t="str">
+        <v>ATLANTICA- HIC RENOVABLES S.A.S</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" t="str">
+        <v>EXTRACTORA SICARARE S.A.S</v>
+      </c>
+      <c r="F11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" t="str">
+        <v>MARÍA CLAUDIA VILLERO ARZUAGA</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" t="str">
+        <v>LASCANO MORALES &amp; HIJOS S.C.S</v>
+      </c>
+      <c r="F13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" t="str">
+        <v>VIVA MAYALES S.A.S</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" t="str">
+        <v>PROMOTORA RESERVAS DE ANDALUCÍA S.A.S</v>
+      </c>
+      <c r="F15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" t="str">
+        <v>DAYANA MARCELA LEYVA
+CARCAMO</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" t="str">
+        <v>LUIS ROBERTO POSADA SANCHEZ</v>
+      </c>
+      <c r="F17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" t="str">
+        <v>JUAN DANIEL ROJAS MEJIA</v>
+      </c>
+      <c r="F18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" t="str">
+        <v>CARMEN MARIA
+SERRANO ROMERO</v>
+      </c>
+      <c r="F19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" t="str">
+        <v>ESE HOSPITAL ROSARIO
+PUMAREJO DE LÓPEZ</v>
+      </c>
+      <c r="F20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" t="str">
+        <v>PROYECTOS E INVERSIONES MPL</v>
+      </c>
+      <c r="F21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" t="str">
+        <v>Departamento del Cesar</v>
+      </c>
+      <c r="F22" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" t="str">
+        <v>BLACK ORCHID SOLAR MANAGEMENT S.A.S</v>
+      </c>
+      <c r="F23" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" t="str">
+        <v>CENIT TRANSPORTE Y LOGISTICA DE HIDROCARBUROS S.A.S.</v>
+      </c>
+      <c r="F24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" t="str">
+        <v>RODAS SOLAR S.A.S</v>
+      </c>
+      <c r="F25" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" t="str">
+        <v>CONSORCIO TRANSVERSAL VIAL NEVADĀ</v>
+      </c>
+      <c r="F26" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" t="str">
+        <v>Municipio de Valledupar</v>
+      </c>
+      <c r="F27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" t="str">
+        <v>SERPETCOL
+S.A.S</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" t="str">
+        <v>NUEVA CLINICA ARENAS</v>
+      </c>
+      <c r="F29" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" t="str">
+        <v>SERVICONSTRUCCIONES DEL CARIBE S.A.S.</v>
+      </c>
+      <c r="F30" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" t="str">
+        <v>Secretario de Obras Públicas</v>
+      </c>
+      <c r="F31" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" t="str">
+        <v>Alcaldia</v>
+      </c>
+      <c r="F32" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" t="str">
+        <v>CESAR AUGUSTO SIERRA MARQUEZ</v>
+      </c>
+      <c r="F33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34" t="str">
+        <v>DIEGO MERCADO SANABRIA</v>
+      </c>
+      <c r="F34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35" t="str">
+        <v>INVERSIONES GALAMBAO S.A.S</v>
+      </c>
+      <c r="F35" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" t="str">
+        <v>CLAUDIA LUZ PARRA CASTAÑO</v>
+      </c>
+      <c r="F36" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" t="str">
+        <v>Gobernacion</v>
+      </c>
+      <c r="F37" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" t="str">
+        <v>NELSON MANUEL GONZALEZ GONZALEZ</v>
+      </c>
+      <c r="F38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39" t="str">
+        <v>ANYEL DANIELA QUIÑONEZ HUERTAS</v>
+      </c>
+      <c r="F39" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40" t="str">
+        <v>MARIA ALEJANDRA ARZUAGA PADILLA</v>
+      </c>
+      <c r="F40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B41" t="str">
+        <v>UNIÓN TEMPORAL VIAL VLP</v>
+      </c>
+      <c r="F41" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B42" t="str">
+        <v>ALCALDÍA DEL MUNICIPIO DE VALLEDUPAR</v>
+      </c>
+      <c r="F42" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B43" t="str">
+        <v>CONSTRUAMBIENTE S.A.S</v>
+      </c>
+      <c r="F43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B44" t="str">
+        <v>CORPORACION DE CIENCIA Y TECNOLOGIA PARA EL DESARROLLO DE LA INDUSTRIA NAVAL, MARITIMA Y FLUVIAL- COTECMAR</v>
+      </c>
+      <c r="F44" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45" t="str">
+        <v>TRANSPORTADORA DE GAS INTERNACIONAL S.A</v>
+      </c>
+      <c r="F45" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B46" t="str">
+        <v>YUMA CONCESIONARIA S.A.</v>
+      </c>
+      <c r="F46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B47" t="str">
+        <v>HELCIAS RODOLFO
+CASTILLA VALERA</v>
+      </c>
+      <c r="F47" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48" t="str">
+        <v>EQUIMAQ DEL CESAR S.A.S.</v>
+      </c>
+      <c r="F48" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B49" t="str">
+        <v>CONSORCIO LA GLORIETA</v>
+      </c>
+      <c r="F49" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B50" t="str">
+        <v>ORBE SAS CONSTRUCCIONES</v>
+      </c>
+      <c r="F50" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B51" t="str">
+        <v>OLIVIERO CARDENAS QUINTERO</v>
+      </c>
+      <c r="F51" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B52" t="str">
+        <v>LIZANDRO JOSE VEGA ARAUJO</v>
+      </c>
+      <c r="F52" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B53" t="str">
+        <v>ANTONIO LUIS ANDRADRE ANDRADE</v>
+      </c>
+      <c r="F53" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B54" t="str">
+        <v>SOMAYA LILI CASTRO PACHECO</v>
+      </c>
+      <c r="F54" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B55" t="str">
+        <v>REDOMACOL SAS</v>
+      </c>
+      <c r="F55" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B56" t="str">
+        <v>UNIVERSIDAD DE SANTANDER</v>
+      </c>
+      <c r="F56" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B57" t="str">
+        <v>INVERSIONES GLP SAS ESP</v>
+      </c>
+      <c r="F57" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B58" t="str">
+        <v>GLORISETH QUINTANA PABON</v>
+      </c>
+      <c r="F58" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B59" t="str">
+        <v>RODOLFO CALDERÓN OROZCO</v>
+      </c>
+      <c r="F59" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B60" t="str">
+        <v>AEREOPUERTO DE ORIENTES S.A.S</v>
+      </c>
+      <c r="F60" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B61" t="str">
+        <v>JOSE ALBERTO GUTIERREZ MIELES</v>
+      </c>
+      <c r="F61" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B62" t="str">
+        <v>INVERSIONES Y PROYECTOS SAS</v>
+      </c>
+      <c r="F62" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B63" t="str">
+        <v>ESE HOSPITAL ROSARIO PUMAREJO DE LÓPEZ</v>
+      </c>
+      <c r="F63" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B64" t="str">
+        <v>IMEM CONTRUCCIONES</v>
+      </c>
+      <c r="F64" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B65" t="str">
+        <v>ESE HOSPITAL el Socorro</v>
+      </c>
+      <c r="F65" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B66" t="str">
+        <v>JUDITH DEL CARMEN GONZALES BOLAÑOS</v>
+      </c>
+      <c r="F66" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B67" t="str">
+        <v>CONSTRUVID S.A.S</v>
+      </c>
+      <c r="F67" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B68" t="str">
+        <v>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA (UNAD)</v>
+      </c>
+      <c r="F68" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B69" t="str">
+        <v>AUTOPISTA DEL RIO GRANDE S.A.S</v>
+      </c>
+      <c r="F69" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B70" t="str">
+        <v>OVIER JOSE JIMENEZ PALMERA</v>
+      </c>
+      <c r="F70" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B71" t="str">
+        <v>INVERSIONES GUATAPURI SAS</v>
+      </c>
+      <c r="F71" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B72" t="str">
+        <v>CONSORCIO CONTRU-EDUCATIVO EL COPEY</v>
+      </c>
+      <c r="F72" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B73" t="str">
+        <v>PEDRO NEL PINO PORTILLA</v>
+      </c>
+      <c r="F73" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B74" t="str">
+        <v>HERNÁN
+EDUARDO BAQUERO RODRIGUEZ</v>
+      </c>
+      <c r="F74" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B75" t="str">
+        <v>JUAN DANIEL ROJAS MEJÍA.</v>
+      </c>
+      <c r="F75" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B76" t="str">
+        <v>MOISES EDUARDO GIL MAESTR</v>
+      </c>
+      <c r="F76" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B77" t="str">
+        <v>PARQUE SOLAR EL UNIÓN S.A.S E.S.P</v>
+      </c>
+      <c r="F77" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B78" t="str">
+        <v>BUEN FUTURO LIMITADA Y
+COMPAÑÍA S.C.A</v>
+      </c>
+      <c r="F78" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B79" t="str">
+        <v>LLALIME SERRANO DAZA</v>
+      </c>
+      <c r="F79" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B80" t="str">
+        <v>ALCALDÍA DEL MUNICIPIO DE PAILITAS</v>
+      </c>
+      <c r="F80" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B81" t="str">
+        <v>PEDRO MIGUEL LOZANO ORTIZ</v>
+      </c>
+      <c r="F81" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B82" t="str">
+        <v>VICTOR ENRIQUE FUENTES JIMENEZ</v>
+      </c>
+      <c r="F82" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B83" t="str">
+        <v>JOSE DEL CARMEN SUAREZ INFANTE</v>
+      </c>
+      <c r="F83" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B84" t="str">
+        <v>MARIA TERESA ORTIZ MOLINA</v>
+      </c>
+      <c r="F84" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B85" t="str">
+        <v>GRUPO ENERGETICO DE SANTANDER S.A.S E.S.P</v>
+      </c>
+      <c r="F85" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B86" t="str">
+        <v>ORLANDO ANTONIO
+AGUILAR QUINTERO</v>
+      </c>
+      <c r="F86" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B87" t="str">
+        <v>EVOLUSUN COLOMBIA S.A.S</v>
+      </c>
+      <c r="F87" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B88" t="str">
+        <v>SELENA QUINTERO QUINTERO</v>
+      </c>
+      <c r="F88" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B89" t="str">
+        <v>ELVIA MILENA SANJUAN DÁVILA</v>
+      </c>
+      <c r="F89" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B90" t="str">
+        <v>VIVIANA GONZALEZ SANCHEZ</v>
+      </c>
+      <c r="F90" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B91" t="str">
+        <v>FERMIN RAMÍREZ BAYONA</v>
+      </c>
+      <c r="F91" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B92" t="str">
+        <v>JENNIFER ANILLO RIOS</v>
+      </c>
+      <c r="F92" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B93" t="str">
+        <v>MARICELA BECERRA
+CALDERON</v>
+      </c>
+      <c r="F93" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B94" t="str">
+        <v>MARIA MARTHA
+LACOUTURE MAYA</v>
+      </c>
+      <c r="F94" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B95" t="str">
+        <v>SILVIA PATRICIA MARTINEZ MARTINEZ</v>
+      </c>
+      <c r="F95" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B96" t="str">
+        <v>LILIA VARGAS DE MENDOZA</v>
+      </c>
+      <c r="F96" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B97" t="str">
+        <v>NESTOR JAVIER ALFARO BENITEZ</v>
+      </c>
+      <c r="F97" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B98" t="str">
+        <v>JOSE LUIS PALOMINO LOPEZ</v>
+      </c>
+      <c r="F98" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B99" t="str">
+        <v>SANDRA MILENA BARAHONA VELEZ</v>
+      </c>
+      <c r="F99" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B100" t="str">
+        <v>Fermin Ramirez Bayona</v>
+      </c>
+      <c r="F100" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B101" t="str">
+        <v>Javier Murgas Barreto</v>
+      </c>
+      <c r="F101" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B102" t="str">
+        <v>Elizabeth Gutiérrez</v>
+      </c>
+      <c r="F102" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B103" t="str">
+        <v>Ricardo Rafael Fuente Jiménez</v>
+      </c>
+      <c r="F103" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B104" t="str">
+        <v>COL AGROFORESTAL LA JAGUA ZOMAC S.A.S</v>
+      </c>
+      <c r="F104" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B105" t="str">
+        <v>RODAS SOLAR S.A.S.</v>
+      </c>
+      <c r="F105" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B106" t="str">
+        <v>LA ESTACIÓN SOLAR S.A.S E.S.P</v>
+      </c>
+      <c r="F106" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B107" t="str">
+        <v>Persona natural</v>
+      </c>
+      <c r="F107" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F108" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F109" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F110" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F111" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F112" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="113" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F113" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="114" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F114" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F115" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="116" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F116" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="117" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F117" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="118" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F118" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F119" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="120" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F120" t="s">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:F120">
+    <sortCondition ref="F2:F120"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Fechas_CARS.xlsx
+++ b/Fechas_CARS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MiguelAndresBeltranG\Documents\UNERGY\Automatizacion\App CARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D875E87B-B879-4273-9394-EDF71E50D93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6CB127-A3F5-4223-9A98-6A9578B37153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="556" xr2:uid="{360465FD-DB33-40A4-B804-83F77FD168BF}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="321">
   <si>
     <t>Tipo</t>
   </si>
@@ -3131,7 +3131,7 @@
         <v>105</v>
       </c>
       <c r="G49" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2">
@@ -3657,7 +3657,7 @@
         <v>125</v>
       </c>
       <c r="G63" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2">
@@ -6770,7 +6770,7 @@
         <v>229</v>
       </c>
       <c r="G142" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="2">
@@ -7772,6 +7772,9 @@
       </c>
       <c r="F168" t="s">
         <v>203</v>
+      </c>
+      <c r="G168" t="s">
+        <v>89</v>
       </c>
       <c r="H168" s="2">
         <v>46100</v>

--- a/Fechas_CARS.xlsx
+++ b/Fechas_CARS.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MiguelAndresBeltranG\Documents\UNERGY\Automatizacion\App CARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDB07C4-CD3D-4AC8-A0F6-A12276A82B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AA74B10-973B-4706-96A5-599CF7609C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$P$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$Q$177</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="341">
   <si>
     <t>Archivo</t>
   </si>
@@ -970,56 +969,6 @@
     <t>LA ESTACIÓN SOLAR S.A.S E.S.P</t>
   </si>
   <si>
-    <t>ATLANTICA-HIC RENOVABLES S.A.S</t>
-  </si>
-  <si>
-    <t>AUTOPISTA DEL RIO
-GRANDE S.A.S</t>
-  </si>
-  <si>
-    <t>BLACK
-ORCHID SOLAR MANAGEMENT S.A.S</t>
-  </si>
-  <si>
-    <t>CESAR AUGUSTO SIERRA
-MARQUEZ</t>
-  </si>
-  <si>
-    <t>CONSORCIO CONSTRUCTOR
-PISTA DEL RIO GRANDE</t>
-  </si>
-  <si>
-    <t>CONSORCIO
-CONSTRUCTOR AUTOPISTA DEL RIO GRANDE</t>
-  </si>
-  <si>
-    <t>CORPORACION DE CIENCIA Y TECNOLOGIA PARA EL DESARROLLO DE LA INDUSTRIA NAVAL, MARITIMA Y FLUVIAL- CОТЕСМАR</t>
-  </si>
-  <si>
-    <t>ERCO ENERGIA S.A.S</t>
-  </si>
-  <si>
-    <t>ERCO
-ENERGIA S.A.S</t>
-  </si>
-  <si>
-    <t>SOLENIUM S.A.S</t>
-  </si>
-  <si>
-    <t>TRANSPORTADORA DE GAS INTERNACIONAL S</t>
-  </si>
-  <si>
-    <t>TRANSPORTADORA DE GAS
-INTERNACIONAL S.A</t>
-  </si>
-  <si>
-    <t>UNERGY ENERGÍA DIGITAL S.A.S E.S.P,</t>
-  </si>
-  <si>
-    <t>UNERGY
-ENERGÍA DIGITAL S.A.S ESP</t>
-  </si>
-  <si>
     <t>AA-00032-26</t>
   </si>
   <si>
@@ -1105,6 +1054,21 @@
   </si>
   <si>
     <t>OICA TA SOLAR 1 S.A.S</t>
+  </si>
+  <si>
+    <t>CORPOGUAJIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solicitud liquidacion </t>
+  </si>
+  <si>
+    <t>FORESTAGRO R S.A.S</t>
+  </si>
+  <si>
+    <t>POLLO ANDINO S.A.</t>
+  </si>
+  <si>
+    <t>Bosque natural</t>
   </si>
 </sst>
 </file>
@@ -1480,27 +1444,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P225"/>
+  <dimension ref="A1:Q253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.21875" customWidth="1"/>
     <col min="6" max="6" width="112.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="68.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" customWidth="1"/>
+    <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="16.44140625" customWidth="1"/>
+    <col min="15" max="15" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1523,31 +1487,34 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>337</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1566,27 +1533,27 @@
       <c r="G2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2">
         <v>45894</v>
       </c>
-      <c r="J2" s="2">
+      <c r="K2" s="2">
         <v>45911</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <v>46062</v>
       </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
       <c r="M2" t="s">
         <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1608,30 +1575,30 @@
       <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>45602</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J3" s="2">
         <v>45707</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
         <v>46071</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>11</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>35.229999999999997</v>
       </c>
-      <c r="N3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3">
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1653,24 +1620,24 @@
       <c r="G4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>45954</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <v>45973</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
         <v>46056</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>106</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>579.298</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1689,16 +1656,16 @@
       <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>46051</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <v>46080</v>
       </c>
-      <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1717,16 +1684,16 @@
       <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>45939</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <v>46078</v>
       </c>
-      <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1745,16 +1712,16 @@
       <c r="G7" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45982</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>46078</v>
       </c>
-      <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -1773,16 +1740,16 @@
       <c r="G8" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>45986</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <v>46078</v>
       </c>
-      <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1801,16 +1768,16 @@
       <c r="G9" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>45988</v>
       </c>
-      <c r="I9" s="2">
+      <c r="J9" s="2">
         <v>46078</v>
       </c>
-      <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1829,14 +1796,14 @@
       <c r="G10" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2">
+      <c r="I10" s="2"/>
+      <c r="J10" s="2">
         <v>46069</v>
       </c>
-      <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1855,18 +1822,18 @@
       <c r="G11" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2">
+      <c r="I11" s="2"/>
+      <c r="J11" s="2">
         <v>45392</v>
       </c>
-      <c r="J11" s="2">
+      <c r="K11" s="2">
         <v>45402</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="2">
         <v>45604</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1885,16 +1852,16 @@
       <c r="G12" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <v>45974</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="2">
         <v>46063</v>
       </c>
-      <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1916,19 +1883,19 @@
       <c r="G13" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <v>46042</v>
       </c>
-      <c r="I13" s="2">
+      <c r="J13" s="2">
         <v>46062</v>
       </c>
-      <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="N13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="L13" s="2"/>
+      <c r="O13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -1947,14 +1914,14 @@
       <c r="G14" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2">
+      <c r="I14" s="2"/>
+      <c r="J14" s="2">
         <v>46062</v>
       </c>
-      <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -1973,14 +1940,14 @@
       <c r="G15" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2">
+      <c r="I15" s="2"/>
+      <c r="J15" s="2">
         <v>46062</v>
       </c>
-      <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>51</v>
       </c>
@@ -1999,14 +1966,14 @@
       <c r="G16" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2">
         <v>46062</v>
       </c>
-      <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -2025,14 +1992,14 @@
       <c r="G17" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2">
+      <c r="I17" s="2"/>
+      <c r="J17" s="2">
         <v>46062</v>
       </c>
-      <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -2051,16 +2018,16 @@
       <c r="G18" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>46041</v>
       </c>
-      <c r="I18" s="2">
+      <c r="J18" s="2">
         <v>46059</v>
       </c>
-      <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>57</v>
       </c>
@@ -2079,16 +2046,16 @@
       <c r="G19" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>46020</v>
       </c>
-      <c r="I19" s="2">
+      <c r="J19" s="2">
         <v>46076</v>
       </c>
-      <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>59</v>
       </c>
@@ -2107,16 +2074,16 @@
       <c r="G20" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <v>45975</v>
       </c>
-      <c r="I20" s="2">
+      <c r="J20" s="2">
         <v>46028</v>
       </c>
-      <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -2135,22 +2102,22 @@
       <c r="G21" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="2">
         <v>46001</v>
       </c>
-      <c r="I21" s="2">
+      <c r="J21" s="2">
         <v>46050</v>
       </c>
-      <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="N21" t="s">
-        <v>22</v>
-      </c>
-      <c r="O21">
+      <c r="L21" s="2"/>
+      <c r="O21" t="s">
+        <v>22</v>
+      </c>
+      <c r="P21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -2169,16 +2136,16 @@
       <c r="G22" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <v>46013</v>
       </c>
-      <c r="I22" s="2">
+      <c r="J22" s="2">
         <v>46051</v>
       </c>
-      <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -2197,22 +2164,22 @@
       <c r="G23" t="s">
         <v>29</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="2">
         <v>46037</v>
       </c>
-      <c r="I23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="2">
+      <c r="K23" s="2"/>
+      <c r="L23" s="2">
         <v>46050</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>1</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.72</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -2231,22 +2198,22 @@
       <c r="G24" t="s">
         <v>20</v>
       </c>
-      <c r="H24" s="2">
+      <c r="I24" s="2">
         <v>45953</v>
       </c>
-      <c r="I24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="2">
+      <c r="K24" s="2"/>
+      <c r="L24" s="2">
         <v>46050</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>2</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>68</v>
       </c>
@@ -2268,16 +2235,16 @@
       <c r="G25" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="2">
+      <c r="I25" s="2">
         <v>46043</v>
       </c>
-      <c r="I25" s="2">
+      <c r="J25" s="2">
         <v>46083</v>
       </c>
-      <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -2296,27 +2263,27 @@
       <c r="G26" t="s">
         <v>20</v>
       </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2">
+      <c r="I26" s="2"/>
+      <c r="J26" s="2">
         <v>45874</v>
       </c>
-      <c r="J26" s="2">
+      <c r="K26" s="2">
         <v>45891</v>
       </c>
-      <c r="K26" s="2">
+      <c r="L26" s="2">
         <v>46097</v>
       </c>
-      <c r="L26" t="s">
-        <v>21</v>
-      </c>
       <c r="M26" t="s">
         <v>21</v>
       </c>
       <c r="N26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -2338,27 +2305,27 @@
       <c r="G27" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="2">
+      <c r="I27" s="2">
         <v>46009</v>
       </c>
-      <c r="I27" s="2">
+      <c r="J27" s="2">
         <v>46083</v>
       </c>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2">
+      <c r="K27" s="2"/>
+      <c r="L27" s="2">
         <v>46248</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>557</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>301.72000000000003</v>
       </c>
-      <c r="N27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="O27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>74</v>
       </c>
@@ -2377,16 +2344,16 @@
       <c r="G28" t="s">
         <v>20</v>
       </c>
-      <c r="H28" s="2">
+      <c r="I28" s="2">
         <v>46085</v>
       </c>
-      <c r="I28" s="2">
+      <c r="J28" s="2">
         <v>46099</v>
       </c>
-      <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>75</v>
       </c>
@@ -2408,24 +2375,24 @@
       <c r="G29" t="s">
         <v>20</v>
       </c>
-      <c r="H29" s="2">
+      <c r="I29" s="2">
         <v>46008</v>
       </c>
-      <c r="I29" s="2">
+      <c r="J29" s="2">
         <v>46062</v>
       </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2">
+      <c r="K29" s="2"/>
+      <c r="L29" s="2">
         <v>46090</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>1</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>29.981999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>76</v>
       </c>
@@ -2444,27 +2411,27 @@
       <c r="G30" t="s">
         <v>20</v>
       </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2">
+      <c r="I30" s="2"/>
+      <c r="J30" s="2">
         <v>45520</v>
       </c>
-      <c r="J30" s="2">
+      <c r="K30" s="2">
         <v>45546</v>
       </c>
-      <c r="K30" s="2">
+      <c r="L30" s="2">
         <v>46100</v>
       </c>
-      <c r="L30" t="s">
-        <v>21</v>
-      </c>
       <c r="M30" t="s">
         <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -2486,24 +2453,24 @@
       <c r="G31" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="2">
+      <c r="I31" s="2">
         <v>45938</v>
       </c>
-      <c r="I31" s="2">
+      <c r="J31" s="2">
         <v>46062</v>
       </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2">
+      <c r="K31" s="2"/>
+      <c r="L31" s="2">
         <v>46097</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>15</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>82.825000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -2522,23 +2489,23 @@
       <c r="G32" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="2">
+      <c r="K32" s="2"/>
+      <c r="L32" s="2">
         <v>46100</v>
       </c>
-      <c r="L32" t="s">
-        <v>21</v>
-      </c>
       <c r="M32" t="s">
         <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>81</v>
       </c>
@@ -2557,27 +2524,27 @@
       <c r="G33" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2">
+      <c r="I33" s="2"/>
+      <c r="J33" s="2">
         <v>45874</v>
       </c>
-      <c r="J33" s="2">
+      <c r="K33" s="2">
         <v>45903</v>
       </c>
-      <c r="K33" s="2">
+      <c r="L33" s="2">
         <v>46099</v>
       </c>
-      <c r="L33" t="s">
-        <v>21</v>
-      </c>
       <c r="M33" t="s">
         <v>21</v>
       </c>
       <c r="N33" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>83</v>
       </c>
@@ -2599,24 +2566,24 @@
       <c r="G34" t="s">
         <v>20</v>
       </c>
-      <c r="H34" s="2">
+      <c r="I34" s="2">
         <v>45754</v>
       </c>
-      <c r="I34" s="2">
+      <c r="J34" s="2">
         <v>45883</v>
       </c>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2">
+      <c r="K34" s="2"/>
+      <c r="L34" s="2">
         <v>46105</v>
       </c>
-      <c r="L34" s="1">
+      <c r="M34" s="1">
         <v>239</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>5558.38</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>84</v>
       </c>
@@ -2635,27 +2602,27 @@
       <c r="G35" t="s">
         <v>20</v>
       </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2">
+      <c r="I35" s="2"/>
+      <c r="J35" s="2">
         <v>45946</v>
       </c>
-      <c r="J35" s="2">
+      <c r="K35" s="2">
         <v>45971</v>
       </c>
-      <c r="K35" s="2">
+      <c r="L35" s="2">
         <v>46100</v>
       </c>
-      <c r="L35" t="s">
-        <v>21</v>
-      </c>
       <c r="M35" t="s">
         <v>21</v>
       </c>
       <c r="N35" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>86</v>
       </c>
@@ -2674,27 +2641,27 @@
       <c r="G36" t="s">
         <v>20</v>
       </c>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2">
+      <c r="I36" s="2"/>
+      <c r="J36" s="2">
         <v>45520</v>
       </c>
-      <c r="J36" s="2">
+      <c r="K36" s="2">
         <v>45574</v>
       </c>
-      <c r="K36" s="2">
+      <c r="L36" s="2">
         <v>46100</v>
       </c>
-      <c r="L36" t="s">
-        <v>21</v>
-      </c>
       <c r="M36" t="s">
         <v>21</v>
       </c>
       <c r="N36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>87</v>
       </c>
@@ -2713,23 +2680,23 @@
       <c r="G37" t="s">
         <v>20</v>
       </c>
-      <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="2">
+      <c r="K37" s="2"/>
+      <c r="L37" s="2">
         <v>46105</v>
       </c>
-      <c r="L37" t="s">
-        <v>21</v>
-      </c>
       <c r="M37" t="s">
         <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>90</v>
       </c>
@@ -2748,27 +2715,27 @@
       <c r="G38" t="s">
         <v>20</v>
       </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2">
+      <c r="I38" s="2"/>
+      <c r="J38" s="2">
         <v>45821</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45861</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>46105</v>
       </c>
-      <c r="L38" t="s">
-        <v>21</v>
-      </c>
       <c r="M38" t="s">
         <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>91</v>
       </c>
@@ -2790,22 +2757,22 @@
       <c r="G39" t="s">
         <v>20</v>
       </c>
-      <c r="H39" s="2">
+      <c r="I39" s="2">
         <v>46118</v>
       </c>
-      <c r="I39" s="2">
+      <c r="J39" s="2">
         <v>46150</v>
       </c>
-      <c r="J39" s="2"/>
       <c r="K39" s="2"/>
-      <c r="M39" t="s">
+      <c r="L39" s="2"/>
+      <c r="N39" t="s">
         <v>93</v>
       </c>
-      <c r="N39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="O39" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -2824,30 +2791,30 @@
       <c r="G40" t="s">
         <v>20</v>
       </c>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2">
+      <c r="I40" s="2"/>
+      <c r="J40" s="2">
         <v>45692</v>
       </c>
-      <c r="J40" s="2">
+      <c r="K40" s="2">
         <v>45713</v>
       </c>
-      <c r="K40" s="2">
+      <c r="L40" s="2">
         <v>46014</v>
       </c>
-      <c r="L40" t="s">
-        <v>21</v>
-      </c>
       <c r="M40" t="s">
         <v>21</v>
       </c>
       <c r="N40" t="s">
-        <v>22</v>
-      </c>
-      <c r="O40">
+        <v>21</v>
+      </c>
+      <c r="O40" t="s">
+        <v>22</v>
+      </c>
+      <c r="P40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -2866,27 +2833,27 @@
       <c r="G41" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2">
+      <c r="I41" s="2"/>
+      <c r="J41" s="2">
         <v>45967</v>
       </c>
-      <c r="J41" s="2">
+      <c r="K41" s="2">
         <v>45980</v>
       </c>
-      <c r="K41" s="2">
+      <c r="L41" s="2">
         <v>46014</v>
       </c>
-      <c r="L41" t="s">
-        <v>21</v>
-      </c>
       <c r="M41" t="s">
         <v>21</v>
       </c>
       <c r="N41" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -2905,27 +2872,27 @@
       <c r="G42" t="s">
         <v>20</v>
       </c>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2">
+      <c r="I42" s="2"/>
+      <c r="J42" s="2">
         <v>45952</v>
       </c>
-      <c r="J42" s="2">
+      <c r="K42" s="2">
         <v>45966</v>
       </c>
-      <c r="K42" s="2">
+      <c r="L42" s="2">
         <v>46014</v>
       </c>
-      <c r="L42" t="s">
-        <v>21</v>
-      </c>
       <c r="M42" t="s">
         <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>100</v>
       </c>
@@ -2944,27 +2911,27 @@
       <c r="G43" t="s">
         <v>20</v>
       </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2">
+      <c r="I43" s="2"/>
+      <c r="J43" s="2">
         <v>45776</v>
       </c>
-      <c r="J43" s="2">
+      <c r="K43" s="2">
         <v>45800</v>
       </c>
-      <c r="K43" s="2">
+      <c r="L43" s="2">
         <v>46003</v>
       </c>
-      <c r="L43" t="s">
-        <v>21</v>
-      </c>
       <c r="M43" t="s">
         <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>101</v>
       </c>
@@ -2986,27 +2953,27 @@
       <c r="G44" t="s">
         <v>29</v>
       </c>
-      <c r="H44" s="2">
+      <c r="I44" s="2">
         <v>45674</v>
       </c>
-      <c r="I44" s="2">
+      <c r="J44" s="2">
         <v>45677</v>
       </c>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2">
+      <c r="K44" s="2"/>
+      <c r="L44" s="2">
         <v>46014</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>126</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>1052.8</v>
       </c>
-      <c r="N44" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="O44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>103</v>
       </c>
@@ -3028,27 +2995,27 @@
       <c r="G45" t="s">
         <v>29</v>
       </c>
-      <c r="H45" s="2">
+      <c r="I45" s="2">
         <v>45814</v>
       </c>
-      <c r="I45" s="2">
+      <c r="J45" s="2">
         <v>45846</v>
       </c>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2">
+      <c r="K45" s="2"/>
+      <c r="L45" s="2">
         <v>46009</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>1</v>
       </c>
-      <c r="M45">
+      <c r="N45">
         <v>4.37</v>
       </c>
-      <c r="N45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="O45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>105</v>
       </c>
@@ -3070,27 +3037,27 @@
       <c r="G46" t="s">
         <v>20</v>
       </c>
-      <c r="H46" s="2">
+      <c r="I46" s="2">
         <v>45967</v>
       </c>
-      <c r="I46" s="2">
+      <c r="J46" s="2">
         <v>45974</v>
       </c>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2">
+      <c r="K46" s="2"/>
+      <c r="L46" s="2">
         <v>46007</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>9</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>51.7</v>
       </c>
-      <c r="N46" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="O46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>107</v>
       </c>
@@ -3112,27 +3079,27 @@
       <c r="G47" t="s">
         <v>29</v>
       </c>
-      <c r="H47" s="2">
+      <c r="I47" s="2">
         <v>45811</v>
       </c>
-      <c r="I47" s="2">
+      <c r="J47" s="2">
         <v>45959</v>
       </c>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2">
+      <c r="K47" s="2"/>
+      <c r="L47" s="2">
         <v>45996</v>
       </c>
-      <c r="L47">
+      <c r="M47">
         <v>1</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <v>1.2450000000000001</v>
       </c>
-      <c r="N47" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="O47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>109</v>
       </c>
@@ -3154,27 +3121,27 @@
       <c r="G48" t="s">
         <v>20</v>
       </c>
-      <c r="H48" s="2">
+      <c r="I48" s="2">
         <v>45937</v>
       </c>
-      <c r="I48" s="2">
+      <c r="J48" s="2">
         <v>45966</v>
       </c>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2">
+      <c r="K48" s="2"/>
+      <c r="L48" s="2">
         <v>46001</v>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>10</v>
       </c>
-      <c r="M48">
+      <c r="N48">
         <v>10.949</v>
       </c>
-      <c r="N48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="O48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49" t="s">
         <v>111</v>
       </c>
@@ -3193,23 +3160,23 @@
       <c r="G49" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2">
+      <c r="I49" s="2"/>
+      <c r="J49" s="2">
         <v>45994</v>
       </c>
-      <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-      <c r="L49" t="s">
-        <v>21</v>
-      </c>
+      <c r="L49" s="2"/>
       <c r="M49" t="s">
         <v>21</v>
       </c>
       <c r="N49" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
       <c r="A50" t="s">
         <v>113</v>
       </c>
@@ -3228,25 +3195,25 @@
       <c r="G50" t="s">
         <v>29</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="2">
         <v>45811</v>
       </c>
-      <c r="I50" s="2">
+      <c r="J50" s="2">
         <v>45959</v>
       </c>
-      <c r="J50" s="2"/>
       <c r="K50" s="2"/>
-      <c r="L50" t="s">
-        <v>21</v>
-      </c>
+      <c r="L50" s="2"/>
       <c r="M50" t="s">
         <v>21</v>
       </c>
       <c r="N50" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51" t="s">
         <v>114</v>
       </c>
@@ -3268,25 +3235,25 @@
       <c r="G51" t="s">
         <v>29</v>
       </c>
-      <c r="H51" s="2">
+      <c r="I51" s="2">
         <v>45881</v>
       </c>
-      <c r="I51" s="2">
+      <c r="J51" s="2">
         <v>45959</v>
       </c>
-      <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-      <c r="L51" t="s">
-        <v>21</v>
-      </c>
+      <c r="L51" s="2"/>
       <c r="M51" t="s">
         <v>21</v>
       </c>
       <c r="N51" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" t="s">
         <v>116</v>
       </c>
@@ -3305,25 +3272,25 @@
       <c r="G52" t="s">
         <v>29</v>
       </c>
-      <c r="H52" s="2">
+      <c r="I52" s="2">
         <v>45922</v>
       </c>
-      <c r="I52" s="2">
+      <c r="J52" s="2">
         <v>45951</v>
       </c>
-      <c r="J52" s="2"/>
       <c r="K52" s="2"/>
-      <c r="L52" t="s">
-        <v>21</v>
-      </c>
+      <c r="L52" s="2"/>
       <c r="M52" t="s">
         <v>21</v>
       </c>
       <c r="N52" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53" t="s">
         <v>118</v>
       </c>
@@ -3342,23 +3309,23 @@
       <c r="G53" t="s">
         <v>20</v>
       </c>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2">
+      <c r="I53" s="2"/>
+      <c r="J53" s="2">
         <v>45951</v>
       </c>
-      <c r="J53" s="2"/>
       <c r="K53" s="2"/>
-      <c r="L53" t="s">
-        <v>21</v>
-      </c>
+      <c r="L53" s="2"/>
       <c r="M53" t="s">
         <v>21</v>
       </c>
       <c r="N53" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O53" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" t="s">
         <v>120</v>
       </c>
@@ -3377,25 +3344,25 @@
       <c r="G54" t="s">
         <v>20</v>
       </c>
-      <c r="H54" s="2">
+      <c r="I54" s="2">
         <v>45833</v>
       </c>
-      <c r="I54" s="2">
+      <c r="J54" s="2">
         <v>45939</v>
       </c>
-      <c r="J54" s="2"/>
       <c r="K54" s="2"/>
-      <c r="L54" t="s">
-        <v>21</v>
-      </c>
+      <c r="L54" s="2"/>
       <c r="M54" t="s">
         <v>21</v>
       </c>
       <c r="N54" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O54" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -3414,25 +3381,25 @@
       <c r="G55" t="s">
         <v>20</v>
       </c>
-      <c r="H55" s="2">
+      <c r="I55" s="2">
         <v>45925</v>
       </c>
-      <c r="I55" s="2">
+      <c r="J55" s="2">
         <v>45939</v>
       </c>
-      <c r="J55" s="2"/>
       <c r="K55" s="2"/>
-      <c r="L55" t="s">
-        <v>21</v>
-      </c>
+      <c r="L55" s="2"/>
       <c r="M55" t="s">
         <v>21</v>
       </c>
       <c r="N55" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56" t="s">
         <v>123</v>
       </c>
@@ -3451,32 +3418,32 @@
       <c r="G56" t="s">
         <v>20</v>
       </c>
-      <c r="H56" s="2">
+      <c r="I56" s="2">
         <v>45485</v>
       </c>
-      <c r="I56" s="2">
+      <c r="J56" s="2">
         <v>45583</v>
       </c>
-      <c r="J56" s="2">
+      <c r="K56" s="2">
         <v>45603</v>
       </c>
-      <c r="K56" s="2">
+      <c r="L56" s="2">
         <v>45933</v>
       </c>
-      <c r="L56" t="s">
-        <v>21</v>
-      </c>
       <c r="M56" t="s">
         <v>21</v>
       </c>
       <c r="N56" t="s">
-        <v>22</v>
-      </c>
-      <c r="O56">
+        <v>21</v>
+      </c>
+      <c r="O56" t="s">
+        <v>22</v>
+      </c>
+      <c r="P56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:16">
       <c r="A57" t="s">
         <v>125</v>
       </c>
@@ -3495,30 +3462,30 @@
       <c r="G57" t="s">
         <v>20</v>
       </c>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2">
+      <c r="I57" s="2"/>
+      <c r="J57" s="2">
         <v>45786</v>
       </c>
-      <c r="J57" s="2">
+      <c r="K57" s="2">
         <v>45811</v>
       </c>
-      <c r="K57" s="2">
+      <c r="L57" s="2">
         <v>45933</v>
       </c>
-      <c r="L57" t="s">
-        <v>21</v>
-      </c>
       <c r="M57" t="s">
         <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>22</v>
-      </c>
-      <c r="O57">
+        <v>21</v>
+      </c>
+      <c r="O57" t="s">
+        <v>22</v>
+      </c>
+      <c r="P57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:16">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -3537,30 +3504,30 @@
       <c r="G58" t="s">
         <v>20</v>
       </c>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2">
+      <c r="I58" s="2"/>
+      <c r="J58" s="2">
         <v>45786</v>
       </c>
-      <c r="J58" s="2">
+      <c r="K58" s="2">
         <v>45813</v>
       </c>
-      <c r="K58" s="2">
+      <c r="L58" s="2">
         <v>45932</v>
       </c>
-      <c r="L58" t="s">
-        <v>21</v>
-      </c>
       <c r="M58" t="s">
         <v>21</v>
       </c>
       <c r="N58" t="s">
-        <v>22</v>
-      </c>
-      <c r="O58">
+        <v>21</v>
+      </c>
+      <c r="O58" t="s">
+        <v>22</v>
+      </c>
+      <c r="P58">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:16">
       <c r="A59" t="s">
         <v>128</v>
       </c>
@@ -3579,23 +3546,23 @@
       <c r="G59" t="s">
         <v>20</v>
       </c>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2">
+      <c r="I59" s="2"/>
+      <c r="J59" s="2">
         <v>45954</v>
       </c>
-      <c r="J59" s="2"/>
       <c r="K59" s="2"/>
-      <c r="L59" t="s">
-        <v>21</v>
-      </c>
+      <c r="L59" s="2"/>
       <c r="M59" t="s">
         <v>21</v>
       </c>
       <c r="N59" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O59" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60" t="s">
         <v>130</v>
       </c>
@@ -3614,23 +3581,23 @@
       <c r="G60" t="s">
         <v>20</v>
       </c>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2">
+      <c r="I60" s="2"/>
+      <c r="J60" s="2">
         <v>45954</v>
       </c>
-      <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" t="s">
-        <v>21</v>
-      </c>
+      <c r="L60" s="2"/>
       <c r="M60" t="s">
         <v>21</v>
       </c>
       <c r="N60" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O60" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61" t="s">
         <v>131</v>
       </c>
@@ -3649,23 +3616,23 @@
       <c r="G61" t="s">
         <v>20</v>
       </c>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2">
+      <c r="I61" s="2"/>
+      <c r="J61" s="2">
         <v>45936</v>
       </c>
-      <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-      <c r="L61" t="s">
-        <v>21</v>
-      </c>
+      <c r="L61" s="2"/>
       <c r="M61" t="s">
         <v>21</v>
       </c>
       <c r="N61" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62" t="s">
         <v>132</v>
       </c>
@@ -3684,23 +3651,23 @@
       <c r="G62" t="s">
         <v>20</v>
       </c>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2">
+      <c r="I62" s="2"/>
+      <c r="J62" s="2">
         <v>45945</v>
       </c>
-      <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-      <c r="L62" t="s">
-        <v>21</v>
-      </c>
+      <c r="L62" s="2"/>
       <c r="M62" t="s">
         <v>21</v>
       </c>
       <c r="N62" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
       <c r="A63" t="s">
         <v>134</v>
       </c>
@@ -3719,23 +3686,23 @@
       <c r="G63" t="s">
         <v>29</v>
       </c>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2">
+      <c r="I63" s="2"/>
+      <c r="J63" s="2">
         <v>45944</v>
       </c>
-      <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" t="s">
-        <v>21</v>
-      </c>
+      <c r="L63" s="2"/>
       <c r="M63" t="s">
         <v>21</v>
       </c>
       <c r="N63" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O63" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
       <c r="A64" t="s">
         <v>136</v>
       </c>
@@ -3754,23 +3721,23 @@
       <c r="G64" t="s">
         <v>20</v>
       </c>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2">
+      <c r="I64" s="2"/>
+      <c r="J64" s="2">
         <v>46224</v>
       </c>
-      <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-      <c r="L64" t="s">
-        <v>21</v>
-      </c>
+      <c r="L64" s="2"/>
       <c r="M64" t="s">
         <v>21</v>
       </c>
       <c r="N64" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O64" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17">
       <c r="A65" t="s">
         <v>137</v>
       </c>
@@ -3789,23 +3756,23 @@
       <c r="G65" t="s">
         <v>20</v>
       </c>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2">
+      <c r="I65" s="2"/>
+      <c r="J65" s="2">
         <v>46218</v>
       </c>
-      <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" t="s">
-        <v>21</v>
-      </c>
+      <c r="L65" s="2"/>
       <c r="M65" t="s">
         <v>21</v>
       </c>
       <c r="N65" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O65" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
       <c r="A66" t="s">
         <v>139</v>
       </c>
@@ -3824,23 +3791,23 @@
       <c r="G66" t="s">
         <v>20</v>
       </c>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2">
+      <c r="I66" s="2"/>
+      <c r="J66" s="2">
         <v>46218</v>
       </c>
-      <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" t="s">
-        <v>21</v>
-      </c>
+      <c r="L66" s="2"/>
       <c r="M66" t="s">
         <v>21</v>
       </c>
       <c r="N66" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O66" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17">
       <c r="A67" t="s">
         <v>140</v>
       </c>
@@ -3862,30 +3829,30 @@
       <c r="G67" t="s">
         <v>20</v>
       </c>
-      <c r="H67" s="2">
+      <c r="I67" s="2">
         <v>46149</v>
       </c>
-      <c r="I67" s="2">
+      <c r="J67" s="2">
         <v>46189</v>
       </c>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2">
+      <c r="K67" s="2"/>
+      <c r="L67" s="2">
         <v>46233</v>
       </c>
-      <c r="L67">
+      <c r="M67">
         <v>18</v>
       </c>
-      <c r="M67">
+      <c r="N67">
         <v>33.58</v>
       </c>
-      <c r="N67" t="s">
-        <v>22</v>
-      </c>
-      <c r="O67">
+      <c r="O67" t="s">
+        <v>22</v>
+      </c>
+      <c r="P67">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:17">
       <c r="A68" t="s">
         <v>142</v>
       </c>
@@ -3907,27 +3874,27 @@
       <c r="G68" t="s">
         <v>20</v>
       </c>
-      <c r="H68" s="2">
+      <c r="I68" s="2">
         <v>46176</v>
       </c>
-      <c r="I68" s="2">
+      <c r="J68" s="2">
         <v>46195</v>
       </c>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2">
+      <c r="K68" s="2"/>
+      <c r="L68" s="2">
         <v>46227</v>
       </c>
-      <c r="L68">
+      <c r="M68">
         <v>12</v>
       </c>
-      <c r="M68">
+      <c r="N68">
         <v>35.67</v>
       </c>
-      <c r="N68" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16">
+      <c r="O68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17">
       <c r="A69" t="s">
         <v>144</v>
       </c>
@@ -3949,29 +3916,29 @@
       <c r="G69" t="s">
         <v>29</v>
       </c>
-      <c r="H69" s="2">
+      <c r="I69" s="2">
         <v>46049</v>
       </c>
-      <c r="I69" s="2">
+      <c r="J69" s="2">
         <v>46198</v>
       </c>
-      <c r="J69" s="2">
+      <c r="K69" s="2">
         <v>46204</v>
       </c>
-      <c r="K69" s="2">
+      <c r="L69" s="2">
         <v>46220</v>
       </c>
-      <c r="L69">
+      <c r="M69">
         <v>102</v>
       </c>
-      <c r="M69">
+      <c r="N69">
         <v>1096.1410000000001</v>
       </c>
-      <c r="N69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16">
+      <c r="O69" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17">
       <c r="A70" t="s">
         <v>146</v>
       </c>
@@ -3993,27 +3960,27 @@
       <c r="G70" t="s">
         <v>29</v>
       </c>
-      <c r="H70" s="2">
+      <c r="I70" s="2">
         <v>46224</v>
       </c>
-      <c r="I70" s="2">
+      <c r="J70" s="2">
         <v>46162</v>
       </c>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2">
+      <c r="K70" s="2"/>
+      <c r="L70" s="2">
         <v>46211</v>
       </c>
-      <c r="L70">
+      <c r="M70">
         <v>152</v>
       </c>
-      <c r="M70">
+      <c r="N70">
         <v>380.57100000000003</v>
       </c>
-      <c r="N70" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16">
+      <c r="O70" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17">
       <c r="A71" t="s">
         <v>148</v>
       </c>
@@ -4035,27 +4002,27 @@
       <c r="G71" t="s">
         <v>20</v>
       </c>
-      <c r="H71" s="2">
+      <c r="I71" s="2">
         <v>45873</v>
       </c>
-      <c r="I71" s="2">
+      <c r="J71" s="2">
         <v>45901</v>
       </c>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2">
+      <c r="K71" s="2"/>
+      <c r="L71" s="2">
         <v>46206</v>
       </c>
-      <c r="L71">
+      <c r="M71">
         <v>4</v>
       </c>
-      <c r="M71">
+      <c r="N71">
         <v>4.58</v>
       </c>
-      <c r="N71" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16">
+      <c r="O71" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17">
       <c r="A72" t="s">
         <v>149</v>
       </c>
@@ -4077,30 +4044,30 @@
       <c r="G72" t="s">
         <v>20</v>
       </c>
-      <c r="H72" s="2">
+      <c r="I72" s="2">
         <v>45448</v>
       </c>
-      <c r="I72" s="2">
+      <c r="J72" s="2">
         <v>45527</v>
       </c>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2">
+      <c r="K72" s="2"/>
+      <c r="L72" s="2">
         <v>46184</v>
       </c>
-      <c r="L72">
+      <c r="M72">
         <v>142</v>
       </c>
-      <c r="M72">
+      <c r="N72">
         <v>294.24</v>
       </c>
-      <c r="N72" t="s">
-        <v>22</v>
-      </c>
-      <c r="O72">
+      <c r="O72" t="s">
+        <v>22</v>
+      </c>
+      <c r="P72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:17">
       <c r="A73" t="s">
         <v>150</v>
       </c>
@@ -4122,33 +4089,33 @@
       <c r="G73" t="s">
         <v>20</v>
       </c>
-      <c r="H73" s="2">
+      <c r="I73" s="2">
         <v>46051</v>
       </c>
-      <c r="I73" s="2">
+      <c r="J73" s="2">
         <v>46080</v>
       </c>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2">
+      <c r="K73" s="2"/>
+      <c r="L73" s="2">
         <v>46184</v>
       </c>
-      <c r="L73">
-        <v>16</v>
-      </c>
       <c r="M73">
+        <v>16</v>
+      </c>
+      <c r="N73">
         <v>12.025</v>
       </c>
-      <c r="N73" t="s">
-        <v>22</v>
-      </c>
-      <c r="O73">
+      <c r="O73" t="s">
+        <v>22</v>
+      </c>
+      <c r="P73">
         <v>1</v>
       </c>
-      <c r="P73" t="s">
+      <c r="Q73" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:17">
       <c r="A74" t="s">
         <v>152</v>
       </c>
@@ -4170,29 +4137,29 @@
       <c r="G74" t="s">
         <v>20</v>
       </c>
-      <c r="H74" s="2">
+      <c r="I74" s="2">
         <v>45833</v>
       </c>
-      <c r="I74" s="2">
+      <c r="J74" s="2">
         <v>45868</v>
       </c>
-      <c r="J74" s="2">
+      <c r="K74" s="2">
         <v>45939</v>
       </c>
-      <c r="K74" s="2">
+      <c r="L74" s="2">
         <v>46175</v>
       </c>
-      <c r="L74">
+      <c r="M74">
         <v>73</v>
       </c>
-      <c r="M74">
+      <c r="N74">
         <v>23.67</v>
       </c>
-      <c r="N74" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16">
+      <c r="O74" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17">
       <c r="A75" t="s">
         <v>153</v>
       </c>
@@ -4214,27 +4181,27 @@
       <c r="G75" t="s">
         <v>29</v>
       </c>
-      <c r="H75" s="2">
+      <c r="I75" s="2">
         <v>46049</v>
       </c>
-      <c r="I75" s="2">
+      <c r="J75" s="2">
         <v>46170</v>
       </c>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2">
+      <c r="K75" s="2"/>
+      <c r="L75" s="2">
         <v>46183</v>
       </c>
-      <c r="L75">
+      <c r="M75">
         <v>109</v>
       </c>
-      <c r="M75">
+      <c r="N75">
         <v>1172.77</v>
       </c>
-      <c r="N75" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16">
+      <c r="O75" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17">
       <c r="A76" t="s">
         <v>155</v>
       </c>
@@ -4253,25 +4220,25 @@
       <c r="G76" t="s">
         <v>20</v>
       </c>
-      <c r="H76" s="2">
+      <c r="I76" s="2">
         <v>46149</v>
       </c>
-      <c r="I76" s="2">
+      <c r="J76" s="2">
         <v>46203</v>
       </c>
-      <c r="J76" s="2"/>
       <c r="K76" s="2"/>
-      <c r="L76" t="s">
-        <v>21</v>
-      </c>
+      <c r="L76" s="2"/>
       <c r="M76" t="s">
         <v>21</v>
       </c>
       <c r="N76" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O76" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17">
       <c r="A77" t="s">
         <v>156</v>
       </c>
@@ -4293,25 +4260,25 @@
       <c r="G77" t="s">
         <v>29</v>
       </c>
-      <c r="H77" s="2">
+      <c r="I77" s="2">
         <v>46174</v>
       </c>
-      <c r="I77" s="2">
+      <c r="J77" s="2">
         <v>46199</v>
       </c>
-      <c r="J77" s="2"/>
       <c r="K77" s="2"/>
-      <c r="L77" t="s">
-        <v>21</v>
-      </c>
+      <c r="L77" s="2"/>
       <c r="M77" t="s">
         <v>21</v>
       </c>
       <c r="N77" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O77" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17">
       <c r="A78" t="s">
         <v>158</v>
       </c>
@@ -4333,28 +4300,28 @@
       <c r="G78" t="s">
         <v>20</v>
       </c>
-      <c r="H78" s="2">
+      <c r="I78" s="2">
         <v>46161</v>
       </c>
-      <c r="I78" s="2">
+      <c r="J78" s="2">
         <v>46199</v>
       </c>
-      <c r="J78" s="2"/>
       <c r="K78" s="2"/>
-      <c r="L78" t="s">
-        <v>21</v>
-      </c>
+      <c r="L78" s="2"/>
       <c r="M78" t="s">
         <v>21</v>
       </c>
       <c r="N78" t="s">
-        <v>22</v>
-      </c>
-      <c r="O78">
+        <v>21</v>
+      </c>
+      <c r="O78" t="s">
+        <v>22</v>
+      </c>
+      <c r="P78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:17">
       <c r="A79" t="s">
         <v>160</v>
       </c>
@@ -4376,25 +4343,25 @@
       <c r="G79" t="s">
         <v>29</v>
       </c>
-      <c r="H79" s="2">
+      <c r="I79" s="2">
         <v>46049</v>
       </c>
-      <c r="I79" s="2">
+      <c r="J79" s="2">
         <v>46198</v>
       </c>
-      <c r="J79" s="2"/>
       <c r="K79" s="2"/>
-      <c r="L79" t="s">
-        <v>21</v>
-      </c>
+      <c r="L79" s="2"/>
       <c r="M79" t="s">
         <v>21</v>
       </c>
       <c r="N79" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O79" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17">
       <c r="A80" t="s">
         <v>161</v>
       </c>
@@ -4416,25 +4383,25 @@
       <c r="G80" t="s">
         <v>20</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>46176</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>46197</v>
       </c>
-      <c r="J80" s="2"/>
       <c r="K80" s="2"/>
-      <c r="L80" t="s">
-        <v>21</v>
-      </c>
+      <c r="L80" s="2"/>
       <c r="M80" t="s">
         <v>21</v>
       </c>
       <c r="N80" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O80" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17">
       <c r="A81" t="s">
         <v>162</v>
       </c>
@@ -4456,25 +4423,25 @@
       <c r="G81" t="s">
         <v>20</v>
       </c>
-      <c r="H81" s="2">
+      <c r="I81" s="2">
         <v>46135</v>
       </c>
-      <c r="I81" s="2">
+      <c r="J81" s="2">
         <v>46195</v>
       </c>
-      <c r="J81" s="2"/>
       <c r="K81" s="2"/>
-      <c r="L81" t="s">
-        <v>21</v>
-      </c>
+      <c r="L81" s="2"/>
       <c r="M81" t="s">
         <v>21</v>
       </c>
       <c r="N81" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17">
       <c r="A82" t="s">
         <v>164</v>
       </c>
@@ -4493,25 +4460,25 @@
       <c r="G82" t="s">
         <v>20</v>
       </c>
-      <c r="H82" s="2">
+      <c r="I82" s="2">
         <v>46171</v>
       </c>
-      <c r="I82" s="2">
+      <c r="J82" s="2">
         <v>46195</v>
       </c>
-      <c r="J82" s="2"/>
       <c r="K82" s="2"/>
-      <c r="L82" t="s">
-        <v>21</v>
-      </c>
+      <c r="L82" s="2"/>
       <c r="M82" t="s">
         <v>21</v>
       </c>
       <c r="N82" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O82" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17">
       <c r="A83" t="s">
         <v>166</v>
       </c>
@@ -4530,25 +4497,25 @@
       <c r="G83" t="s">
         <v>20</v>
       </c>
-      <c r="H83" s="2">
+      <c r="I83" s="2">
         <v>46169</v>
       </c>
-      <c r="I83" s="2">
+      <c r="J83" s="2">
         <v>46189</v>
       </c>
-      <c r="J83" s="2"/>
       <c r="K83" s="2"/>
-      <c r="L83" t="s">
-        <v>21</v>
-      </c>
+      <c r="L83" s="2"/>
       <c r="M83" t="s">
         <v>21</v>
       </c>
       <c r="N83" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O83" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17">
       <c r="A84" t="s">
         <v>167</v>
       </c>
@@ -4570,25 +4537,25 @@
       <c r="G84" t="s">
         <v>20</v>
       </c>
-      <c r="H84" s="2">
+      <c r="I84" s="2">
         <v>46120</v>
       </c>
-      <c r="I84" s="2">
+      <c r="J84" s="2">
         <v>46183</v>
       </c>
-      <c r="J84" s="2"/>
       <c r="K84" s="2"/>
-      <c r="L84" t="s">
-        <v>21</v>
-      </c>
+      <c r="L84" s="2"/>
       <c r="M84" t="s">
         <v>21</v>
       </c>
       <c r="N84" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O84" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17">
       <c r="A85" t="s">
         <v>168</v>
       </c>
@@ -4610,25 +4577,25 @@
       <c r="G85" t="s">
         <v>20</v>
       </c>
-      <c r="H85" s="2">
+      <c r="I85" s="2">
         <v>46120</v>
       </c>
-      <c r="I85" s="2">
+      <c r="J85" s="2">
         <v>46183</v>
       </c>
-      <c r="J85" s="2"/>
       <c r="K85" s="2"/>
-      <c r="L85" t="s">
-        <v>21</v>
-      </c>
+      <c r="L85" s="2"/>
       <c r="M85" t="s">
         <v>21</v>
       </c>
       <c r="N85" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O85" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17">
       <c r="A86" t="s">
         <v>169</v>
       </c>
@@ -4647,23 +4614,23 @@
       <c r="G86" t="s">
         <v>20</v>
       </c>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2">
+      <c r="I86" s="2"/>
+      <c r="J86" s="2">
         <v>46182</v>
       </c>
-      <c r="J86" s="2"/>
       <c r="K86" s="2"/>
-      <c r="L86" t="s">
-        <v>21</v>
-      </c>
+      <c r="L86" s="2"/>
       <c r="M86" t="s">
         <v>21</v>
       </c>
       <c r="N86" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O86" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17">
       <c r="A87" t="s">
         <v>171</v>
       </c>
@@ -4682,23 +4649,23 @@
       <c r="G87" t="s">
         <v>29</v>
       </c>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2">
+      <c r="I87" s="2"/>
+      <c r="J87" s="2">
         <v>46177</v>
       </c>
-      <c r="J87" s="2"/>
       <c r="K87" s="2"/>
-      <c r="L87" t="s">
-        <v>21</v>
-      </c>
+      <c r="L87" s="2"/>
       <c r="M87" t="s">
         <v>21</v>
       </c>
       <c r="N87" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O87" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17">
       <c r="A88" t="s">
         <v>173</v>
       </c>
@@ -4717,25 +4684,25 @@
       <c r="G88" t="s">
         <v>20</v>
       </c>
-      <c r="H88" s="2">
+      <c r="I88" s="2">
         <v>46059</v>
       </c>
-      <c r="I88" s="2">
+      <c r="J88" s="2">
         <v>46175</v>
       </c>
-      <c r="J88" s="2"/>
       <c r="K88" s="2"/>
-      <c r="L88" t="s">
-        <v>21</v>
-      </c>
+      <c r="L88" s="2"/>
       <c r="M88" t="s">
         <v>21</v>
       </c>
       <c r="N88" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -4757,30 +4724,30 @@
       <c r="G89" t="s">
         <v>29</v>
       </c>
-      <c r="H89" s="2">
+      <c r="I89" s="2">
         <v>45881</v>
       </c>
-      <c r="I89" s="2">
+      <c r="J89" s="2">
         <v>45959</v>
       </c>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2">
+      <c r="K89" s="2"/>
+      <c r="L89" s="2">
         <v>45988</v>
       </c>
-      <c r="L89">
+      <c r="M89">
         <v>27</v>
       </c>
-      <c r="M89">
+      <c r="N89">
         <v>3.5209999999999999</v>
       </c>
-      <c r="N89" t="s">
-        <v>22</v>
-      </c>
-      <c r="O89">
+      <c r="O89" t="s">
+        <v>22</v>
+      </c>
+      <c r="P89">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:17">
       <c r="A90" t="s">
         <v>177</v>
       </c>
@@ -4802,32 +4769,32 @@
       <c r="G90" t="s">
         <v>29</v>
       </c>
-      <c r="H90" s="2">
+      <c r="I90" s="2">
         <v>45959</v>
       </c>
-      <c r="I90" s="2">
+      <c r="J90" s="2">
         <v>45971</v>
       </c>
-      <c r="J90" s="2">
+      <c r="K90" s="2">
         <v>45974</v>
       </c>
-      <c r="K90" s="2">
+      <c r="L90" s="2">
         <v>45980</v>
       </c>
-      <c r="L90">
+      <c r="M90">
         <v>3</v>
       </c>
-      <c r="M90">
+      <c r="N90">
         <v>0.69899999999999995</v>
       </c>
-      <c r="N90" t="s">
-        <v>22</v>
-      </c>
-      <c r="P90" t="s">
+      <c r="O90" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q90" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:17">
       <c r="A91" t="s">
         <v>180</v>
       </c>
@@ -4849,28 +4816,28 @@
       <c r="G91" t="s">
         <v>20</v>
       </c>
-      <c r="H91" s="2">
+      <c r="I91" s="2">
         <v>45911</v>
       </c>
-      <c r="I91" s="2">
+      <c r="J91" s="2">
         <v>45986</v>
       </c>
-      <c r="J91" s="2"/>
       <c r="K91" s="2"/>
-      <c r="L91" t="s">
-        <v>21</v>
-      </c>
+      <c r="L91" s="2"/>
       <c r="M91" t="s">
         <v>21</v>
       </c>
       <c r="N91" t="s">
-        <v>22</v>
-      </c>
-      <c r="O91">
+        <v>21</v>
+      </c>
+      <c r="O91" t="s">
+        <v>22</v>
+      </c>
+      <c r="P91">
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:17">
       <c r="A92" t="s">
         <v>182</v>
       </c>
@@ -4889,23 +4856,23 @@
       <c r="G92" t="s">
         <v>20</v>
       </c>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2">
+      <c r="I92" s="2"/>
+      <c r="J92" s="2">
         <v>45985</v>
       </c>
-      <c r="J92" s="2"/>
       <c r="K92" s="2"/>
-      <c r="L92" t="s">
-        <v>21</v>
-      </c>
+      <c r="L92" s="2"/>
       <c r="M92" t="s">
         <v>21</v>
       </c>
       <c r="N92" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O92" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17">
       <c r="A93" t="s">
         <v>183</v>
       </c>
@@ -4924,25 +4891,25 @@
       <c r="G93" t="s">
         <v>20</v>
       </c>
-      <c r="H93" s="2">
+      <c r="I93" s="2">
         <v>45852</v>
       </c>
-      <c r="I93" s="2">
+      <c r="J93" s="2">
         <v>45985</v>
       </c>
-      <c r="J93" s="2"/>
       <c r="K93" s="2"/>
-      <c r="L93" t="s">
-        <v>21</v>
-      </c>
+      <c r="L93" s="2"/>
       <c r="M93" t="s">
         <v>21</v>
       </c>
       <c r="N93" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O93" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17">
       <c r="A94" t="s">
         <v>184</v>
       </c>
@@ -4961,23 +4928,23 @@
       <c r="G94" t="s">
         <v>20</v>
       </c>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2">
+      <c r="I94" s="2"/>
+      <c r="J94" s="2">
         <v>45985</v>
       </c>
-      <c r="J94" s="2"/>
       <c r="K94" s="2"/>
-      <c r="L94" t="s">
-        <v>21</v>
-      </c>
+      <c r="L94" s="2"/>
       <c r="M94" t="s">
         <v>21</v>
       </c>
       <c r="N94" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O94" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17">
       <c r="A95" t="s">
         <v>185</v>
       </c>
@@ -4996,25 +4963,25 @@
       <c r="G95" t="s">
         <v>20</v>
       </c>
-      <c r="H95" s="2">
+      <c r="I95" s="2">
         <v>45953</v>
       </c>
-      <c r="I95" s="2">
+      <c r="J95" s="2">
         <v>45980</v>
       </c>
-      <c r="J95" s="2"/>
       <c r="K95" s="2"/>
-      <c r="L95" t="s">
-        <v>21</v>
-      </c>
+      <c r="L95" s="2"/>
       <c r="M95" t="s">
         <v>21</v>
       </c>
       <c r="N95" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O95" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17">
       <c r="A96" t="s">
         <v>187</v>
       </c>
@@ -5036,25 +5003,25 @@
       <c r="G96" t="s">
         <v>20</v>
       </c>
-      <c r="H96" s="2">
+      <c r="I96" s="2">
         <v>45980</v>
       </c>
-      <c r="I96" s="2">
+      <c r="J96" s="2">
         <v>45982</v>
       </c>
-      <c r="J96" s="2"/>
       <c r="K96" s="2"/>
-      <c r="L96" t="s">
-        <v>21</v>
-      </c>
+      <c r="L96" s="2"/>
       <c r="M96" t="s">
         <v>21</v>
       </c>
       <c r="N96" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O96" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
       <c r="A97" t="s">
         <v>189</v>
       </c>
@@ -5073,25 +5040,25 @@
       <c r="G97" t="s">
         <v>20</v>
       </c>
-      <c r="H97" s="2">
+      <c r="I97" s="2">
         <v>45967</v>
       </c>
-      <c r="I97" s="2">
+      <c r="J97" s="2">
         <v>45974</v>
       </c>
-      <c r="J97" s="2"/>
       <c r="K97" s="2"/>
-      <c r="L97" t="s">
-        <v>21</v>
-      </c>
+      <c r="L97" s="2"/>
       <c r="M97" t="s">
         <v>21</v>
       </c>
       <c r="N97" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O97" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
       <c r="A98" t="s">
         <v>190</v>
       </c>
@@ -5113,25 +5080,25 @@
       <c r="G98" t="s">
         <v>29</v>
       </c>
-      <c r="H98" s="2">
+      <c r="I98" s="2">
         <v>45959</v>
       </c>
-      <c r="I98" s="2">
+      <c r="J98" s="2">
         <v>45971</v>
       </c>
-      <c r="J98" s="2"/>
       <c r="K98" s="2"/>
-      <c r="L98" t="s">
-        <v>21</v>
-      </c>
+      <c r="L98" s="2"/>
       <c r="M98" t="s">
         <v>21</v>
       </c>
       <c r="N98" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O98" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
       <c r="A99" t="s">
         <v>191</v>
       </c>
@@ -5150,25 +5117,25 @@
       <c r="G99" t="s">
         <v>29</v>
       </c>
-      <c r="H99" s="2">
+      <c r="I99" s="2">
         <v>45954</v>
       </c>
-      <c r="I99" s="2">
+      <c r="J99" s="2">
         <v>45973</v>
       </c>
-      <c r="J99" s="2"/>
       <c r="K99" s="2"/>
-      <c r="L99" t="s">
-        <v>21</v>
-      </c>
+      <c r="L99" s="2"/>
       <c r="M99" t="s">
         <v>21</v>
       </c>
       <c r="N99" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O99" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
       <c r="A100" t="s">
         <v>192</v>
       </c>
@@ -5187,25 +5154,25 @@
       <c r="G100" t="s">
         <v>29</v>
       </c>
-      <c r="H100" s="2">
+      <c r="I100" s="2">
         <v>45954</v>
       </c>
-      <c r="I100" s="2">
+      <c r="J100" s="2">
         <v>45973</v>
       </c>
-      <c r="J100" s="2"/>
       <c r="K100" s="2"/>
-      <c r="L100" t="s">
-        <v>21</v>
-      </c>
+      <c r="L100" s="2"/>
       <c r="M100" t="s">
         <v>21</v>
       </c>
       <c r="N100" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O100" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
       <c r="A101" t="s">
         <v>193</v>
       </c>
@@ -5224,25 +5191,25 @@
       <c r="G101" t="s">
         <v>20</v>
       </c>
-      <c r="H101" s="2">
+      <c r="I101" s="2">
         <v>45799</v>
       </c>
-      <c r="I101" s="2">
+      <c r="J101" s="2">
         <v>45971</v>
       </c>
-      <c r="J101" s="2"/>
       <c r="K101" s="2"/>
-      <c r="L101" t="s">
-        <v>21</v>
-      </c>
+      <c r="L101" s="2"/>
       <c r="M101" t="s">
         <v>21</v>
       </c>
       <c r="N101" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O101" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
       <c r="A102" t="s">
         <v>194</v>
       </c>
@@ -5261,25 +5228,25 @@
       <c r="G102" t="s">
         <v>20</v>
       </c>
-      <c r="H102" s="2">
+      <c r="I102" s="2">
         <v>45852</v>
       </c>
-      <c r="I102" s="2">
+      <c r="J102" s="2">
         <v>45971</v>
       </c>
-      <c r="J102" s="2"/>
       <c r="K102" s="2"/>
-      <c r="L102" t="s">
-        <v>21</v>
-      </c>
+      <c r="L102" s="2"/>
       <c r="M102" t="s">
         <v>21</v>
       </c>
       <c r="N102" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O102" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
       <c r="A103" t="s">
         <v>195</v>
       </c>
@@ -5301,25 +5268,25 @@
       <c r="G103" t="s">
         <v>20</v>
       </c>
-      <c r="H103" s="2">
+      <c r="I103" s="2">
         <v>45937</v>
       </c>
-      <c r="I103" s="2">
+      <c r="J103" s="2">
         <v>45966</v>
       </c>
-      <c r="J103" s="2"/>
       <c r="K103" s="2"/>
-      <c r="L103" t="s">
-        <v>21</v>
-      </c>
+      <c r="L103" s="2"/>
       <c r="M103" t="s">
         <v>21</v>
       </c>
       <c r="N103" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O103" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
       <c r="A104" t="s">
         <v>197</v>
       </c>
@@ -5338,27 +5305,27 @@
       <c r="G104" t="s">
         <v>20</v>
       </c>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2">
+      <c r="I104" s="2"/>
+      <c r="J104" s="2">
         <v>45776</v>
       </c>
-      <c r="J104" s="2">
+      <c r="K104" s="2">
         <v>45798</v>
       </c>
-      <c r="K104" s="2">
+      <c r="L104" s="2">
         <v>45972</v>
       </c>
-      <c r="L104" t="s">
-        <v>21</v>
-      </c>
       <c r="M104" t="s">
         <v>21</v>
       </c>
       <c r="N104" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O104" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
       <c r="A105" t="s">
         <v>198</v>
       </c>
@@ -5377,23 +5344,23 @@
       <c r="G105" t="s">
         <v>20</v>
       </c>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2">
+      <c r="I105" s="2"/>
+      <c r="J105" s="2">
         <v>45975</v>
       </c>
-      <c r="J105" s="2"/>
       <c r="K105" s="2"/>
-      <c r="L105" t="s">
-        <v>21</v>
-      </c>
+      <c r="L105" s="2"/>
       <c r="M105" t="s">
         <v>21</v>
       </c>
       <c r="N105" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O105" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
       <c r="A106" t="s">
         <v>199</v>
       </c>
@@ -5412,27 +5379,27 @@
       <c r="G106" t="s">
         <v>20</v>
       </c>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2">
+      <c r="I106" s="2"/>
+      <c r="J106" s="2">
         <v>45936</v>
       </c>
-      <c r="J106" s="2">
+      <c r="K106" s="2">
         <v>45972</v>
       </c>
-      <c r="K106" s="2">
+      <c r="L106" s="2">
         <v>46140</v>
       </c>
-      <c r="L106" t="s">
-        <v>21</v>
-      </c>
       <c r="M106" t="s">
         <v>21</v>
       </c>
       <c r="N106" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O106" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16">
       <c r="A107" t="s">
         <v>200</v>
       </c>
@@ -5454,27 +5421,27 @@
       <c r="G107" t="s">
         <v>20</v>
       </c>
-      <c r="H107" s="2">
+      <c r="I107" s="2">
         <v>45873</v>
       </c>
-      <c r="I107" s="2">
+      <c r="J107" s="2">
         <v>45901</v>
       </c>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2">
+      <c r="K107" s="2"/>
+      <c r="L107" s="2">
         <v>46129</v>
       </c>
-      <c r="L107" t="s">
-        <v>21</v>
-      </c>
       <c r="M107" t="s">
         <v>21</v>
       </c>
       <c r="N107" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O107" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
       <c r="A108" t="s">
         <v>201</v>
       </c>
@@ -5496,27 +5463,27 @@
       <c r="G108" t="s">
         <v>29</v>
       </c>
-      <c r="H108" s="2">
+      <c r="I108" s="2">
         <v>46030</v>
       </c>
-      <c r="I108" s="2">
+      <c r="J108" s="2">
         <v>46069</v>
       </c>
-      <c r="J108" s="2"/>
-      <c r="K108" s="2">
+      <c r="K108" s="2"/>
+      <c r="L108" s="2">
         <v>46125</v>
       </c>
-      <c r="L108">
+      <c r="M108">
         <v>80</v>
       </c>
-      <c r="M108">
+      <c r="N108">
         <v>1211.4269999999999</v>
       </c>
-      <c r="N108" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15">
+      <c r="O108" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
       <c r="A109" t="s">
         <v>202</v>
       </c>
@@ -5538,25 +5505,25 @@
       <c r="G109" t="s">
         <v>29</v>
       </c>
-      <c r="H109" s="2">
+      <c r="I109" s="2">
         <v>46106</v>
       </c>
-      <c r="I109" s="2">
+      <c r="J109" s="2">
         <v>46140</v>
       </c>
-      <c r="J109" s="2"/>
       <c r="K109" s="2"/>
-      <c r="L109" t="s">
-        <v>21</v>
-      </c>
+      <c r="L109" s="2"/>
       <c r="M109" t="s">
         <v>21</v>
       </c>
       <c r="N109" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O109" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
       <c r="A110" t="s">
         <v>204</v>
       </c>
@@ -5578,28 +5545,28 @@
       <c r="G110" t="s">
         <v>20</v>
       </c>
-      <c r="H110" s="2">
+      <c r="I110" s="2">
         <v>46076</v>
       </c>
-      <c r="I110" s="2">
+      <c r="J110" s="2">
         <v>46133</v>
       </c>
-      <c r="J110" s="2"/>
       <c r="K110" s="2"/>
-      <c r="L110" t="s">
-        <v>21</v>
-      </c>
+      <c r="L110" s="2"/>
       <c r="M110" t="s">
         <v>21</v>
       </c>
       <c r="N110" t="s">
-        <v>22</v>
-      </c>
-      <c r="O110">
+        <v>21</v>
+      </c>
+      <c r="O110" t="s">
+        <v>22</v>
+      </c>
+      <c r="P110">
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:15">
+    <row r="111" spans="1:16">
       <c r="A111" t="s">
         <v>206</v>
       </c>
@@ -5621,23 +5588,23 @@
       <c r="G111" t="s">
         <v>20</v>
       </c>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2">
+      <c r="I111" s="2"/>
+      <c r="J111" s="2">
         <v>46126</v>
       </c>
-      <c r="J111" s="2"/>
       <c r="K111" s="2"/>
-      <c r="L111" t="s">
-        <v>21</v>
-      </c>
+      <c r="L111" s="2"/>
       <c r="M111" t="s">
         <v>21</v>
       </c>
       <c r="N111" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O111" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
       <c r="A112" t="s">
         <v>208</v>
       </c>
@@ -5656,25 +5623,25 @@
       <c r="G112" t="s">
         <v>20</v>
       </c>
-      <c r="H112" s="2">
+      <c r="I112" s="2">
         <v>46080</v>
       </c>
-      <c r="I112" s="2">
+      <c r="J112" s="2">
         <v>46126</v>
       </c>
-      <c r="J112" s="2"/>
       <c r="K112" s="2"/>
-      <c r="L112" t="s">
-        <v>21</v>
-      </c>
+      <c r="L112" s="2"/>
       <c r="M112" t="s">
         <v>21</v>
       </c>
       <c r="N112" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O112" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
       <c r="A113" t="s">
         <v>209</v>
       </c>
@@ -5693,23 +5660,23 @@
       <c r="G113" t="s">
         <v>20</v>
       </c>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2">
+      <c r="I113" s="2"/>
+      <c r="J113" s="2">
         <v>46125</v>
       </c>
-      <c r="J113" s="2"/>
       <c r="K113" s="2"/>
-      <c r="L113" t="s">
-        <v>21</v>
-      </c>
+      <c r="L113" s="2"/>
       <c r="M113" t="s">
         <v>21</v>
       </c>
       <c r="N113" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O113" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
       <c r="A114" t="s">
         <v>211</v>
       </c>
@@ -5728,25 +5695,25 @@
       <c r="G114" t="s">
         <v>20</v>
       </c>
-      <c r="H114" s="2">
+      <c r="I114" s="2">
         <v>45932</v>
       </c>
-      <c r="I114" s="2">
+      <c r="J114" s="2">
         <v>46125</v>
       </c>
-      <c r="J114" s="2"/>
       <c r="K114" s="2"/>
-      <c r="L114" t="s">
-        <v>21</v>
-      </c>
+      <c r="L114" s="2"/>
       <c r="M114" t="s">
         <v>21</v>
       </c>
       <c r="N114" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O114" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
       <c r="A115" t="s">
         <v>212</v>
       </c>
@@ -5765,25 +5732,25 @@
       <c r="G115" t="s">
         <v>29</v>
       </c>
-      <c r="H115" s="2">
+      <c r="I115" s="2">
         <v>46091</v>
       </c>
-      <c r="I115" s="2">
+      <c r="J115" s="2">
         <v>46121</v>
       </c>
-      <c r="J115" s="2"/>
       <c r="K115" s="2"/>
-      <c r="L115" t="s">
-        <v>21</v>
-      </c>
+      <c r="L115" s="2"/>
       <c r="M115" t="s">
         <v>21</v>
       </c>
       <c r="N115" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O115" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
       <c r="A116" t="s">
         <v>214</v>
       </c>
@@ -5802,23 +5769,23 @@
       <c r="G116" t="s">
         <v>29</v>
       </c>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2">
+      <c r="I116" s="2"/>
+      <c r="J116" s="2">
         <v>46121</v>
       </c>
-      <c r="J116" s="2"/>
       <c r="K116" s="2"/>
-      <c r="L116" t="s">
-        <v>21</v>
-      </c>
+      <c r="L116" s="2"/>
       <c r="M116" t="s">
         <v>21</v>
       </c>
       <c r="N116" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O116" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
       <c r="A117" t="s">
         <v>216</v>
       </c>
@@ -5837,25 +5804,25 @@
       <c r="G117" t="s">
         <v>20</v>
       </c>
-      <c r="H117" s="2">
+      <c r="I117" s="2">
         <v>46063</v>
       </c>
-      <c r="I117" s="2">
+      <c r="J117" s="2">
         <v>46120</v>
       </c>
-      <c r="J117" s="2"/>
       <c r="K117" s="2"/>
-      <c r="L117" t="s">
-        <v>21</v>
-      </c>
+      <c r="L117" s="2"/>
       <c r="M117" t="s">
         <v>21</v>
       </c>
       <c r="N117" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O117" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
       <c r="A118" t="s">
         <v>217</v>
       </c>
@@ -5877,25 +5844,25 @@
       <c r="G118" t="s">
         <v>20</v>
       </c>
-      <c r="H118" s="2">
+      <c r="I118" s="2">
         <v>46043</v>
       </c>
-      <c r="I118" s="2">
+      <c r="J118" s="2">
         <v>46119</v>
       </c>
-      <c r="J118" s="2"/>
       <c r="K118" s="2"/>
-      <c r="L118" t="s">
-        <v>21</v>
-      </c>
+      <c r="L118" s="2"/>
       <c r="M118" t="s">
         <v>21</v>
       </c>
       <c r="N118" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O118" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
       <c r="A119" t="s">
         <v>219</v>
       </c>
@@ -5914,25 +5881,25 @@
       <c r="G119" t="s">
         <v>20</v>
       </c>
-      <c r="H119" s="2">
+      <c r="I119" s="2">
         <v>45932</v>
       </c>
-      <c r="I119" s="2">
+      <c r="J119" s="2">
         <v>46118</v>
       </c>
-      <c r="J119" s="2"/>
       <c r="K119" s="2"/>
-      <c r="L119" t="s">
-        <v>21</v>
-      </c>
+      <c r="L119" s="2"/>
       <c r="M119" t="s">
         <v>21</v>
       </c>
       <c r="N119" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O119" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
       <c r="A120" t="s">
         <v>220</v>
       </c>
@@ -5951,23 +5918,23 @@
       <c r="G120" t="s">
         <v>20</v>
       </c>
-      <c r="H120" s="2"/>
-      <c r="I120" s="2">
+      <c r="I120" s="2"/>
+      <c r="J120" s="2">
         <v>46118</v>
       </c>
-      <c r="J120" s="2"/>
       <c r="K120" s="2"/>
-      <c r="L120" t="s">
-        <v>21</v>
-      </c>
+      <c r="L120" s="2"/>
       <c r="M120" t="s">
         <v>21</v>
       </c>
       <c r="N120" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O120" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
       <c r="A121" t="s">
         <v>221</v>
       </c>
@@ -5989,25 +5956,25 @@
       <c r="G121" t="s">
         <v>29</v>
       </c>
-      <c r="H121" s="2">
+      <c r="I121" s="2">
         <v>46027</v>
       </c>
-      <c r="I121" s="2">
+      <c r="J121" s="2">
         <v>46118</v>
       </c>
-      <c r="J121" s="2"/>
       <c r="K121" s="2"/>
-      <c r="L121" t="s">
-        <v>21</v>
-      </c>
+      <c r="L121" s="2"/>
       <c r="M121" t="s">
         <v>21</v>
       </c>
       <c r="N121" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O121" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
       <c r="A122" t="s">
         <v>223</v>
       </c>
@@ -6029,27 +5996,27 @@
       <c r="G122" t="s">
         <v>29</v>
       </c>
-      <c r="H122" s="2">
+      <c r="I122" s="2">
         <v>45845</v>
       </c>
-      <c r="I122" s="2">
+      <c r="J122" s="2">
         <v>46224</v>
       </c>
-      <c r="J122" s="2"/>
-      <c r="K122" s="2">
+      <c r="K122" s="2"/>
+      <c r="L122" s="2">
         <v>46157</v>
       </c>
-      <c r="L122">
+      <c r="M122">
         <v>1</v>
       </c>
-      <c r="M122">
+      <c r="N122">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N122" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15">
+      <c r="O122" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
       <c r="A123" t="s">
         <v>225</v>
       </c>
@@ -6068,25 +6035,25 @@
       <c r="G123" t="s">
         <v>29</v>
       </c>
-      <c r="H123" s="2">
+      <c r="I123" s="2">
         <v>45954</v>
       </c>
-      <c r="I123" s="2"/>
       <c r="J123" s="2"/>
-      <c r="K123" s="2">
+      <c r="K123" s="2"/>
+      <c r="L123" s="2">
         <v>46157</v>
       </c>
-      <c r="L123" t="s">
-        <v>21</v>
-      </c>
       <c r="M123" t="s">
         <v>21</v>
       </c>
       <c r="N123" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O123" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
       <c r="A124" t="s">
         <v>226</v>
       </c>
@@ -6108,30 +6075,30 @@
       <c r="G124" t="s">
         <v>29</v>
       </c>
-      <c r="H124" s="2">
+      <c r="I124" s="2">
         <v>46001</v>
       </c>
-      <c r="I124" s="2">
+      <c r="J124" s="2">
         <v>46050</v>
       </c>
-      <c r="J124" s="2"/>
-      <c r="K124" s="2">
+      <c r="K124" s="2"/>
+      <c r="L124" s="2">
         <v>46150</v>
       </c>
-      <c r="L124">
+      <c r="M124">
         <v>1</v>
       </c>
-      <c r="M124">
+      <c r="N124">
         <v>0.74</v>
       </c>
-      <c r="N124" t="s">
-        <v>22</v>
-      </c>
-      <c r="O124">
+      <c r="O124" t="s">
+        <v>22</v>
+      </c>
+      <c r="P124">
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:15">
+    <row r="125" spans="1:16">
       <c r="A125" t="s">
         <v>228</v>
       </c>
@@ -6153,28 +6120,28 @@
       <c r="G125" t="s">
         <v>29</v>
       </c>
-      <c r="H125" s="2">
+      <c r="I125" s="2">
         <v>45760</v>
       </c>
-      <c r="I125" s="2">
+      <c r="J125" s="2">
         <v>46170</v>
       </c>
-      <c r="J125" s="2"/>
       <c r="K125" s="2"/>
-      <c r="L125" t="s">
-        <v>21</v>
-      </c>
+      <c r="L125" s="2"/>
       <c r="M125" t="s">
         <v>21</v>
       </c>
       <c r="N125" t="s">
-        <v>22</v>
-      </c>
-      <c r="O125">
+        <v>21</v>
+      </c>
+      <c r="O125" t="s">
+        <v>22</v>
+      </c>
+      <c r="P125">
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:15">
+    <row r="126" spans="1:16">
       <c r="A126" t="s">
         <v>230</v>
       </c>
@@ -6196,25 +6163,25 @@
       <c r="G126" t="s">
         <v>29</v>
       </c>
-      <c r="H126" s="2">
+      <c r="I126" s="2">
         <v>46049</v>
       </c>
-      <c r="I126" s="2">
+      <c r="J126" s="2">
         <v>46170</v>
       </c>
-      <c r="J126" s="2"/>
       <c r="K126" s="2"/>
-      <c r="L126" t="s">
-        <v>21</v>
-      </c>
+      <c r="L126" s="2"/>
       <c r="M126" t="s">
         <v>21</v>
       </c>
       <c r="N126" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O126" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
       <c r="A127" t="s">
         <v>231</v>
       </c>
@@ -6233,23 +6200,23 @@
       <c r="G127" t="s">
         <v>20</v>
       </c>
-      <c r="H127" s="2"/>
-      <c r="I127" s="2">
+      <c r="I127" s="2"/>
+      <c r="J127" s="2">
         <v>46163</v>
       </c>
-      <c r="J127" s="2"/>
       <c r="K127" s="2"/>
-      <c r="L127" t="s">
-        <v>21</v>
-      </c>
+      <c r="L127" s="2"/>
       <c r="M127" t="s">
         <v>21</v>
       </c>
       <c r="N127" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15">
+        <v>21</v>
+      </c>
+      <c r="O127" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
       <c r="A128" t="s">
         <v>233</v>
       </c>
@@ -6271,25 +6238,25 @@
       <c r="G128" t="s">
         <v>20</v>
       </c>
-      <c r="H128" s="2">
+      <c r="I128" s="2">
         <v>46140</v>
       </c>
-      <c r="I128" s="2">
+      <c r="J128" s="2">
         <v>46163</v>
       </c>
-      <c r="J128" s="2"/>
       <c r="K128" s="2"/>
-      <c r="L128" t="s">
-        <v>21</v>
-      </c>
+      <c r="L128" s="2"/>
       <c r="M128" t="s">
         <v>21</v>
       </c>
       <c r="N128" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O128" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17">
       <c r="A129" t="s">
         <v>234</v>
       </c>
@@ -6311,25 +6278,25 @@
       <c r="G129" t="s">
         <v>29</v>
       </c>
-      <c r="H129" s="2">
+      <c r="I129" s="2">
         <v>46133</v>
       </c>
-      <c r="I129" s="2">
+      <c r="J129" s="2">
         <v>46162</v>
       </c>
-      <c r="J129" s="2"/>
       <c r="K129" s="2"/>
-      <c r="L129" t="s">
-        <v>21</v>
-      </c>
+      <c r="L129" s="2"/>
       <c r="M129" t="s">
         <v>21</v>
       </c>
       <c r="N129" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O129" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17">
       <c r="A130" t="s">
         <v>235</v>
       </c>
@@ -6348,23 +6315,23 @@
       <c r="G130" t="s">
         <v>20</v>
       </c>
-      <c r="H130" s="2"/>
-      <c r="I130" s="2">
+      <c r="I130" s="2"/>
+      <c r="J130" s="2">
         <v>46161</v>
       </c>
-      <c r="J130" s="2"/>
       <c r="K130" s="2"/>
-      <c r="L130" t="s">
-        <v>21</v>
-      </c>
+      <c r="L130" s="2"/>
       <c r="M130" t="s">
         <v>21</v>
       </c>
       <c r="N130" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O130" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17">
       <c r="A131" t="s">
         <v>237</v>
       </c>
@@ -6386,25 +6353,25 @@
       <c r="G131" t="s">
         <v>20</v>
       </c>
-      <c r="H131" s="2">
+      <c r="I131" s="2">
         <v>46118</v>
       </c>
-      <c r="I131" s="2">
+      <c r="J131" s="2">
         <v>46150</v>
       </c>
-      <c r="J131" s="2"/>
       <c r="K131" s="2"/>
-      <c r="L131" t="s">
-        <v>21</v>
-      </c>
+      <c r="L131" s="2"/>
       <c r="M131" t="s">
         <v>21</v>
       </c>
       <c r="N131" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O131" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17">
       <c r="A132" t="s">
         <v>238</v>
       </c>
@@ -6426,25 +6393,25 @@
       <c r="G132" t="s">
         <v>29</v>
       </c>
-      <c r="H132" s="2">
+      <c r="I132" s="2">
         <v>46079</v>
       </c>
-      <c r="I132" s="2">
+      <c r="J132" s="2">
         <v>46148</v>
       </c>
-      <c r="J132" s="2"/>
       <c r="K132" s="2"/>
-      <c r="L132" t="s">
-        <v>21</v>
-      </c>
+      <c r="L132" s="2"/>
       <c r="M132" t="s">
         <v>21</v>
       </c>
       <c r="N132" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O132" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17">
       <c r="A133" t="s">
         <v>240</v>
       </c>
@@ -6466,32 +6433,32 @@
       <c r="G133" t="s">
         <v>20</v>
       </c>
-      <c r="H133" s="2">
+      <c r="I133" s="2">
         <v>46071</v>
       </c>
-      <c r="I133" s="2">
+      <c r="J133" s="2">
         <v>46072</v>
       </c>
-      <c r="J133" s="2">
+      <c r="K133" s="2">
         <v>46073</v>
       </c>
-      <c r="K133" s="2">
+      <c r="L133" s="2">
         <v>46076</v>
       </c>
-      <c r="L133">
+      <c r="M133">
         <v>6</v>
       </c>
-      <c r="M133">
+      <c r="N133">
         <v>8.44</v>
       </c>
-      <c r="N133" t="s">
+      <c r="O133" t="s">
         <v>242</v>
       </c>
-      <c r="P133" t="s">
+      <c r="Q133" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:17">
       <c r="A134" t="s">
         <v>244</v>
       </c>
@@ -6513,27 +6480,27 @@
       <c r="G134" t="s">
         <v>29</v>
       </c>
-      <c r="H134" s="2">
-        <v>45994</v>
-      </c>
       <c r="I134" s="2">
         <v>45994</v>
       </c>
-      <c r="J134" s="2"/>
-      <c r="K134" s="2">
+      <c r="J134" s="2">
+        <v>45994</v>
+      </c>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2">
         <v>46038</v>
       </c>
-      <c r="L134">
+      <c r="M134">
         <v>100</v>
       </c>
-      <c r="M134">
+      <c r="N134">
         <v>1176.6099999999999</v>
       </c>
-      <c r="N134" t="s">
+      <c r="O134" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:17">
       <c r="A135" t="s">
         <v>246</v>
       </c>
@@ -6555,27 +6522,27 @@
       <c r="G135" t="s">
         <v>29</v>
       </c>
-      <c r="H135" s="2">
+      <c r="I135" s="2">
         <v>46000</v>
       </c>
-      <c r="I135" s="2">
+      <c r="J135" s="2">
         <v>46002</v>
       </c>
-      <c r="J135" s="2"/>
-      <c r="K135" s="2">
+      <c r="K135" s="2"/>
+      <c r="L135" s="2">
         <v>46036</v>
       </c>
-      <c r="L135">
+      <c r="M135">
         <v>100</v>
       </c>
-      <c r="M135">
+      <c r="N135">
         <v>942.49</v>
       </c>
-      <c r="N135" t="s">
+      <c r="O135" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:17">
       <c r="A136" t="s">
         <v>248</v>
       </c>
@@ -6594,23 +6561,23 @@
       <c r="G136" t="s">
         <v>29</v>
       </c>
-      <c r="H136" s="2"/>
-      <c r="I136" s="2">
+      <c r="I136" s="2"/>
+      <c r="J136" s="2">
         <v>46259</v>
       </c>
-      <c r="J136" s="2"/>
       <c r="K136" s="2"/>
-      <c r="L136" t="s">
-        <v>21</v>
-      </c>
+      <c r="L136" s="2"/>
       <c r="M136" t="s">
         <v>21</v>
       </c>
       <c r="N136" t="s">
+        <v>21</v>
+      </c>
+      <c r="O136" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:17">
       <c r="A137" t="s">
         <v>250</v>
       </c>
@@ -6629,23 +6596,23 @@
       <c r="G137" t="s">
         <v>29</v>
       </c>
-      <c r="H137" s="2"/>
-      <c r="I137" s="2">
+      <c r="I137" s="2"/>
+      <c r="J137" s="2">
         <v>46058</v>
       </c>
-      <c r="J137" s="2"/>
       <c r="K137" s="2"/>
-      <c r="L137" t="s">
-        <v>21</v>
-      </c>
+      <c r="L137" s="2"/>
       <c r="M137" t="s">
         <v>21</v>
       </c>
       <c r="N137" t="s">
+        <v>21</v>
+      </c>
+      <c r="O137" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:17">
       <c r="A138" t="s">
         <v>252</v>
       </c>
@@ -6667,29 +6634,29 @@
       <c r="G138" t="s">
         <v>20</v>
       </c>
-      <c r="H138" s="2">
+      <c r="I138" s="2">
         <v>46191</v>
       </c>
-      <c r="I138" s="2">
+      <c r="J138" s="2">
         <v>46217</v>
       </c>
-      <c r="J138" s="2">
+      <c r="K138" s="2">
         <v>37454</v>
       </c>
-      <c r="K138" s="2">
+      <c r="L138" s="2">
         <v>46227</v>
       </c>
-      <c r="L138">
-        <v>24</v>
-      </c>
       <c r="M138">
+        <v>24</v>
+      </c>
+      <c r="N138">
         <v>97.3</v>
       </c>
-      <c r="N138" t="s">
+      <c r="O138" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:17">
       <c r="A139" t="s">
         <v>255</v>
       </c>
@@ -6711,27 +6678,27 @@
       <c r="G139" t="s">
         <v>20</v>
       </c>
-      <c r="H139" s="2"/>
-      <c r="I139" s="2">
+      <c r="I139" s="2"/>
+      <c r="J139" s="2">
         <v>46119</v>
       </c>
-      <c r="J139" s="2">
+      <c r="K139" s="2">
         <v>46122</v>
       </c>
-      <c r="K139" s="2">
+      <c r="L139" s="2">
         <v>46147</v>
       </c>
-      <c r="L139">
+      <c r="M139">
         <v>122</v>
       </c>
-      <c r="M139">
+      <c r="N139">
         <v>3.61</v>
       </c>
-      <c r="N139" t="s">
+      <c r="O139" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:17">
       <c r="A140" t="s">
         <v>258</v>
       </c>
@@ -6753,25 +6720,25 @@
       <c r="G140" t="s">
         <v>20</v>
       </c>
-      <c r="H140" s="2"/>
-      <c r="I140" s="2">
+      <c r="I140" s="2"/>
+      <c r="J140" s="2">
         <v>46106</v>
       </c>
-      <c r="J140" s="2"/>
-      <c r="K140" s="2">
+      <c r="K140" s="2"/>
+      <c r="L140" s="2">
         <v>46132</v>
       </c>
-      <c r="L140">
+      <c r="M140">
         <v>62</v>
       </c>
-      <c r="M140">
+      <c r="N140">
         <v>101.23</v>
       </c>
-      <c r="N140" t="s">
+      <c r="O140" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:17">
       <c r="A141" t="s">
         <v>260</v>
       </c>
@@ -6793,27 +6760,27 @@
       <c r="G141" t="s">
         <v>29</v>
       </c>
-      <c r="H141" s="2">
+      <c r="I141" s="2">
         <v>46209</v>
       </c>
-      <c r="I141" s="2">
+      <c r="J141" s="2">
         <v>46260</v>
       </c>
-      <c r="J141" s="2"/>
-      <c r="K141" s="2">
+      <c r="K141" s="2"/>
+      <c r="L141" s="2">
         <v>46279</v>
       </c>
-      <c r="L141">
+      <c r="M141">
         <v>3</v>
       </c>
-      <c r="M141">
+      <c r="N141">
         <v>2.161</v>
       </c>
-      <c r="N141" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16">
+      <c r="O141" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17">
       <c r="A142" t="s">
         <v>263</v>
       </c>
@@ -6832,23 +6799,23 @@
       <c r="G142" t="s">
         <v>29</v>
       </c>
-      <c r="H142" s="2"/>
-      <c r="I142" s="2">
+      <c r="I142" s="2"/>
+      <c r="J142" s="2">
         <v>46247</v>
       </c>
-      <c r="J142" s="2"/>
       <c r="K142" s="2"/>
-      <c r="L142" t="s">
-        <v>21</v>
-      </c>
+      <c r="L142" s="2"/>
       <c r="M142" t="s">
         <v>21</v>
       </c>
       <c r="N142" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O142" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17">
       <c r="A143" t="s">
         <v>265</v>
       </c>
@@ -6867,23 +6834,23 @@
       <c r="G143" t="s">
         <v>20</v>
       </c>
-      <c r="H143" s="2"/>
-      <c r="I143" s="2">
+      <c r="I143" s="2"/>
+      <c r="J143" s="2">
         <v>46237</v>
       </c>
-      <c r="J143" s="2"/>
       <c r="K143" s="2"/>
-      <c r="L143" t="s">
-        <v>21</v>
-      </c>
+      <c r="L143" s="2"/>
       <c r="M143" t="s">
         <v>21</v>
       </c>
       <c r="N143" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="O143" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17">
       <c r="A144" t="s">
         <v>267</v>
       </c>
@@ -6905,30 +6872,30 @@
       <c r="G144" t="s">
         <v>20</v>
       </c>
-      <c r="H144" s="2">
+      <c r="I144" s="2">
         <v>46009</v>
       </c>
-      <c r="I144" s="2">
+      <c r="J144" s="2">
         <v>46083</v>
       </c>
-      <c r="J144" s="2"/>
-      <c r="K144" s="2">
+      <c r="K144" s="2"/>
+      <c r="L144" s="2">
         <v>46248</v>
       </c>
-      <c r="L144">
+      <c r="M144">
         <v>339</v>
       </c>
-      <c r="M144">
+      <c r="N144">
         <v>67.849999999999994</v>
       </c>
-      <c r="N144" t="s">
-        <v>22</v>
-      </c>
-      <c r="O144">
+      <c r="O144" t="s">
+        <v>22</v>
+      </c>
+      <c r="P144">
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:15">
       <c r="A145" t="s">
         <v>268</v>
       </c>
@@ -6950,27 +6917,27 @@
       <c r="G145" t="s">
         <v>20</v>
       </c>
-      <c r="H145" s="2">
+      <c r="I145" s="2">
         <v>46217</v>
       </c>
-      <c r="I145" s="2">
+      <c r="J145" s="2">
         <v>46247</v>
       </c>
-      <c r="J145" s="2"/>
-      <c r="K145" s="2">
+      <c r="K145" s="2"/>
+      <c r="L145" s="2">
         <v>46253</v>
       </c>
-      <c r="L145">
+      <c r="M145">
         <v>10</v>
       </c>
-      <c r="M145">
+      <c r="N145">
         <v>10.949</v>
       </c>
-      <c r="N145" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14">
+      <c r="O145" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
       <c r="A146" t="s">
         <v>270</v>
       </c>
@@ -6992,27 +6959,27 @@
       <c r="G146" t="s">
         <v>29</v>
       </c>
-      <c r="H146" s="2">
+      <c r="I146" s="2">
         <v>45826</v>
       </c>
-      <c r="I146" s="2">
+      <c r="J146" s="2">
         <v>46228</v>
       </c>
-      <c r="J146" s="2"/>
-      <c r="K146" s="2">
+      <c r="K146" s="2"/>
+      <c r="L146" s="2">
         <v>45910</v>
       </c>
-      <c r="L146">
+      <c r="M146">
         <v>68</v>
       </c>
-      <c r="M146">
+      <c r="N146">
         <v>1210.6400000000001</v>
       </c>
-      <c r="N146" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14">
+      <c r="O146" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
       <c r="A147" t="s">
         <v>272</v>
       </c>
@@ -7034,27 +7001,27 @@
       <c r="G147" t="s">
         <v>29</v>
       </c>
-      <c r="H147" s="2">
+      <c r="I147" s="2">
         <v>45866</v>
       </c>
-      <c r="I147" s="2">
+      <c r="J147" s="2">
         <v>45884</v>
       </c>
-      <c r="J147" s="2"/>
-      <c r="K147" s="2">
+      <c r="K147" s="2"/>
+      <c r="L147" s="2">
         <v>45905</v>
       </c>
-      <c r="L147">
+      <c r="M147">
         <v>1</v>
       </c>
-      <c r="M147">
+      <c r="N147">
         <v>6.7350000000000003</v>
       </c>
-      <c r="N147" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14">
+      <c r="O147" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15">
       <c r="A148" t="s">
         <v>274</v>
       </c>
@@ -7076,27 +7043,27 @@
       <c r="G148" t="s">
         <v>29</v>
       </c>
-      <c r="H148" s="2">
+      <c r="I148" s="2">
         <v>45856</v>
       </c>
-      <c r="I148" s="2">
+      <c r="J148" s="2">
         <v>45880</v>
       </c>
-      <c r="J148" s="2"/>
-      <c r="K148" s="2">
+      <c r="K148" s="2"/>
+      <c r="L148" s="2">
         <v>45905</v>
       </c>
-      <c r="L148">
+      <c r="M148">
         <v>1</v>
       </c>
-      <c r="M148">
+      <c r="N148">
         <v>16.376999999999999</v>
       </c>
-      <c r="N148" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14">
+      <c r="O148" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15">
       <c r="A149" t="s">
         <v>276</v>
       </c>
@@ -7118,27 +7085,27 @@
       <c r="G149" t="s">
         <v>20</v>
       </c>
-      <c r="H149" s="2">
+      <c r="I149" s="2">
         <v>45758</v>
       </c>
-      <c r="I149" s="2">
+      <c r="J149" s="2">
         <v>45817</v>
       </c>
-      <c r="J149" s="2"/>
-      <c r="K149" s="2">
+      <c r="K149" s="2"/>
+      <c r="L149" s="2">
         <v>45905</v>
       </c>
-      <c r="L149">
+      <c r="M149">
         <v>15</v>
       </c>
-      <c r="M149">
+      <c r="N149">
         <v>1.83</v>
       </c>
-      <c r="N149" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14">
+      <c r="O149" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
       <c r="A150" t="s">
         <v>278</v>
       </c>
@@ -7160,27 +7127,27 @@
       <c r="G150" t="s">
         <v>29</v>
       </c>
-      <c r="H150" s="2">
+      <c r="I150" s="2">
         <v>45854</v>
       </c>
-      <c r="I150" s="2">
+      <c r="J150" s="2">
         <v>45868</v>
       </c>
-      <c r="J150" s="2"/>
-      <c r="K150" s="2">
+      <c r="K150" s="2"/>
+      <c r="L150" s="2">
         <v>45902</v>
       </c>
-      <c r="L150">
+      <c r="M150">
         <v>2</v>
       </c>
-      <c r="M150">
+      <c r="N150">
         <v>54.24</v>
       </c>
-      <c r="N150" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14">
+      <c r="O150" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15">
       <c r="A151" t="s">
         <v>280</v>
       </c>
@@ -7202,27 +7169,27 @@
       <c r="G151" t="s">
         <v>29</v>
       </c>
-      <c r="H151" s="2">
+      <c r="I151" s="2">
         <v>45804</v>
       </c>
-      <c r="I151" s="2">
+      <c r="J151" s="2">
         <v>45817</v>
       </c>
-      <c r="J151" s="2"/>
-      <c r="K151" s="2">
+      <c r="K151" s="2"/>
+      <c r="L151" s="2">
         <v>45908</v>
       </c>
-      <c r="L151">
+      <c r="M151">
         <v>1</v>
       </c>
-      <c r="M151">
+      <c r="N151">
         <v>13.68</v>
       </c>
-      <c r="N151" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14">
+      <c r="O151" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
       <c r="A152" t="s">
         <v>282</v>
       </c>
@@ -7241,23 +7208,23 @@
       <c r="G152" t="s">
         <v>29</v>
       </c>
-      <c r="H152" s="2"/>
-      <c r="I152" s="2">
+      <c r="I152" s="2"/>
+      <c r="J152" s="2">
         <v>45912</v>
       </c>
-      <c r="J152" s="2"/>
       <c r="K152" s="2"/>
-      <c r="L152" t="s">
-        <v>21</v>
-      </c>
+      <c r="L152" s="2"/>
       <c r="M152" t="s">
         <v>21</v>
       </c>
       <c r="N152" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O152" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
       <c r="A153" t="s">
         <v>284</v>
       </c>
@@ -7276,23 +7243,23 @@
       <c r="G153" t="s">
         <v>29</v>
       </c>
-      <c r="H153" s="2"/>
-      <c r="I153" s="2">
+      <c r="I153" s="2"/>
+      <c r="J153" s="2">
         <v>45912</v>
       </c>
-      <c r="J153" s="2"/>
       <c r="K153" s="2"/>
-      <c r="L153" t="s">
-        <v>21</v>
-      </c>
+      <c r="L153" s="2"/>
       <c r="M153" t="s">
         <v>21</v>
       </c>
       <c r="N153" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O153" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15">
       <c r="A154" t="s">
         <v>286</v>
       </c>
@@ -7311,23 +7278,23 @@
       <c r="G154" t="s">
         <v>29</v>
       </c>
-      <c r="H154" s="2"/>
-      <c r="I154" s="2">
+      <c r="I154" s="2"/>
+      <c r="J154" s="2">
         <v>45912</v>
       </c>
-      <c r="J154" s="2"/>
       <c r="K154" s="2"/>
-      <c r="L154" t="s">
-        <v>21</v>
-      </c>
+      <c r="L154" s="2"/>
       <c r="M154" t="s">
         <v>21</v>
       </c>
       <c r="N154" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O154" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15">
       <c r="A155" t="s">
         <v>287</v>
       </c>
@@ -7346,23 +7313,23 @@
       <c r="G155" t="s">
         <v>29</v>
       </c>
-      <c r="H155" s="2"/>
-      <c r="I155" s="2">
+      <c r="I155" s="2"/>
+      <c r="J155" s="2">
         <v>45912</v>
       </c>
-      <c r="J155" s="2"/>
       <c r="K155" s="2"/>
-      <c r="L155" t="s">
-        <v>21</v>
-      </c>
+      <c r="L155" s="2"/>
       <c r="M155" t="s">
         <v>21</v>
       </c>
       <c r="N155" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O155" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15">
       <c r="A156" t="s">
         <v>289</v>
       </c>
@@ -7384,25 +7351,25 @@
       <c r="G156" t="s">
         <v>29</v>
       </c>
-      <c r="H156" s="2">
+      <c r="I156" s="2">
         <v>45860</v>
       </c>
-      <c r="I156" s="2">
+      <c r="J156" s="2">
         <v>45908</v>
       </c>
-      <c r="J156" s="2"/>
       <c r="K156" s="2"/>
-      <c r="L156">
+      <c r="L156" s="2"/>
+      <c r="M156">
         <v>82</v>
       </c>
-      <c r="M156" t="s">
-        <v>21</v>
-      </c>
       <c r="N156" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O156" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
       <c r="A157" t="s">
         <v>291</v>
       </c>
@@ -7424,25 +7391,25 @@
       <c r="G157" t="s">
         <v>29</v>
       </c>
-      <c r="H157" s="2">
+      <c r="I157" s="2">
         <v>45866</v>
       </c>
-      <c r="I157" s="2">
+      <c r="J157" s="2">
         <v>45908</v>
       </c>
-      <c r="J157" s="2"/>
       <c r="K157" s="2"/>
-      <c r="L157">
+      <c r="L157" s="2"/>
+      <c r="M157">
         <v>93</v>
       </c>
-      <c r="M157" t="s">
-        <v>21</v>
-      </c>
       <c r="N157" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O157" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15">
       <c r="A158" t="s">
         <v>293</v>
       </c>
@@ -7464,25 +7431,25 @@
       <c r="G158" t="s">
         <v>29</v>
       </c>
-      <c r="H158" s="2">
+      <c r="I158" s="2">
         <v>45866</v>
       </c>
-      <c r="I158" s="2">
+      <c r="J158" s="2">
         <v>45908</v>
       </c>
-      <c r="J158" s="2"/>
       <c r="K158" s="2"/>
-      <c r="L158">
+      <c r="L158" s="2"/>
+      <c r="M158">
         <v>77</v>
       </c>
-      <c r="M158" t="s">
-        <v>21</v>
-      </c>
       <c r="N158" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O158" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
       <c r="A159" t="s">
         <v>295</v>
       </c>
@@ -7504,25 +7471,25 @@
       <c r="G159" t="s">
         <v>29</v>
       </c>
-      <c r="H159" s="2">
+      <c r="I159" s="2">
         <v>45860</v>
       </c>
-      <c r="I159" s="2">
+      <c r="J159" s="2">
         <v>45908</v>
       </c>
-      <c r="J159" s="2"/>
       <c r="K159" s="2"/>
-      <c r="L159">
+      <c r="L159" s="2"/>
+      <c r="M159">
         <v>73</v>
       </c>
-      <c r="M159" t="s">
-        <v>21</v>
-      </c>
       <c r="N159" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="160" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O159" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15">
       <c r="A160" t="s">
         <v>297</v>
       </c>
@@ -7541,25 +7508,25 @@
       <c r="G160" t="s">
         <v>20</v>
       </c>
-      <c r="H160" s="2">
+      <c r="I160" s="2">
         <v>45873</v>
       </c>
-      <c r="I160" s="2">
+      <c r="J160" s="2">
         <v>45901</v>
       </c>
-      <c r="J160" s="2"/>
       <c r="K160" s="2"/>
-      <c r="L160" t="s">
-        <v>21</v>
-      </c>
+      <c r="L160" s="2"/>
       <c r="M160" t="s">
         <v>21</v>
       </c>
       <c r="N160" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O160" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15">
       <c r="A161" t="s">
         <v>298</v>
       </c>
@@ -7578,25 +7545,25 @@
       <c r="G161" t="s">
         <v>20</v>
       </c>
-      <c r="H161" s="2">
+      <c r="I161" s="2">
         <v>45873</v>
       </c>
-      <c r="I161" s="2">
+      <c r="J161" s="2">
         <v>45901</v>
       </c>
-      <c r="J161" s="2"/>
       <c r="K161" s="2"/>
-      <c r="L161" t="s">
-        <v>21</v>
-      </c>
+      <c r="L161" s="2"/>
       <c r="M161" t="s">
         <v>21</v>
       </c>
       <c r="N161" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O161" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15">
       <c r="A162" t="s">
         <v>299</v>
       </c>
@@ -7615,25 +7582,25 @@
       <c r="G162" t="s">
         <v>20</v>
       </c>
-      <c r="H162" s="2">
+      <c r="I162" s="2">
         <v>45873</v>
       </c>
-      <c r="I162" s="2">
+      <c r="J162" s="2">
         <v>45901</v>
       </c>
-      <c r="J162" s="2"/>
       <c r="K162" s="2"/>
-      <c r="L162" t="s">
-        <v>21</v>
-      </c>
+      <c r="L162" s="2"/>
       <c r="M162" t="s">
         <v>21</v>
       </c>
       <c r="N162" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O162" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
       <c r="A163" t="s">
         <v>300</v>
       </c>
@@ -7652,25 +7619,25 @@
       <c r="G163" t="s">
         <v>20</v>
       </c>
-      <c r="H163" s="2">
+      <c r="I163" s="2">
         <v>45894</v>
       </c>
-      <c r="I163" s="2">
+      <c r="J163" s="2">
         <v>45901</v>
       </c>
-      <c r="J163" s="2"/>
       <c r="K163" s="2"/>
-      <c r="L163" t="s">
-        <v>21</v>
-      </c>
+      <c r="L163" s="2"/>
       <c r="M163" t="s">
         <v>21</v>
       </c>
       <c r="N163" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O163" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15">
       <c r="A164" t="s">
         <v>301</v>
       </c>
@@ -7689,25 +7656,25 @@
       <c r="G164" t="s">
         <v>20</v>
       </c>
-      <c r="H164" s="2">
+      <c r="I164" s="2">
         <v>45351</v>
       </c>
-      <c r="I164" s="2">
+      <c r="J164" s="2">
         <v>45901</v>
       </c>
-      <c r="J164" s="2"/>
       <c r="K164" s="2"/>
-      <c r="L164" t="s">
-        <v>21</v>
-      </c>
+      <c r="L164" s="2"/>
       <c r="M164" t="s">
         <v>21</v>
       </c>
       <c r="N164" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O164" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
       <c r="A165" t="s">
         <v>303</v>
       </c>
@@ -7726,25 +7693,25 @@
       <c r="G165" t="s">
         <v>20</v>
       </c>
-      <c r="H165" s="2">
+      <c r="I165" s="2">
         <v>45849</v>
       </c>
-      <c r="I165" s="2">
+      <c r="J165" s="2">
         <v>45901</v>
       </c>
-      <c r="J165" s="2"/>
       <c r="K165" s="2"/>
-      <c r="L165" t="s">
-        <v>21</v>
-      </c>
+      <c r="L165" s="2"/>
       <c r="M165" t="s">
         <v>21</v>
       </c>
       <c r="N165" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O165" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15">
       <c r="A166" t="s">
         <v>304</v>
       </c>
@@ -7763,23 +7730,23 @@
       <c r="G166" t="s">
         <v>20</v>
       </c>
-      <c r="H166" s="2"/>
-      <c r="I166" s="2">
+      <c r="I166" s="2"/>
+      <c r="J166" s="2">
         <v>45909</v>
       </c>
-      <c r="J166" s="2"/>
       <c r="K166" s="2"/>
-      <c r="L166" t="s">
-        <v>21</v>
-      </c>
+      <c r="L166" s="2"/>
       <c r="M166" t="s">
         <v>21</v>
       </c>
       <c r="N166" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O166" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15">
       <c r="B167" t="s">
         <v>16</v>
       </c>
@@ -7798,26 +7765,26 @@
       <c r="G167" t="s">
         <v>20</v>
       </c>
-      <c r="H167" s="2">
+      <c r="I167" s="2">
         <v>45146</v>
       </c>
-      <c r="I167" s="2">
+      <c r="J167" s="2">
         <v>45160</v>
       </c>
-      <c r="J167" s="2">
+      <c r="K167" s="2">
         <v>45167</v>
       </c>
-      <c r="K167" s="2">
+      <c r="L167" s="2">
         <v>45251</v>
       </c>
-      <c r="L167" s="3">
+      <c r="M167" s="3">
         <v>979</v>
       </c>
-      <c r="M167" s="1">
+      <c r="N167" s="1">
         <v>335.5</v>
       </c>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:15">
       <c r="B168" t="s">
         <v>16</v>
       </c>
@@ -7836,25 +7803,25 @@
       <c r="G168" t="s">
         <v>20</v>
       </c>
-      <c r="H168" s="2">
+      <c r="I168" s="2">
         <v>46100</v>
       </c>
-      <c r="I168" s="2">
+      <c r="J168" s="2">
         <v>46163</v>
       </c>
-      <c r="J168" s="2"/>
-      <c r="K168" s="2">
+      <c r="K168" s="2"/>
+      <c r="L168" s="2">
         <v>46272</v>
       </c>
-      <c r="L168" s="1">
+      <c r="M168" s="1">
         <f>469+404</f>
         <v>873</v>
       </c>
-      <c r="M168" s="1">
+      <c r="N168" s="1">
         <v>22.440999999999999</v>
       </c>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:15">
       <c r="B169" t="s">
         <v>16</v>
       </c>
@@ -7873,24 +7840,24 @@
       <c r="G169" t="s">
         <v>29</v>
       </c>
-      <c r="H169" s="2">
+      <c r="I169" s="2">
         <v>46027</v>
       </c>
-      <c r="I169" s="2">
+      <c r="J169" s="2">
         <v>46118</v>
       </c>
-      <c r="J169" s="2"/>
-      <c r="K169" s="2">
+      <c r="K169" s="2"/>
+      <c r="L169" s="2">
         <v>46272</v>
       </c>
-      <c r="L169" s="3">
+      <c r="M169" s="3">
         <v>94</v>
       </c>
-      <c r="M169" s="1">
+      <c r="N169" s="1">
         <v>287.91000000000003</v>
       </c>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:15">
       <c r="B170" t="s">
         <v>16</v>
       </c>
@@ -7909,27 +7876,27 @@
       <c r="G170" t="s">
         <v>20</v>
       </c>
-      <c r="H170" s="2"/>
-      <c r="I170" s="2">
+      <c r="I170" s="2"/>
+      <c r="J170" s="2">
         <v>45392</v>
       </c>
-      <c r="J170" s="2">
+      <c r="K170" s="2">
         <v>45402</v>
       </c>
-      <c r="K170" s="2">
+      <c r="L170" s="2">
         <v>45609</v>
       </c>
-      <c r="L170" s="1">
+      <c r="M170" s="1">
         <v>11</v>
       </c>
-      <c r="M170" s="1">
+      <c r="N170" s="1">
         <v>24.26</v>
       </c>
-      <c r="N170" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="171" spans="1:14">
+      <c r="O170" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15">
       <c r="B171" t="s">
         <v>16</v>
       </c>
@@ -7948,27 +7915,27 @@
       <c r="G171" t="s">
         <v>20</v>
       </c>
-      <c r="H171" s="2">
+      <c r="I171" s="2">
         <v>45166</v>
       </c>
-      <c r="I171" s="2">
+      <c r="J171" s="2">
         <v>45253</v>
       </c>
-      <c r="J171" s="2"/>
-      <c r="K171" s="2">
+      <c r="K171" s="2"/>
+      <c r="L171" s="2">
         <v>45271</v>
       </c>
-      <c r="L171" s="1">
+      <c r="M171" s="1">
         <v>42</v>
       </c>
-      <c r="M171" s="1">
+      <c r="N171" s="1">
         <v>443.39400000000001</v>
       </c>
-      <c r="N171" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14">
+      <c r="O171" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15">
       <c r="B172" t="s">
         <v>16</v>
       </c>
@@ -7987,20 +7954,20 @@
       <c r="G172" t="s">
         <v>20</v>
       </c>
-      <c r="H172" s="2">
+      <c r="I172" s="2">
         <v>46149</v>
       </c>
-      <c r="I172" s="2">
+      <c r="J172" s="2">
         <v>46203</v>
       </c>
-      <c r="J172" s="2"/>
-      <c r="K172" s="2">
+      <c r="K172" s="2"/>
+      <c r="L172" s="2">
         <v>46269</v>
       </c>
-      <c r="L172" s="1"/>
       <c r="M172" s="1"/>
-    </row>
-    <row r="173" spans="1:14">
+      <c r="N172" s="1"/>
+    </row>
+    <row r="173" spans="1:15">
       <c r="B173" t="s">
         <v>16</v>
       </c>
@@ -8019,27 +7986,27 @@
       <c r="G173" t="s">
         <v>20</v>
       </c>
-      <c r="H173" s="2"/>
-      <c r="I173" s="2">
+      <c r="I173" s="2"/>
+      <c r="J173" s="2">
         <v>45392</v>
       </c>
-      <c r="J173" s="2">
+      <c r="K173" s="2">
         <v>45400</v>
       </c>
-      <c r="K173" s="2">
+      <c r="L173" s="2">
         <v>45609</v>
       </c>
-      <c r="L173" s="1">
+      <c r="M173" s="1">
         <v>117</v>
       </c>
-      <c r="M173" s="1">
+      <c r="N173" s="1">
         <v>10.36</v>
       </c>
-      <c r="N173" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14">
+      <c r="O173" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15">
       <c r="B174" t="s">
         <v>16</v>
       </c>
@@ -8058,20 +8025,20 @@
       <c r="G174" t="s">
         <v>20</v>
       </c>
-      <c r="H174" s="2"/>
-      <c r="I174" s="2">
-        <v>45392</v>
-      </c>
+      <c r="I174" s="2"/>
       <c r="J174" s="2">
         <v>45392</v>
       </c>
       <c r="K174" s="2">
+        <v>45392</v>
+      </c>
+      <c r="L174" s="2">
         <v>45609</v>
       </c>
-      <c r="L174" s="1"/>
       <c r="M174" s="1"/>
-    </row>
-    <row r="175" spans="1:14">
+      <c r="N174" s="1"/>
+    </row>
+    <row r="175" spans="1:15">
       <c r="B175" t="s">
         <v>16</v>
       </c>
@@ -8090,27 +8057,27 @@
       <c r="G175" t="s">
         <v>20</v>
       </c>
-      <c r="H175" s="2">
+      <c r="I175" s="2">
         <v>45643</v>
       </c>
-      <c r="I175" s="2">
+      <c r="J175" s="2">
         <v>45800</v>
       </c>
-      <c r="J175" s="2"/>
-      <c r="K175" s="2">
+      <c r="K175" s="2"/>
+      <c r="L175" s="2">
         <v>45994</v>
       </c>
-      <c r="L175" s="1">
+      <c r="M175" s="1">
         <v>152</v>
       </c>
-      <c r="M175" s="1">
+      <c r="N175" s="1">
         <v>100.06</v>
       </c>
-      <c r="N175" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14">
+      <c r="O175" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15">
       <c r="B176" t="s">
         <v>16</v>
       </c>
@@ -8129,27 +8096,27 @@
       <c r="G176" t="s">
         <v>20</v>
       </c>
-      <c r="H176" s="2">
+      <c r="I176" s="2">
         <v>45750</v>
       </c>
-      <c r="I176" s="2">
+      <c r="J176" s="2">
         <v>45868</v>
       </c>
-      <c r="J176" s="2"/>
-      <c r="K176" s="2">
+      <c r="K176" s="2"/>
+      <c r="L176" s="2">
         <v>46129</v>
       </c>
-      <c r="L176" s="1">
-        <v>25</v>
-      </c>
       <c r="M176" s="1">
+        <v>25</v>
+      </c>
+      <c r="N176" s="1">
         <v>3.54</v>
       </c>
-      <c r="N176" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14">
+      <c r="O176" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15">
       <c r="B177" t="s">
         <v>16</v>
       </c>
@@ -8168,32 +8135,32 @@
       <c r="G177" t="s">
         <v>20</v>
       </c>
-      <c r="H177" s="2">
+      <c r="I177" s="2">
         <v>45812</v>
       </c>
-      <c r="I177" s="2">
+      <c r="J177" s="2">
         <v>45868</v>
       </c>
-      <c r="J177" s="2"/>
-      <c r="K177" s="2">
+      <c r="K177" s="2"/>
+      <c r="L177" s="2">
         <v>46129</v>
       </c>
-      <c r="L177" s="1">
+      <c r="M177" s="1">
         <v>1</v>
       </c>
-      <c r="M177" s="1">
+      <c r="N177" s="1">
         <v>1.99</v>
       </c>
-      <c r="N177" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14">
+      <c r="O177" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15">
       <c r="A178" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B178" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C178" t="s">
         <v>31</v>
@@ -8210,21 +8177,21 @@
       <c r="G178" t="s">
         <v>29</v>
       </c>
-      <c r="H178" s="2">
+      <c r="I178" s="2">
         <v>45994</v>
       </c>
-      <c r="I178" s="2">
+      <c r="J178" s="2">
         <v>46240</v>
       </c>
-      <c r="L178" s="1"/>
       <c r="M178" s="1"/>
-    </row>
-    <row r="179" spans="1:14">
+      <c r="N178" s="1"/>
+    </row>
+    <row r="179" spans="1:15">
       <c r="A179" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B179" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C179" t="s">
         <v>31</v>
@@ -8241,19 +8208,19 @@
       <c r="G179" t="s">
         <v>29</v>
       </c>
-      <c r="H179" s="2">
+      <c r="I179" s="2">
         <v>46021</v>
       </c>
-      <c r="I179" s="2">
+      <c r="J179" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="180" spans="1:14">
+    <row r="180" spans="1:15">
       <c r="A180" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="B180" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C180" t="s">
         <v>31</v>
@@ -8270,19 +8237,19 @@
       <c r="G180" t="s">
         <v>29</v>
       </c>
-      <c r="H180" s="2">
+      <c r="I180" s="2">
         <v>46052</v>
       </c>
-      <c r="I180" s="2">
+      <c r="J180" s="2">
         <v>46240</v>
       </c>
     </row>
-    <row r="181" spans="1:14">
+    <row r="181" spans="1:15">
       <c r="A181" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B181" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C181" t="s">
         <v>31</v>
@@ -8299,19 +8266,19 @@
       <c r="G181" t="s">
         <v>20</v>
       </c>
-      <c r="H181" s="2">
+      <c r="I181" s="2">
         <v>45883</v>
       </c>
-      <c r="I181" s="2">
+      <c r="J181" s="2">
         <v>46226</v>
       </c>
     </row>
-    <row r="182" spans="1:14">
+    <row r="182" spans="1:15">
       <c r="A182" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="B182" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C182" t="s">
         <v>31</v>
@@ -8328,16 +8295,16 @@
       <c r="G182" t="s">
         <v>29</v>
       </c>
-      <c r="H182" s="2">
+      <c r="I182" s="2">
         <v>46139</v>
       </c>
-      <c r="I182" s="2">
+      <c r="J182" s="2">
         <v>46230</v>
       </c>
     </row>
-    <row r="183" spans="1:14">
+    <row r="183" spans="1:15">
       <c r="B183" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C183" t="s">
         <v>31</v>
@@ -8354,16 +8321,16 @@
       <c r="G183" t="s">
         <v>29</v>
       </c>
-      <c r="H183" s="2">
+      <c r="I183" s="2">
         <v>45818</v>
       </c>
-      <c r="I183" s="2">
+      <c r="J183" s="2">
         <v>46252</v>
       </c>
     </row>
-    <row r="184" spans="1:14">
+    <row r="184" spans="1:15">
       <c r="B184" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C184" t="s">
         <v>31</v>
@@ -8380,16 +8347,16 @@
       <c r="G184" t="s">
         <v>29</v>
       </c>
-      <c r="H184" s="2">
+      <c r="I184" s="2">
         <v>46108</v>
       </c>
-      <c r="I184" s="2">
+      <c r="J184" s="2">
         <v>46227</v>
       </c>
     </row>
-    <row r="185" spans="1:14">
+    <row r="185" spans="1:15">
       <c r="B185" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C185" t="s">
         <v>31</v>
@@ -8406,22 +8373,22 @@
       <c r="G185" t="s">
         <v>29</v>
       </c>
-      <c r="H185" s="2">
+      <c r="I185" s="2">
         <v>45736</v>
       </c>
-      <c r="I185" s="2">
+      <c r="J185" s="2">
         <v>46227</v>
       </c>
-      <c r="L185">
+      <c r="M185">
         <v>41</v>
       </c>
-      <c r="M185">
+      <c r="N185">
         <v>23.27</v>
       </c>
     </row>
-    <row r="186" spans="1:14">
+    <row r="186" spans="1:15">
       <c r="B186" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C186" t="s">
         <v>31</v>
@@ -8438,24 +8405,24 @@
       <c r="G186" t="s">
         <v>29</v>
       </c>
-      <c r="H186" s="2">
+      <c r="I186" s="2">
         <v>46041</v>
       </c>
-      <c r="I186" s="2">
+      <c r="J186" s="2">
         <v>46227</v>
       </c>
-      <c r="J186" s="2"/>
       <c r="K186" s="2"/>
-      <c r="L186">
+      <c r="L186" s="2"/>
+      <c r="M186">
         <v>45</v>
       </c>
-      <c r="M186">
+      <c r="N186">
         <v>39.99</v>
       </c>
     </row>
-    <row r="187" spans="1:14">
+    <row r="187" spans="1:15">
       <c r="B187" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C187" t="s">
         <v>31</v>
@@ -8472,24 +8439,24 @@
       <c r="G187" t="s">
         <v>29</v>
       </c>
-      <c r="H187" s="2">
+      <c r="I187" s="2">
         <v>46066</v>
       </c>
-      <c r="I187" s="2">
+      <c r="J187" s="2">
         <v>46227</v>
       </c>
-      <c r="J187" s="2"/>
       <c r="K187" s="2"/>
-      <c r="L187">
+      <c r="L187" s="2"/>
+      <c r="M187">
         <v>50</v>
       </c>
-      <c r="M187">
+      <c r="N187">
         <v>3.46</v>
       </c>
     </row>
-    <row r="188" spans="1:14">
+    <row r="188" spans="1:15">
       <c r="B188" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C188" t="s">
         <v>31</v>
@@ -8506,24 +8473,24 @@
       <c r="G188" t="s">
         <v>29</v>
       </c>
-      <c r="H188" s="2">
+      <c r="I188" s="2">
         <v>46157</v>
       </c>
-      <c r="I188" s="2">
+      <c r="J188" s="2">
         <v>46227</v>
       </c>
-      <c r="J188" s="2"/>
       <c r="K188" s="2"/>
-      <c r="L188">
+      <c r="L188" s="2"/>
+      <c r="M188">
         <v>32</v>
       </c>
-      <c r="M188">
+      <c r="N188">
         <v>49.83</v>
       </c>
     </row>
-    <row r="189" spans="1:14">
+    <row r="189" spans="1:15">
       <c r="B189" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C189" t="s">
         <v>31</v>
@@ -8540,27 +8507,27 @@
       <c r="G189" t="s">
         <v>29</v>
       </c>
-      <c r="H189" s="2">
+      <c r="I189" s="2">
         <v>46139</v>
       </c>
-      <c r="I189" s="2">
+      <c r="J189" s="2">
         <v>46230</v>
       </c>
-      <c r="J189" s="2"/>
       <c r="K189" s="2"/>
-      <c r="L189">
+      <c r="L189" s="2"/>
+      <c r="M189">
         <v>389</v>
       </c>
-      <c r="M189">
+      <c r="N189">
         <v>823.24</v>
       </c>
     </row>
-    <row r="190" spans="1:14">
+    <row r="190" spans="1:15">
       <c r="A190" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="B190" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C190" t="s">
         <v>261</v>
@@ -8572,32 +8539,32 @@
         <v>25</v>
       </c>
       <c r="F190" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="G190" t="s">
         <v>20</v>
       </c>
-      <c r="H190" s="2"/>
-      <c r="I190" s="2">
+      <c r="I190" s="2"/>
+      <c r="J190" s="2">
         <v>45560</v>
       </c>
-      <c r="J190" s="2"/>
-      <c r="K190" s="2">
+      <c r="K190" s="2"/>
+      <c r="L190" s="2">
         <v>45590</v>
       </c>
-      <c r="L190">
+      <c r="M190">
         <v>60</v>
       </c>
-      <c r="M190">
+      <c r="N190">
         <v>14.7</v>
       </c>
     </row>
-    <row r="191" spans="1:14">
+    <row r="191" spans="1:15">
       <c r="A191" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="B191" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C191" t="s">
         <v>261</v>
@@ -8609,32 +8576,32 @@
         <v>25</v>
       </c>
       <c r="F191" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="G191" t="s">
         <v>20</v>
       </c>
-      <c r="H191" s="2"/>
-      <c r="I191" s="2">
+      <c r="I191" s="2"/>
+      <c r="J191" s="2">
         <v>45553</v>
       </c>
-      <c r="J191" s="2"/>
-      <c r="K191" s="2">
+      <c r="K191" s="2"/>
+      <c r="L191" s="2">
         <v>45629</v>
       </c>
-      <c r="L191">
+      <c r="M191">
         <v>265</v>
       </c>
-      <c r="M191">
+      <c r="N191">
         <v>149.29</v>
       </c>
     </row>
-    <row r="192" spans="1:14">
+    <row r="192" spans="1:15">
       <c r="A192" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B192" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C192" t="s">
         <v>261</v>
@@ -8646,32 +8613,32 @@
         <v>25</v>
       </c>
       <c r="F192" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="G192" t="s">
         <v>20</v>
       </c>
-      <c r="H192" s="2"/>
-      <c r="I192" s="2">
+      <c r="I192" s="2"/>
+      <c r="J192" s="2">
         <v>45785</v>
       </c>
-      <c r="J192" s="2"/>
-      <c r="K192" s="2">
+      <c r="K192" s="2"/>
+      <c r="L192" s="2">
         <v>45841</v>
       </c>
-      <c r="L192">
+      <c r="M192">
         <v>242</v>
       </c>
-      <c r="M192">
+      <c r="N192">
         <v>148</v>
       </c>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:14">
       <c r="A193" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B193" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C193" t="s">
         <v>261</v>
@@ -8683,32 +8650,32 @@
         <v>25</v>
       </c>
       <c r="F193" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="G193" t="s">
         <v>20</v>
       </c>
-      <c r="H193" s="2"/>
-      <c r="I193" s="2">
+      <c r="I193" s="2"/>
+      <c r="J193" s="2">
         <v>45939</v>
       </c>
-      <c r="J193" s="2"/>
-      <c r="K193" s="2">
+      <c r="K193" s="2"/>
+      <c r="L193" s="2">
         <v>45951</v>
       </c>
-      <c r="L193">
+      <c r="M193">
         <v>82</v>
       </c>
-      <c r="M193">
+      <c r="N193">
         <v>59.112000000000002</v>
       </c>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:14">
       <c r="A194" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="B194" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C194" t="s">
         <v>261</v>
@@ -8720,32 +8687,32 @@
         <v>25</v>
       </c>
       <c r="F194" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="G194" t="s">
         <v>20</v>
       </c>
-      <c r="H194" s="2"/>
-      <c r="I194" s="2">
+      <c r="I194" s="2"/>
+      <c r="J194" s="2">
         <v>45411</v>
       </c>
-      <c r="J194" s="2"/>
-      <c r="K194" s="2">
+      <c r="K194" s="2"/>
+      <c r="L194" s="2">
         <v>45456</v>
       </c>
-      <c r="L194">
+      <c r="M194">
         <v>165</v>
       </c>
-      <c r="M194">
+      <c r="N194">
         <v>33.07</v>
       </c>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:14">
       <c r="A195" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="B195" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C195" t="s">
         <v>261</v>
@@ -8757,32 +8724,32 @@
         <v>25</v>
       </c>
       <c r="F195" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="G195" t="s">
         <v>20</v>
       </c>
-      <c r="H195" s="2"/>
-      <c r="I195" s="2">
+      <c r="I195" s="2"/>
+      <c r="J195" s="2">
         <v>45673</v>
       </c>
-      <c r="J195" s="2"/>
-      <c r="K195" s="2">
+      <c r="K195" s="2"/>
+      <c r="L195" s="2">
         <v>45694</v>
       </c>
-      <c r="L195">
+      <c r="M195">
         <v>63</v>
       </c>
-      <c r="M195">
+      <c r="N195">
         <v>71.28</v>
       </c>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:14">
       <c r="A196" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B196" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C196" t="s">
         <v>261</v>
@@ -8794,32 +8761,32 @@
         <v>25</v>
       </c>
       <c r="F196" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="G196" t="s">
         <v>20</v>
       </c>
-      <c r="H196" s="2"/>
-      <c r="I196" s="2">
+      <c r="I196" s="2"/>
+      <c r="J196" s="2">
         <v>45721</v>
       </c>
-      <c r="J196" s="2"/>
-      <c r="K196" s="2">
+      <c r="K196" s="2"/>
+      <c r="L196" s="2">
         <v>45915</v>
       </c>
-      <c r="L196">
+      <c r="M196">
         <v>5</v>
       </c>
-      <c r="M196">
+      <c r="N196">
         <v>1.05</v>
       </c>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:14">
       <c r="A197" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="B197" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C197" t="s">
         <v>261</v>
@@ -8831,29 +8798,29 @@
         <v>25</v>
       </c>
       <c r="F197" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="G197" t="s">
         <v>20</v>
       </c>
-      <c r="H197" s="2"/>
-      <c r="I197" s="2">
+      <c r="I197" s="2"/>
+      <c r="J197" s="2">
         <v>45826</v>
       </c>
-      <c r="J197" s="2"/>
-      <c r="K197" s="2">
+      <c r="K197" s="2"/>
+      <c r="L197" s="2">
         <v>45957</v>
       </c>
-      <c r="L197">
+      <c r="M197">
         <v>15</v>
       </c>
-      <c r="M197">
+      <c r="N197">
         <v>3.02</v>
       </c>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:14">
       <c r="B198" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C198" t="s">
         <v>261</v>
@@ -8870,26 +8837,26 @@
       <c r="G198" t="s">
         <v>29</v>
       </c>
-      <c r="H198" s="2">
+      <c r="I198" s="2">
         <v>45880</v>
       </c>
-      <c r="I198" s="2">
+      <c r="J198" s="2">
         <v>45958</v>
       </c>
-      <c r="J198" s="2"/>
-      <c r="K198" s="2">
+      <c r="K198" s="2"/>
+      <c r="L198" s="2">
         <v>46226</v>
       </c>
-      <c r="L198">
+      <c r="M198">
         <v>71</v>
       </c>
-      <c r="M198">
+      <c r="N198">
         <v>49.98</v>
       </c>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:14">
       <c r="B199" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C199" t="s">
         <v>261</v>
@@ -8906,26 +8873,26 @@
       <c r="G199" t="s">
         <v>29</v>
       </c>
-      <c r="H199" s="2">
+      <c r="I199" s="2">
         <v>45791</v>
       </c>
-      <c r="I199" s="2">
+      <c r="J199" s="2">
         <v>45861</v>
       </c>
-      <c r="J199" s="2"/>
-      <c r="K199" s="2">
+      <c r="K199" s="2"/>
+      <c r="L199" s="2">
         <v>46226</v>
       </c>
-      <c r="L199">
+      <c r="M199">
         <v>40</v>
       </c>
-      <c r="M199">
+      <c r="N199">
         <v>44.38</v>
       </c>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:14">
       <c r="B200" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C200" t="s">
         <v>261</v>
@@ -8942,29 +8909,29 @@
       <c r="G200" t="s">
         <v>29</v>
       </c>
-      <c r="H200" s="2">
+      <c r="I200" s="2">
         <v>45796</v>
       </c>
-      <c r="I200" s="2">
+      <c r="J200" s="2">
         <v>45866</v>
       </c>
-      <c r="J200" s="2"/>
-      <c r="K200" s="2">
+      <c r="K200" s="2"/>
+      <c r="L200" s="2">
         <v>46226</v>
       </c>
-      <c r="L200">
+      <c r="M200">
         <v>70</v>
       </c>
-      <c r="M200">
+      <c r="N200">
         <v>49.96</v>
       </c>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" spans="1:14">
       <c r="A201" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B201" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C201" t="s">
         <v>261</v>
@@ -8981,29 +8948,29 @@
       <c r="G201" t="s">
         <v>20</v>
       </c>
-      <c r="H201" s="2">
+      <c r="I201" s="2">
         <v>45793</v>
       </c>
-      <c r="I201" s="2">
+      <c r="J201" s="2">
         <v>46013</v>
       </c>
-      <c r="J201" s="2"/>
-      <c r="K201" s="2">
+      <c r="K201" s="2"/>
+      <c r="L201" s="2">
         <v>46230</v>
       </c>
-      <c r="L201">
+      <c r="M201">
         <v>708</v>
       </c>
-      <c r="M201">
+      <c r="N201">
         <v>367.51</v>
       </c>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:14">
       <c r="A202" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="B202" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C202" t="s">
         <v>261</v>
@@ -9020,17 +8987,17 @@
       <c r="G202" t="s">
         <v>29</v>
       </c>
-      <c r="I202" s="2">
+      <c r="J202" s="2">
         <v>44405</v>
       </c>
-      <c r="J202" s="2"/>
-      <c r="K202" s="2">
+      <c r="K202" s="2"/>
+      <c r="L202" s="2">
         <v>44432</v>
       </c>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:14">
       <c r="B203" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C203" t="s">
         <v>261</v>
@@ -9047,26 +9014,26 @@
       <c r="G203" t="s">
         <v>29</v>
       </c>
-      <c r="I203" s="2">
+      <c r="J203" s="2">
         <v>44474</v>
       </c>
-      <c r="J203" s="2"/>
-      <c r="K203" s="2">
+      <c r="K203" s="2"/>
+      <c r="L203" s="2">
         <v>44540</v>
       </c>
-      <c r="L203">
+      <c r="M203">
         <v>191</v>
       </c>
-      <c r="M203">
+      <c r="N203">
         <v>43.18</v>
       </c>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:14">
       <c r="A204" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="B204" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C204" t="s">
         <v>261</v>
@@ -9083,26 +9050,26 @@
       <c r="G204" t="s">
         <v>29</v>
       </c>
-      <c r="I204" s="2">
+      <c r="J204" s="2">
         <v>44683</v>
       </c>
-      <c r="J204" s="2"/>
-      <c r="K204" s="2">
+      <c r="K204" s="2"/>
+      <c r="L204" s="2">
         <v>44767</v>
       </c>
-      <c r="L204">
+      <c r="M204">
         <v>49</v>
       </c>
-      <c r="M204">
+      <c r="N204">
         <v>32.96</v>
       </c>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" spans="1:14">
       <c r="A205" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="B205" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C205" t="s">
         <v>261</v>
@@ -9119,25 +9086,25 @@
       <c r="G205" t="s">
         <v>29</v>
       </c>
-      <c r="I205" s="2">
+      <c r="J205" s="2">
         <v>46008</v>
       </c>
-      <c r="J205" s="2">
+      <c r="K205" s="2">
         <v>46063</v>
       </c>
-      <c r="K205" s="2">
+      <c r="L205" s="2">
         <v>46247</v>
       </c>
-      <c r="L205">
+      <c r="M205">
         <v>90</v>
       </c>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206" spans="1:14">
       <c r="A206" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B206" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C206" t="s">
         <v>261</v>
@@ -9154,29 +9121,29 @@
       <c r="G206" t="s">
         <v>20</v>
       </c>
-      <c r="H206" s="2"/>
-      <c r="I206" s="2">
+      <c r="I206" s="2"/>
+      <c r="J206" s="2">
         <v>46065</v>
       </c>
-      <c r="J206" s="2">
+      <c r="K206" s="2">
         <v>46097</v>
       </c>
-      <c r="K206" s="2">
+      <c r="L206" s="2">
         <v>46247</v>
       </c>
-      <c r="L206">
+      <c r="M206">
         <v>23</v>
       </c>
-      <c r="M206">
+      <c r="N206">
         <v>111.72</v>
       </c>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:14">
       <c r="A207" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="B207" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C207" t="s">
         <v>261</v>
@@ -9193,24 +9160,24 @@
       <c r="G207" t="s">
         <v>29</v>
       </c>
-      <c r="H207" s="2"/>
-      <c r="I207" s="2">
+      <c r="I207" s="2"/>
+      <c r="J207" s="2">
         <v>45911</v>
       </c>
-      <c r="J207" s="2"/>
-      <c r="K207" s="2">
+      <c r="K207" s="2"/>
+      <c r="L207" s="2">
         <v>46076</v>
       </c>
-      <c r="L207">
+      <c r="M207">
         <v>13</v>
       </c>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:14">
       <c r="A208" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="B208" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C208" t="s">
         <v>261</v>
@@ -9227,21 +9194,21 @@
       <c r="G208" t="s">
         <v>20</v>
       </c>
-      <c r="H208" s="2">
+      <c r="I208" s="2">
         <v>45986</v>
       </c>
-      <c r="I208" s="2">
+      <c r="J208" s="2">
         <v>46177</v>
       </c>
-      <c r="J208" s="2"/>
       <c r="K208" s="2"/>
-      <c r="L208">
+      <c r="L208" s="2"/>
+      <c r="M208">
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:14">
       <c r="B209" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C209" t="s">
         <v>261</v>
@@ -9258,24 +9225,24 @@
       <c r="G209" t="s">
         <v>29</v>
       </c>
-      <c r="H209" s="2">
+      <c r="I209" s="2">
         <v>45982</v>
       </c>
-      <c r="I209" s="2">
+      <c r="J209" s="2">
         <v>46177</v>
       </c>
-      <c r="J209" s="2"/>
       <c r="K209" s="2"/>
-      <c r="L209">
+      <c r="L209" s="2"/>
+      <c r="M209">
         <v>69</v>
       </c>
-      <c r="M209">
+      <c r="N209">
         <v>183.38</v>
       </c>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:14">
       <c r="B210" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C210" t="s">
         <v>261</v>
@@ -9292,26 +9259,26 @@
       <c r="G210" t="s">
         <v>20</v>
       </c>
-      <c r="H210" s="2">
+      <c r="I210" s="2">
         <v>45971</v>
       </c>
-      <c r="I210" s="2">
+      <c r="J210" s="2">
         <v>46127</v>
       </c>
-      <c r="J210" s="2"/>
-      <c r="K210" s="2">
+      <c r="K210" s="2"/>
+      <c r="L210" s="2">
         <v>46148</v>
       </c>
-      <c r="L210">
+      <c r="M210">
         <v>82</v>
       </c>
-      <c r="M210">
+      <c r="N210">
         <v>29.19</v>
       </c>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:14">
       <c r="B211" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C211" t="s">
         <v>261</v>
@@ -9328,24 +9295,24 @@
       <c r="G211" t="s">
         <v>29</v>
       </c>
-      <c r="H211" s="2">
+      <c r="I211" s="2">
         <v>46079</v>
       </c>
-      <c r="I211" s="2">
+      <c r="J211" s="2">
         <v>46134</v>
       </c>
-      <c r="J211" s="2"/>
       <c r="K211" s="2"/>
-      <c r="L211">
+      <c r="L211" s="2"/>
+      <c r="M211">
         <v>35</v>
       </c>
-      <c r="M211">
+      <c r="N211">
         <v>22.44</v>
       </c>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:14">
       <c r="B212" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C212" t="s">
         <v>31</v>
@@ -9354,26 +9321,26 @@
         <v>18</v>
       </c>
       <c r="F212" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="G212" t="s">
         <v>20</v>
       </c>
-      <c r="H212" s="2">
+      <c r="I212" s="2">
         <v>45944</v>
       </c>
-      <c r="I212" s="2">
+      <c r="J212" s="2">
         <v>46094</v>
       </c>
-      <c r="J212" s="2"/>
       <c r="K212" s="2"/>
-    </row>
-    <row r="213" spans="1:13">
+      <c r="L212" s="2"/>
+    </row>
+    <row r="213" spans="1:14">
       <c r="A213" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="B213" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C213" t="s">
         <v>261</v>
@@ -9385,31 +9352,31 @@
         <v>25</v>
       </c>
       <c r="F213" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="G213" t="s">
         <v>20</v>
       </c>
-      <c r="H213" s="2">
+      <c r="I213" s="2">
         <v>45605</v>
       </c>
-      <c r="I213" s="2">
+      <c r="J213" s="2">
         <v>45827</v>
       </c>
-      <c r="J213" s="2"/>
-      <c r="K213" s="2">
+      <c r="K213" s="2"/>
+      <c r="L213" s="2">
         <v>45720</v>
       </c>
-      <c r="L213">
+      <c r="M213">
         <v>500</v>
       </c>
-      <c r="M213">
+      <c r="N213">
         <v>73.599999999999994</v>
       </c>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:14">
       <c r="B214" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C214" t="s">
         <v>261</v>
@@ -9426,26 +9393,26 @@
       <c r="G214" t="s">
         <v>29</v>
       </c>
-      <c r="H214" s="2">
+      <c r="I214" s="2">
         <v>45478</v>
       </c>
-      <c r="I214" s="2">
+      <c r="J214" s="2">
         <v>45671</v>
       </c>
-      <c r="J214" s="2"/>
-      <c r="K214" s="2">
+      <c r="K214" s="2"/>
+      <c r="L214" s="2">
         <v>46098</v>
       </c>
-      <c r="L214">
+      <c r="M214">
         <v>60</v>
       </c>
-      <c r="M214">
+      <c r="N214">
         <v>49.92</v>
       </c>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:14">
       <c r="B215" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C215" t="s">
         <v>261</v>
@@ -9457,31 +9424,31 @@
         <v>45</v>
       </c>
       <c r="F215" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="G215" t="s">
         <v>20</v>
       </c>
-      <c r="H215" s="2">
+      <c r="I215" s="2">
         <v>45982</v>
       </c>
-      <c r="I215" s="2">
+      <c r="J215" s="2">
         <v>46057</v>
       </c>
-      <c r="J215" s="2"/>
-      <c r="K215" s="2">
+      <c r="K215" s="2"/>
+      <c r="L215" s="2">
         <v>46098</v>
       </c>
-      <c r="L215">
-        <v>31</v>
-      </c>
       <c r="M215">
+        <v>31</v>
+      </c>
+      <c r="N215">
         <v>8.9</v>
       </c>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:14">
       <c r="B216" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C216" t="s">
         <v>31</v>
@@ -9498,24 +9465,24 @@
       <c r="G216" t="s">
         <v>29</v>
       </c>
-      <c r="H216" s="2">
+      <c r="I216" s="2">
         <v>45877</v>
       </c>
-      <c r="I216" s="2">
+      <c r="J216" s="2">
         <v>46097</v>
       </c>
-      <c r="J216" s="2"/>
       <c r="K216" s="2"/>
-      <c r="L216">
+      <c r="L216" s="2"/>
+      <c r="M216">
         <v>40</v>
       </c>
-      <c r="M216">
+      <c r="N216">
         <v>48.98</v>
       </c>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:14">
       <c r="B217" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C217" t="s">
         <v>261</v>
@@ -9532,28 +9499,28 @@
       <c r="G217" t="s">
         <v>29</v>
       </c>
-      <c r="H217" s="2">
+      <c r="I217" s="2">
         <v>45093</v>
       </c>
-      <c r="I217" s="2">
+      <c r="J217" s="2">
         <v>45225</v>
       </c>
-      <c r="J217" s="2">
+      <c r="K217" s="2">
         <v>46009</v>
       </c>
-      <c r="K217" s="2">
+      <c r="L217" s="2">
         <v>46085</v>
       </c>
-      <c r="L217">
+      <c r="M217">
         <v>39</v>
       </c>
-      <c r="M217">
+      <c r="N217">
         <v>48.39</v>
       </c>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:14">
       <c r="B218" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C218" t="s">
         <v>261</v>
@@ -9565,33 +9532,33 @@
         <v>25</v>
       </c>
       <c r="F218" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="G218" t="s">
         <v>20</v>
       </c>
-      <c r="H218" s="2">
+      <c r="I218" s="2">
         <v>44901</v>
       </c>
-      <c r="I218" s="2">
+      <c r="J218" s="2">
         <v>45749</v>
       </c>
-      <c r="J218" s="2">
+      <c r="K218" s="2">
         <v>45777</v>
       </c>
-      <c r="K218" s="2">
+      <c r="L218" s="2">
         <v>46094</v>
       </c>
-      <c r="L218">
+      <c r="M218">
         <v>26</v>
       </c>
-      <c r="M218">
+      <c r="N218">
         <v>16.395</v>
       </c>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:14">
       <c r="B219" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C219" t="s">
         <v>261</v>
@@ -9608,28 +9575,28 @@
       <c r="G219" t="s">
         <v>29</v>
       </c>
-      <c r="H219" s="2">
+      <c r="I219" s="2">
         <v>45478</v>
       </c>
-      <c r="I219" s="2">
+      <c r="J219" s="2">
         <v>45671</v>
       </c>
-      <c r="J219" s="2">
+      <c r="K219" s="2">
         <v>45848</v>
       </c>
-      <c r="K219" s="2">
+      <c r="L219" s="2">
         <v>46098</v>
       </c>
-      <c r="L219">
+      <c r="M219">
         <v>60</v>
       </c>
-      <c r="M219">
+      <c r="N219">
         <v>49.92</v>
       </c>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:14">
       <c r="B220" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C220" t="s">
         <v>261</v>
@@ -9646,28 +9613,28 @@
       <c r="G220" t="s">
         <v>29</v>
       </c>
-      <c r="H220" s="2">
+      <c r="I220" s="2">
         <v>45818</v>
       </c>
-      <c r="I220" s="2">
+      <c r="J220" s="2">
         <v>45864</v>
       </c>
-      <c r="J220" s="2">
+      <c r="K220" s="2">
         <v>45976</v>
       </c>
-      <c r="K220" s="2">
+      <c r="L220" s="2">
         <v>46098</v>
       </c>
-      <c r="L220">
+      <c r="M220">
         <v>48</v>
       </c>
-      <c r="M220" s="4">
+      <c r="N220">
         <v>49.99</v>
       </c>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:14">
       <c r="B221" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C221" t="s">
         <v>261</v>
@@ -9684,25 +9651,25 @@
       <c r="G221" t="s">
         <v>29</v>
       </c>
-      <c r="H221" s="2">
+      <c r="I221" s="2">
         <v>44417</v>
       </c>
-      <c r="I221" s="2">
+      <c r="J221" s="2">
         <v>44775</v>
       </c>
-      <c r="J221" s="2">
+      <c r="K221" s="2">
         <v>46000</v>
       </c>
-      <c r="K221" s="2">
+      <c r="L221" s="2">
         <v>46101</v>
       </c>
-      <c r="L221">
+      <c r="M221">
         <v>19</v>
       </c>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:14">
       <c r="B222" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C222" t="s">
         <v>31</v>
@@ -9714,23 +9681,23 @@
         <v>25</v>
       </c>
       <c r="F222" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="G222" t="s">
         <v>20</v>
       </c>
-      <c r="H222" s="2">
+      <c r="I222" s="2">
         <v>45770</v>
       </c>
-      <c r="I222" s="2">
+      <c r="J222" s="2">
         <v>46058</v>
       </c>
-      <c r="J222" s="2"/>
       <c r="K222" s="2"/>
-    </row>
-    <row r="223" spans="1:13">
+      <c r="L222" s="2"/>
+    </row>
+    <row r="223" spans="1:14">
       <c r="B223" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C223" t="s">
         <v>31</v>
@@ -9747,18 +9714,18 @@
       <c r="G223" t="s">
         <v>20</v>
       </c>
-      <c r="H223" s="2">
+      <c r="I223" s="2">
         <v>45754</v>
       </c>
-      <c r="I223" s="2">
+      <c r="J223" s="2">
         <v>46063</v>
       </c>
-      <c r="J223" s="2"/>
       <c r="K223" s="2"/>
-    </row>
-    <row r="224" spans="1:13">
+      <c r="L223" s="2"/>
+    </row>
+    <row r="224" spans="1:14">
       <c r="B224" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C224" t="s">
         <v>261</v>
@@ -9770,31 +9737,31 @@
         <v>25</v>
       </c>
       <c r="F224" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="G224" t="s">
         <v>20</v>
       </c>
-      <c r="H224" s="2">
+      <c r="I224" s="2">
         <v>44860</v>
       </c>
-      <c r="I224" s="2">
+      <c r="J224" s="2">
         <v>45749</v>
       </c>
-      <c r="J224" s="2"/>
-      <c r="K224" s="2">
+      <c r="K224" s="2"/>
+      <c r="L224" s="2">
         <v>45733</v>
       </c>
-      <c r="L224">
+      <c r="M224">
         <v>407</v>
       </c>
-      <c r="M224">
+      <c r="N224">
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="225" spans="2:11">
+    <row r="225" spans="2:16">
       <c r="B225" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C225" t="s">
         <v>261</v>
@@ -9811,956 +9778,952 @@
       <c r="G225" t="s">
         <v>29</v>
       </c>
-      <c r="I225" s="2">
+      <c r="J225" s="2">
         <v>45938</v>
       </c>
-      <c r="J225" s="2">
+      <c r="K225" s="2">
         <v>45969</v>
       </c>
-      <c r="K225" s="2">
+      <c r="L225" s="2">
         <v>46041</v>
       </c>
     </row>
+    <row r="226" spans="2:16" ht="15.6" customHeight="1">
+      <c r="B226" t="s">
+        <v>336</v>
+      </c>
+      <c r="C226" t="s">
+        <v>261</v>
+      </c>
+      <c r="D226" t="s">
+        <v>24</v>
+      </c>
+      <c r="E226" t="s">
+        <v>45</v>
+      </c>
+      <c r="F226" t="s">
+        <v>99</v>
+      </c>
+      <c r="G226" t="s">
+        <v>20</v>
+      </c>
+      <c r="I226" s="2">
+        <v>46164</v>
+      </c>
+      <c r="J226" s="2">
+        <v>46171</v>
+      </c>
+      <c r="K226" s="2">
+        <v>46171</v>
+      </c>
+      <c r="L226" s="2">
+        <v>46189</v>
+      </c>
+      <c r="M226">
+        <v>3</v>
+      </c>
+      <c r="N226">
+        <v>7.4660000000000004E-2</v>
+      </c>
+    </row>
+    <row r="227" spans="2:16">
+      <c r="B227" t="s">
+        <v>336</v>
+      </c>
+      <c r="C227" t="s">
+        <v>261</v>
+      </c>
+      <c r="D227" t="s">
+        <v>24</v>
+      </c>
+      <c r="E227" t="s">
+        <v>45</v>
+      </c>
+      <c r="F227" t="s">
+        <v>99</v>
+      </c>
+      <c r="G227" t="s">
+        <v>20</v>
+      </c>
+      <c r="I227" s="2">
+        <v>45784</v>
+      </c>
+      <c r="J227" s="2">
+        <v>45835</v>
+      </c>
+      <c r="K227" s="2">
+        <v>45835</v>
+      </c>
+      <c r="L227" s="2">
+        <v>45987</v>
+      </c>
+      <c r="M227">
+        <v>71</v>
+      </c>
+      <c r="N227">
+        <v>4.8319999999999999</v>
+      </c>
+    </row>
+    <row r="228" spans="2:16">
+      <c r="B228" t="s">
+        <v>336</v>
+      </c>
+      <c r="C228" t="s">
+        <v>261</v>
+      </c>
+      <c r="D228" t="s">
+        <v>24</v>
+      </c>
+      <c r="E228" t="s">
+        <v>25</v>
+      </c>
+      <c r="F228" t="s">
+        <v>29</v>
+      </c>
+      <c r="G228" t="s">
+        <v>29</v>
+      </c>
+      <c r="I228" s="2">
+        <v>45771</v>
+      </c>
+      <c r="J228" s="2">
+        <v>45860</v>
+      </c>
+      <c r="K228" s="2">
+        <v>45860</v>
+      </c>
+      <c r="L228" s="2">
+        <v>45950</v>
+      </c>
+      <c r="M228">
+        <v>65</v>
+      </c>
+      <c r="N228">
+        <v>17.86</v>
+      </c>
+    </row>
+    <row r="229" spans="2:16">
+      <c r="B229" t="s">
+        <v>336</v>
+      </c>
+      <c r="C229" t="s">
+        <v>261</v>
+      </c>
+      <c r="D229" t="s">
+        <v>24</v>
+      </c>
+      <c r="E229" t="s">
+        <v>25</v>
+      </c>
+      <c r="F229" t="s">
+        <v>99</v>
+      </c>
+      <c r="G229" t="s">
+        <v>20</v>
+      </c>
+      <c r="I229" s="2">
+        <v>45924</v>
+      </c>
+      <c r="J229" s="2">
+        <v>45938</v>
+      </c>
+      <c r="K229" s="2">
+        <v>45938</v>
+      </c>
+      <c r="L229" s="2">
+        <v>45946</v>
+      </c>
+      <c r="M229">
+        <v>4</v>
+      </c>
+      <c r="N229">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="230" spans="2:16">
+      <c r="B230" t="s">
+        <v>336</v>
+      </c>
+      <c r="C230" t="s">
+        <v>261</v>
+      </c>
+      <c r="D230" t="s">
+        <v>24</v>
+      </c>
+      <c r="E230" t="s">
+        <v>45</v>
+      </c>
+      <c r="F230" t="s">
+        <v>34</v>
+      </c>
+      <c r="G230" t="s">
+        <v>20</v>
+      </c>
+      <c r="I230" s="2">
+        <v>45429</v>
+      </c>
+      <c r="J230" s="2">
+        <v>45701</v>
+      </c>
+      <c r="K230" s="2">
+        <v>45701</v>
+      </c>
+      <c r="L230" s="2">
+        <v>45896</v>
+      </c>
+      <c r="M230">
+        <v>68</v>
+      </c>
+      <c r="N230">
+        <v>20.87</v>
+      </c>
+    </row>
+    <row r="231" spans="2:16">
+      <c r="B231" t="s">
+        <v>336</v>
+      </c>
+      <c r="C231" t="s">
+        <v>261</v>
+      </c>
+      <c r="D231" t="s">
+        <v>24</v>
+      </c>
+      <c r="E231" t="s">
+        <v>25</v>
+      </c>
+      <c r="F231" t="s">
+        <v>99</v>
+      </c>
+      <c r="G231" t="s">
+        <v>20</v>
+      </c>
+      <c r="I231" s="2">
+        <v>45777</v>
+      </c>
+      <c r="J231" s="2">
+        <v>45833</v>
+      </c>
+      <c r="K231" s="2">
+        <v>45833</v>
+      </c>
+      <c r="L231" s="2">
+        <v>45866</v>
+      </c>
+      <c r="M231">
+        <v>4</v>
+      </c>
+      <c r="N231">
+        <v>3.9609999999999999</v>
+      </c>
+    </row>
+    <row r="232" spans="2:16">
+      <c r="B232" t="s">
+        <v>336</v>
+      </c>
+      <c r="C232" t="s">
+        <v>261</v>
+      </c>
+      <c r="D232" t="s">
+        <v>24</v>
+      </c>
+      <c r="E232" t="s">
+        <v>45</v>
+      </c>
+      <c r="F232" t="s">
+        <v>34</v>
+      </c>
+      <c r="G232" t="s">
+        <v>20</v>
+      </c>
+      <c r="I232" s="2">
+        <v>45553</v>
+      </c>
+      <c r="J232" s="2">
+        <v>45701</v>
+      </c>
+      <c r="K232" s="2">
+        <v>45714</v>
+      </c>
+      <c r="L232" s="2">
+        <v>45839</v>
+      </c>
+      <c r="M232">
+        <v>27</v>
+      </c>
+      <c r="N232">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="P232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="2:16">
+      <c r="B233" t="s">
+        <v>336</v>
+      </c>
+      <c r="C233" t="s">
+        <v>261</v>
+      </c>
+      <c r="D233" t="s">
+        <v>24</v>
+      </c>
+      <c r="E233" t="s">
+        <v>45</v>
+      </c>
+      <c r="F233" t="s">
+        <v>34</v>
+      </c>
+      <c r="G233" t="s">
+        <v>20</v>
+      </c>
+      <c r="H233" s="2">
+        <v>45278</v>
+      </c>
+      <c r="I233" s="2">
+        <v>45485</v>
+      </c>
+      <c r="J233" s="2">
+        <v>45880</v>
+      </c>
+      <c r="K233" s="2">
+        <v>45880</v>
+      </c>
+      <c r="L233" s="2">
+        <v>46257</v>
+      </c>
+      <c r="M233">
+        <v>9</v>
+      </c>
+      <c r="N233">
+        <v>35.479999999999997</v>
+      </c>
+    </row>
+    <row r="234" spans="2:16">
+      <c r="B234" t="s">
+        <v>1</v>
+      </c>
+      <c r="C234" t="s">
+        <v>261</v>
+      </c>
+      <c r="D234" t="s">
+        <v>24</v>
+      </c>
+      <c r="E234" t="s">
+        <v>45</v>
+      </c>
+      <c r="F234" t="s">
+        <v>20</v>
+      </c>
+      <c r="G234" t="s">
+        <v>20</v>
+      </c>
+      <c r="I234" s="2">
+        <v>45699</v>
+      </c>
+      <c r="J234" s="2">
+        <v>45735</v>
+      </c>
+      <c r="K234" s="2"/>
+      <c r="L234" s="2">
+        <v>46139</v>
+      </c>
+      <c r="M234">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="235" spans="2:16">
+      <c r="B235" t="s">
+        <v>1</v>
+      </c>
+      <c r="C235" t="s">
+        <v>261</v>
+      </c>
+      <c r="D235" t="s">
+        <v>24</v>
+      </c>
+      <c r="E235" t="s">
+        <v>45</v>
+      </c>
+      <c r="F235" t="s">
+        <v>20</v>
+      </c>
+      <c r="G235" t="s">
+        <v>20</v>
+      </c>
+      <c r="I235" s="2">
+        <v>45324</v>
+      </c>
+      <c r="J235" s="2">
+        <v>45391</v>
+      </c>
+      <c r="K235" s="2"/>
+      <c r="L235" s="2">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="236" spans="2:16">
+      <c r="B236" t="s">
+        <v>1</v>
+      </c>
+      <c r="C236" t="s">
+        <v>31</v>
+      </c>
+      <c r="D236" t="s">
+        <v>24</v>
+      </c>
+      <c r="E236" t="s">
+        <v>25</v>
+      </c>
+      <c r="F236" t="s">
+        <v>29</v>
+      </c>
+      <c r="G236" t="s">
+        <v>29</v>
+      </c>
+      <c r="I236" s="2">
+        <v>46009</v>
+      </c>
+      <c r="J236" s="2">
+        <v>46014</v>
+      </c>
+      <c r="K236" s="2"/>
+      <c r="L236" s="2"/>
+      <c r="M236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="2:16">
+      <c r="B237" t="s">
+        <v>1</v>
+      </c>
+      <c r="C237" t="s">
+        <v>261</v>
+      </c>
+      <c r="D237" t="s">
+        <v>24</v>
+      </c>
+      <c r="E237" t="s">
+        <v>25</v>
+      </c>
+      <c r="F237" t="s">
+        <v>338</v>
+      </c>
+      <c r="G237" t="s">
+        <v>20</v>
+      </c>
+      <c r="I237" s="2">
+        <v>45762</v>
+      </c>
+      <c r="J237" s="2">
+        <v>45820</v>
+      </c>
+      <c r="K237" s="2">
+        <v>45829</v>
+      </c>
+      <c r="L237" s="2">
+        <v>45901</v>
+      </c>
+      <c r="M237">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="238" spans="2:16">
+      <c r="B238" t="s">
+        <v>1</v>
+      </c>
+      <c r="C238" t="s">
+        <v>31</v>
+      </c>
+      <c r="D238" t="s">
+        <v>24</v>
+      </c>
+      <c r="E238" t="s">
+        <v>25</v>
+      </c>
+      <c r="F238" t="s">
+        <v>29</v>
+      </c>
+      <c r="G238" t="s">
+        <v>29</v>
+      </c>
+      <c r="I238" s="2">
+        <v>46141</v>
+      </c>
+      <c r="J238" s="2">
+        <v>46164</v>
+      </c>
+      <c r="M238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="2:16">
+      <c r="B239" t="s">
+        <v>1</v>
+      </c>
+      <c r="C239" t="s">
+        <v>31</v>
+      </c>
+      <c r="D239" t="s">
+        <v>24</v>
+      </c>
+      <c r="E239" t="s">
+        <v>25</v>
+      </c>
+      <c r="F239" t="s">
+        <v>29</v>
+      </c>
+      <c r="G239" t="s">
+        <v>29</v>
+      </c>
+      <c r="I239" s="2">
+        <v>46142</v>
+      </c>
+      <c r="J239" s="2">
+        <v>46167</v>
+      </c>
+      <c r="K239" s="2"/>
+      <c r="L239" s="2"/>
+      <c r="M239">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240" spans="2:16">
+      <c r="B240" t="s">
+        <v>1</v>
+      </c>
+      <c r="C240" t="s">
+        <v>31</v>
+      </c>
+      <c r="D240" t="s">
+        <v>24</v>
+      </c>
+      <c r="E240" t="s">
+        <v>25</v>
+      </c>
+      <c r="F240" t="s">
+        <v>29</v>
+      </c>
+      <c r="G240" t="s">
+        <v>29</v>
+      </c>
+      <c r="I240" s="2">
+        <v>46142</v>
+      </c>
+      <c r="J240" s="2">
+        <v>46168</v>
+      </c>
+      <c r="K240" s="2"/>
+      <c r="L240" s="2"/>
+      <c r="M240">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="241" spans="2:14">
+      <c r="B241" t="s">
+        <v>1</v>
+      </c>
+      <c r="C241" t="s">
+        <v>31</v>
+      </c>
+      <c r="D241" t="s">
+        <v>24</v>
+      </c>
+      <c r="E241" t="s">
+        <v>25</v>
+      </c>
+      <c r="F241" t="s">
+        <v>29</v>
+      </c>
+      <c r="G241" t="s">
+        <v>29</v>
+      </c>
+      <c r="I241" s="2">
+        <v>45933</v>
+      </c>
+      <c r="J241" s="2">
+        <v>45951</v>
+      </c>
+    </row>
+    <row r="242" spans="2:14">
+      <c r="B242" t="s">
+        <v>1</v>
+      </c>
+      <c r="C242" t="s">
+        <v>31</v>
+      </c>
+      <c r="D242" t="s">
+        <v>24</v>
+      </c>
+      <c r="E242" t="s">
+        <v>25</v>
+      </c>
+      <c r="F242" t="s">
+        <v>29</v>
+      </c>
+      <c r="G242" t="s">
+        <v>29</v>
+      </c>
+      <c r="I242" s="2">
+        <v>45926</v>
+      </c>
+      <c r="J242" s="2">
+        <v>45951</v>
+      </c>
+      <c r="K242" s="2">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="243" spans="2:14">
+      <c r="B243" t="s">
+        <v>1</v>
+      </c>
+      <c r="C243" t="s">
+        <v>31</v>
+      </c>
+      <c r="D243" t="s">
+        <v>24</v>
+      </c>
+      <c r="E243" t="s">
+        <v>25</v>
+      </c>
+      <c r="F243" t="s">
+        <v>29</v>
+      </c>
+      <c r="G243" t="s">
+        <v>29</v>
+      </c>
+      <c r="I243" s="2">
+        <v>45936</v>
+      </c>
+      <c r="J243" s="2">
+        <v>45951</v>
+      </c>
+      <c r="K243" s="2">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="244" spans="2:14">
+      <c r="B244" t="s">
+        <v>1</v>
+      </c>
+      <c r="C244" t="s">
+        <v>31</v>
+      </c>
+      <c r="D244" t="s">
+        <v>24</v>
+      </c>
+      <c r="E244" t="s">
+        <v>25</v>
+      </c>
+      <c r="F244" t="s">
+        <v>29</v>
+      </c>
+      <c r="G244" t="s">
+        <v>29</v>
+      </c>
+      <c r="I244" s="2">
+        <v>45895</v>
+      </c>
+      <c r="J244" s="2">
+        <v>45951</v>
+      </c>
+      <c r="K244" s="2">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="245" spans="2:14">
+      <c r="B245" t="s">
+        <v>1</v>
+      </c>
+      <c r="C245" t="s">
+        <v>31</v>
+      </c>
+      <c r="D245" t="s">
+        <v>24</v>
+      </c>
+      <c r="E245" t="s">
+        <v>25</v>
+      </c>
+      <c r="F245" t="s">
+        <v>29</v>
+      </c>
+      <c r="G245" t="s">
+        <v>29</v>
+      </c>
+      <c r="I245" s="2">
+        <v>45940</v>
+      </c>
+      <c r="J245" s="2">
+        <v>45950</v>
+      </c>
+      <c r="K245" s="2">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="246" spans="2:14">
+      <c r="B246" t="s">
+        <v>1</v>
+      </c>
+      <c r="C246" t="s">
+        <v>31</v>
+      </c>
+      <c r="D246" t="s">
+        <v>24</v>
+      </c>
+      <c r="E246" t="s">
+        <v>25</v>
+      </c>
+      <c r="F246" t="s">
+        <v>29</v>
+      </c>
+      <c r="G246" t="s">
+        <v>29</v>
+      </c>
+      <c r="I246" s="4">
+        <v>45940</v>
+      </c>
+      <c r="J246" s="4">
+        <v>45950</v>
+      </c>
+      <c r="K246" s="4">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="247" spans="2:14">
+      <c r="B247" t="s">
+        <v>1</v>
+      </c>
+      <c r="C247" t="s">
+        <v>31</v>
+      </c>
+      <c r="D247" t="s">
+        <v>24</v>
+      </c>
+      <c r="E247" t="s">
+        <v>25</v>
+      </c>
+      <c r="F247" t="s">
+        <v>339</v>
+      </c>
+      <c r="G247" t="s">
+        <v>20</v>
+      </c>
+      <c r="I247" s="4">
+        <v>45926</v>
+      </c>
+      <c r="J247" s="4">
+        <v>45950</v>
+      </c>
+      <c r="K247" s="4">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="248" spans="2:14">
+      <c r="B248" t="s">
+        <v>1</v>
+      </c>
+      <c r="C248" t="s">
+        <v>31</v>
+      </c>
+      <c r="D248" t="s">
+        <v>24</v>
+      </c>
+      <c r="E248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F248" t="s">
+        <v>29</v>
+      </c>
+      <c r="G248" t="s">
+        <v>29</v>
+      </c>
+      <c r="I248" s="4">
+        <v>45815</v>
+      </c>
+      <c r="J248" s="4">
+        <v>45863</v>
+      </c>
+      <c r="K248" s="4">
+        <v>45875</v>
+      </c>
+      <c r="M248">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249" spans="2:14">
+      <c r="B249" t="s">
+        <v>1</v>
+      </c>
+      <c r="C249" t="s">
+        <v>261</v>
+      </c>
+      <c r="D249" t="s">
+        <v>24</v>
+      </c>
+      <c r="E249" t="s">
+        <v>340</v>
+      </c>
+      <c r="F249" t="s">
+        <v>29</v>
+      </c>
+      <c r="G249" t="s">
+        <v>29</v>
+      </c>
+      <c r="I249" s="4">
+        <v>45813</v>
+      </c>
+      <c r="J249" s="4">
+        <v>45826</v>
+      </c>
+      <c r="K249" s="4">
+        <v>45839</v>
+      </c>
+      <c r="L249" s="4">
+        <v>45882</v>
+      </c>
+      <c r="M249">
+        <v>6</v>
+      </c>
+      <c r="N249">
+        <v>9.56</v>
+      </c>
+    </row>
+    <row r="250" spans="2:14">
+      <c r="B250" t="s">
+        <v>1</v>
+      </c>
+      <c r="C250" t="s">
+        <v>261</v>
+      </c>
+      <c r="D250" t="s">
+        <v>24</v>
+      </c>
+      <c r="E250" t="s">
+        <v>256</v>
+      </c>
+      <c r="F250" t="s">
+        <v>29</v>
+      </c>
+      <c r="G250" t="s">
+        <v>29</v>
+      </c>
+      <c r="I250" s="4">
+        <v>45713</v>
+      </c>
+      <c r="J250" s="4">
+        <v>45734</v>
+      </c>
+      <c r="K250" s="4">
+        <v>45768</v>
+      </c>
+      <c r="L250" s="4">
+        <v>45890</v>
+      </c>
+    </row>
+    <row r="251" spans="2:14">
+      <c r="B251" t="s">
+        <v>1</v>
+      </c>
+      <c r="C251" t="s">
+        <v>261</v>
+      </c>
+      <c r="D251" t="s">
+        <v>24</v>
+      </c>
+      <c r="E251" t="s">
+        <v>256</v>
+      </c>
+      <c r="F251" t="s">
+        <v>29</v>
+      </c>
+      <c r="G251" t="s">
+        <v>29</v>
+      </c>
+      <c r="I251" s="4">
+        <v>45811</v>
+      </c>
+      <c r="J251" s="4">
+        <v>45846</v>
+      </c>
+      <c r="K251" s="4">
+        <v>45875</v>
+      </c>
+      <c r="L251" s="4">
+        <v>45896</v>
+      </c>
+      <c r="M251" s="4">
+        <v>15</v>
+      </c>
+      <c r="N251" s="4">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="252" spans="2:14">
+      <c r="B252" t="s">
+        <v>1</v>
+      </c>
+      <c r="C252" t="s">
+        <v>261</v>
+      </c>
+      <c r="D252" t="s">
+        <v>24</v>
+      </c>
+      <c r="E252" t="s">
+        <v>256</v>
+      </c>
+      <c r="F252" t="s">
+        <v>29</v>
+      </c>
+      <c r="G252" t="s">
+        <v>29</v>
+      </c>
+      <c r="I252" s="4">
+        <v>45645</v>
+      </c>
+      <c r="J252" s="4">
+        <v>45667</v>
+      </c>
+      <c r="K252" s="4">
+        <v>45673</v>
+      </c>
+      <c r="L252" s="4">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="253" spans="2:14">
+      <c r="B253" t="s">
+        <v>1</v>
+      </c>
+      <c r="C253" t="s">
+        <v>261</v>
+      </c>
+      <c r="D253" t="s">
+        <v>24</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+      <c r="F253" t="s">
+        <v>29</v>
+      </c>
+      <c r="G253" t="s">
+        <v>29</v>
+      </c>
+      <c r="I253" s="4">
+        <v>45813</v>
+      </c>
+      <c r="J253" s="4">
+        <v>45833</v>
+      </c>
+      <c r="K253" s="4">
+        <v>45897</v>
+      </c>
+      <c r="L253" s="4">
+        <v>45918</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P177" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:F120"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="6" max="6" width="105.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="105.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:6">
-      <c r="B2" t="str">
-        <f t="array" ref="B2:B107">+_xlfn.UNIQUE(Hoja2!F2:F172)</f>
-        <v>JUNTA DE ACCION COMUNAL DE LA VEREDA LA PALIZÁ DEL CORREGIMIENTO DE NUEVAS FLORES DEL MUNICIPIO DE SAN DIEGO</v>
-      </c>
-      <c r="F2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6">
-      <c r="B3" t="str">
-        <v>CLUB VALLEDUPAR S.A</v>
-      </c>
-      <c r="F3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" t="str">
-        <v>OLIVERIO CARDENAS QUINTERO</v>
-      </c>
-      <c r="F4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" t="str">
-        <v>ERCO ENERGÍA S.A.S</v>
-      </c>
-      <c r="F5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" t="str">
-        <v>UNERGY ENERGÍA DIGITAL S.A.S ESP</v>
-      </c>
-      <c r="F6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" t="str">
-        <v>BORIS ANTONIO ANDRADE MOVILLA</v>
-      </c>
-      <c r="F7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" t="str">
-        <v>CONSORCIO CONSTRUCTOR AUTOPISTA DEL RIO GRANDE</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" t="str">
-        <v>CARMEN DOLORES BERRIO MAESTRE</v>
-      </c>
-      <c r="F9" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" t="str">
-        <v>ATLANTICA- HIC RENOVABLES S.A.S</v>
-      </c>
-      <c r="F10" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" t="str">
-        <v>EXTRACTORA SICARARE S.A.S</v>
-      </c>
-      <c r="F11" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" t="str">
-        <v>MARÍA CLAUDIA VILLERO ARZUAGA</v>
-      </c>
-      <c r="F12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" t="str">
-        <v>LASCANO MORALES &amp; HIJOS S.C.S</v>
-      </c>
-      <c r="F13" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" t="str">
-        <v>VIVA MAYALES S.A.S</v>
-      </c>
-      <c r="F14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" t="str">
-        <v>PROMOTORA RESERVAS DE ANDALUCÍA S.A.S</v>
-      </c>
-      <c r="F15" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" t="str">
-        <v>DAYANA MARCELA LEYVA
-CARCAMO</v>
-      </c>
-      <c r="F16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" t="str">
-        <v>LUIS ROBERTO POSADA SANCHEZ</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" t="str">
-        <v>JUAN DANIEL ROJAS MEJIA</v>
-      </c>
-      <c r="F18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" t="str">
-        <v>CARMEN MARIA
-SERRANO ROMERO</v>
-      </c>
-      <c r="F19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" t="str">
-        <v>ESE HOSPITAL ROSARIO
-PUMAREJO DE LÓPEZ</v>
-      </c>
-      <c r="F20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" t="str">
-        <v>PROYECTOS E INVERSIONES MPL</v>
-      </c>
-      <c r="F21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" t="str">
-        <v>Departamento del Cesar</v>
-      </c>
-      <c r="F22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" t="str">
-        <v>BLACK ORCHID SOLAR MANAGEMENT S.A.S</v>
-      </c>
-      <c r="F23" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" t="str">
-        <v>CENIT TRANSPORTE Y LOGISTICA DE HIDROCARBUROS S.A.S.</v>
-      </c>
-      <c r="F24" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" t="str">
-        <v>RODAS SOLAR S.A.S</v>
-      </c>
-      <c r="F25" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" t="str">
-        <v>CONSORCIO TRANSVERSAL VIAL NEVADĀ</v>
-      </c>
-      <c r="F26" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27" t="str">
-        <v>Municipio de Valledupar</v>
-      </c>
-      <c r="F27" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28" t="str">
-        <v>SERPETCOL
-S.A.S</v>
-      </c>
-      <c r="F28" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" t="str">
-        <v>NUEVA CLINICA ARENAS</v>
-      </c>
-      <c r="F29" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" t="str">
-        <v>SERVICONSTRUCCIONES DEL CARIBE S.A.S.</v>
-      </c>
-      <c r="F30" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" t="str">
-        <v>Secretario de Obras Públicas</v>
-      </c>
-      <c r="F31" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="B32" t="str">
-        <v>Alcaldia</v>
-      </c>
-      <c r="F32" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" t="str">
-        <v>CESAR AUGUSTO SIERRA MARQUEZ</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" t="str">
-        <v>DIEGO MERCADO SANABRIA</v>
-      </c>
-      <c r="F34" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" t="str">
-        <v>INVERSIONES GALAMBAO S.A.S</v>
-      </c>
-      <c r="F35" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6">
-      <c r="B36" t="str">
-        <v>CLAUDIA LUZ PARRA CASTAÑO</v>
-      </c>
-      <c r="F36" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" t="str">
-        <v>Gobernacion</v>
-      </c>
-      <c r="F37" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" t="str">
-        <v>NELSON MANUEL GONZALEZ GONZALEZ</v>
-      </c>
-      <c r="F38" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" t="str">
-        <v>ANYEL DANIELA QUIÑONEZ HUERTAS</v>
-      </c>
-      <c r="F39" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" t="str">
-        <v>MARIA ALEJANDRA ARZUAGA PADILLA</v>
-      </c>
-      <c r="F40" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" t="str">
-        <v>UNIÓN TEMPORAL VIAL VLP</v>
-      </c>
-      <c r="F41" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" t="str">
-        <v>ALCALDÍA DEL MUNICIPIO DE VALLEDUPAR</v>
-      </c>
-      <c r="F42" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6">
-      <c r="B43" t="str">
-        <v>CONSTRUAMBIENTE S.A.S</v>
-      </c>
-      <c r="F43" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" t="str">
-        <v>CORPORACION DE CIENCIA Y TECNOLOGIA PARA EL DESARROLLO DE LA INDUSTRIA NAVAL, MARITIMA Y FLUVIAL- COTECMAR</v>
-      </c>
-      <c r="F44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" t="str">
-        <v>TRANSPORTADORA DE GAS INTERNACIONAL S.A</v>
-      </c>
-      <c r="F45" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" t="str">
-        <v>YUMA CONCESIONARIA S.A.</v>
-      </c>
-      <c r="F46" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" t="str">
-        <v>HELCIAS RODOLFO
-CASTILLA VALERA</v>
-      </c>
-      <c r="F47" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" t="str">
-        <v>EQUIMAQ DEL CESAR S.A.S.</v>
-      </c>
-      <c r="F48" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" t="str">
-        <v>CONSORCIO LA GLORIETA</v>
-      </c>
-      <c r="F49" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" t="str">
-        <v>ORBE SAS CONSTRUCCIONES</v>
-      </c>
-      <c r="F50" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6">
-      <c r="B51" t="str">
-        <v>OLIVIERO CARDENAS QUINTERO</v>
-      </c>
-      <c r="F51" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" t="str">
-        <v>LIZANDRO JOSE VEGA ARAUJO</v>
-      </c>
-      <c r="F52" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" t="str">
-        <v>ANTONIO LUIS ANDRADRE ANDRADE</v>
-      </c>
-      <c r="F53" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6">
-      <c r="B54" t="str">
-        <v>SOMAYA LILI CASTRO PACHECO</v>
-      </c>
-      <c r="F54" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6">
-      <c r="B55" t="str">
-        <v>REDOMACOL SAS</v>
-      </c>
-      <c r="F55" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6">
-      <c r="B56" t="str">
-        <v>UNIVERSIDAD DE SANTANDER</v>
-      </c>
-      <c r="F56" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6">
-      <c r="B57" t="str">
-        <v>INVERSIONES GLP SAS ESP</v>
-      </c>
-      <c r="F57" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" t="str">
-        <v>GLORISETH QUINTANA PABON</v>
-      </c>
-      <c r="F58" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6">
-      <c r="B59" t="str">
-        <v>RODOLFO CALDERÓN OROZCO</v>
-      </c>
-      <c r="F59" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6">
-      <c r="B60" t="str">
-        <v>AEREOPUERTO DE ORIENTES S.A.S</v>
-      </c>
-      <c r="F60" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" t="str">
-        <v>JOSE ALBERTO GUTIERREZ MIELES</v>
-      </c>
-      <c r="F61" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6">
-      <c r="B62" t="str">
-        <v>INVERSIONES Y PROYECTOS SAS</v>
-      </c>
-      <c r="F62" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6">
-      <c r="B63" t="str">
-        <v>ESE HOSPITAL ROSARIO PUMAREJO DE LÓPEZ</v>
-      </c>
-      <c r="F63" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" t="str">
-        <v>IMEM CONTRUCCIONES</v>
-      </c>
-      <c r="F64" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6">
-      <c r="B65" t="str">
-        <v>ESE HOSPITAL el Socorro</v>
-      </c>
-      <c r="F65" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6">
-      <c r="B66" t="str">
-        <v>JUDITH DEL CARMEN GONZALES BOLAÑOS</v>
-      </c>
-      <c r="F66" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6">
-      <c r="B67" t="str">
-        <v>CONSTRUVID S.A.S</v>
-      </c>
-      <c r="F67" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6">
-      <c r="B68" t="str">
-        <v>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA (UNAD)</v>
-      </c>
-      <c r="F68" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6">
-      <c r="B69" t="str">
-        <v>AUTOPISTA DEL RIO GRANDE S.A.S</v>
-      </c>
-      <c r="F69" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6">
-      <c r="B70" t="str">
-        <v>OVIER JOSE JIMENEZ PALMERA</v>
-      </c>
-      <c r="F70" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6">
-      <c r="B71" t="str">
-        <v>INVERSIONES GUATAPURI SAS</v>
-      </c>
-      <c r="F71" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6">
-      <c r="B72" t="str">
-        <v>CONSORCIO CONTRU-EDUCATIVO EL COPEY</v>
-      </c>
-      <c r="F72" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6">
-      <c r="B73" t="str">
-        <v>PEDRO NEL PINO PORTILLA</v>
-      </c>
-      <c r="F73" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6">
-      <c r="B74" t="str">
-        <v>HERNÁN
-EDUARDO BAQUERO RODRIGUEZ</v>
-      </c>
-      <c r="F74" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6">
-      <c r="B75" t="str">
-        <v>JUAN DANIEL ROJAS MEJÍA.</v>
-      </c>
-      <c r="F75" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6">
-      <c r="B76" t="str">
-        <v>MOISES EDUARDO GIL MAESTR</v>
-      </c>
-      <c r="F76" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6">
-      <c r="B77" t="str">
-        <v>PARQUE SOLAR EL UNIÓN S.A.S E.S.P</v>
-      </c>
-      <c r="F77" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6">
-      <c r="B78" t="str">
-        <v>BUEN FUTURO LIMITADA Y
-COMPAÑÍA S.C.A</v>
-      </c>
-      <c r="F78" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="79" spans="2:6">
-      <c r="B79" t="str">
-        <v>LLALIME SERRANO DAZA</v>
-      </c>
-      <c r="F79" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6">
-      <c r="B80" t="str">
-        <v>ALCALDÍA DEL MUNICIPIO DE PAILITAS</v>
-      </c>
-      <c r="F80" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" t="str">
-        <v>PEDRO MIGUEL LOZANO ORTIZ</v>
-      </c>
-      <c r="F81" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" t="str">
-        <v>VICTOR ENRIQUE FUENTES JIMENEZ</v>
-      </c>
-      <c r="F82" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="83" spans="2:6">
-      <c r="B83" t="str">
-        <v>JOSE DEL CARMEN SUAREZ INFANTE</v>
-      </c>
-      <c r="F83" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6">
-      <c r="B84" t="str">
-        <v>MARIA TERESA ORTIZ MOLINA</v>
-      </c>
-      <c r="F84" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6">
-      <c r="B85" t="str">
-        <v>GRUPO ENERGETICO DE SANTANDER S.A.S E.S.P</v>
-      </c>
-      <c r="F85" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" t="str">
-        <v>ORLANDO ANTONIO
-AGUILAR QUINTERO</v>
-      </c>
-      <c r="F86" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="87" spans="2:6">
-      <c r="B87" t="str">
-        <v>EVOLUSUN COLOMBIA S.A.S</v>
-      </c>
-      <c r="F87" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="88" spans="2:6">
-      <c r="B88" t="str">
-        <v>SELENA QUINTERO QUINTERO</v>
-      </c>
-      <c r="F88" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="89" spans="2:6">
-      <c r="B89" t="str">
-        <v>ELVIA MILENA SANJUAN DÁVILA</v>
-      </c>
-      <c r="F89" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="90" spans="2:6">
-      <c r="B90" t="str">
-        <v>VIVIANA GONZALEZ SANCHEZ</v>
-      </c>
-      <c r="F90" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="91" spans="2:6">
-      <c r="B91" t="str">
-        <v>FERMIN RAMÍREZ BAYONA</v>
-      </c>
-      <c r="F91" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="92" spans="2:6">
-      <c r="B92" t="str">
-        <v>JENNIFER ANILLO RIOS</v>
-      </c>
-      <c r="F92" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6">
-      <c r="B93" t="str">
-        <v>MARICELA BECERRA
-CALDERON</v>
-      </c>
-      <c r="F93" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" t="str">
-        <v>MARIA MARTHA
-LACOUTURE MAYA</v>
-      </c>
-      <c r="F94" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" t="str">
-        <v>SILVIA PATRICIA MARTINEZ MARTINEZ</v>
-      </c>
-      <c r="F95" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="96" spans="2:6">
-      <c r="B96" t="str">
-        <v>LILIA VARGAS DE MENDOZA</v>
-      </c>
-      <c r="F96" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" t="str">
-        <v>NESTOR JAVIER ALFARO BENITEZ</v>
-      </c>
-      <c r="F97" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" t="str">
-        <v>JOSE LUIS PALOMINO LOPEZ</v>
-      </c>
-      <c r="F98" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="99" spans="2:6">
-      <c r="B99" t="str">
-        <v>SANDRA MILENA BARAHONA VELEZ</v>
-      </c>
-      <c r="F99" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="100" spans="2:6">
-      <c r="B100" t="str">
-        <v>Fermin Ramirez Bayona</v>
-      </c>
-      <c r="F100" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6">
-      <c r="B101" t="str">
-        <v>Javier Murgas Barreto</v>
-      </c>
-      <c r="F101" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="102" spans="2:6">
-      <c r="B102" t="str">
-        <v>Elizabeth Gutiérrez</v>
-      </c>
-      <c r="F102" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="103" spans="2:6">
-      <c r="B103" t="str">
-        <v>Ricardo Rafael Fuente Jiménez</v>
-      </c>
-      <c r="F103" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="104" spans="2:6">
-      <c r="B104" t="str">
-        <v>COL AGROFORESTAL LA JAGUA ZOMAC S.A.S</v>
-      </c>
-      <c r="F104" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="105" spans="2:6">
-      <c r="B105" t="str">
-        <v>RODAS SOLAR S.A.S.</v>
-      </c>
-      <c r="F105" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="106" spans="2:6">
-      <c r="B106" t="str">
-        <v>LA ESTACIÓN SOLAR S.A.S E.S.P</v>
-      </c>
-      <c r="F106" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="107" spans="2:6">
-      <c r="B107" t="str">
-        <v>Persona natural</v>
-      </c>
-      <c r="F107" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="F108" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="109" spans="2:6">
-      <c r="F109" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="110" spans="2:6">
-      <c r="F110" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="111" spans="2:6">
-      <c r="F111" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="112" spans="2:6">
-      <c r="F112" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="113" spans="6:6">
-      <c r="F113" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="114" spans="6:6">
-      <c r="F114" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="115" spans="6:6">
-      <c r="F115" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="116" spans="6:6">
-      <c r="F116" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="117" spans="6:6">
-      <c r="F117" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="118" spans="6:6">
-      <c r="F118" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="119" spans="6:6">
-      <c r="F119" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="120" spans="6:6">
-      <c r="F120" t="s">
-        <v>133</v>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:Q177" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Fechas_CARS.xlsx
+++ b/Fechas_CARS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MiguelAndresBeltranG\Documents\UNERGY\Automatizacion\App CARS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AA74B10-973B-4706-96A5-599CF7609C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AAD446-63EA-42F3-82ED-48455AAF0D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1104,12 +1104,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10479,15 +10478,16 @@
       <c r="G246" t="s">
         <v>29</v>
       </c>
-      <c r="I246" s="4">
+      <c r="I246" s="2">
         <v>45940</v>
       </c>
-      <c r="J246" s="4">
+      <c r="J246" s="2">
         <v>45950</v>
       </c>
-      <c r="K246" s="4">
+      <c r="K246" s="2">
         <v>45972</v>
       </c>
+      <c r="L246" s="2"/>
     </row>
     <row r="247" spans="2:14">
       <c r="B247" t="s">
@@ -10508,15 +10508,16 @@
       <c r="G247" t="s">
         <v>20</v>
       </c>
-      <c r="I247" s="4">
+      <c r="I247" s="2">
         <v>45926</v>
       </c>
-      <c r="J247" s="4">
+      <c r="J247" s="2">
         <v>45950</v>
       </c>
-      <c r="K247" s="4">
+      <c r="K247" s="2">
         <v>45972</v>
       </c>
+      <c r="L247" s="2"/>
     </row>
     <row r="248" spans="2:14">
       <c r="B248" t="s">
@@ -10537,15 +10538,16 @@
       <c r="G248" t="s">
         <v>29</v>
       </c>
-      <c r="I248" s="4">
+      <c r="I248" s="2">
         <v>45815</v>
       </c>
-      <c r="J248" s="4">
+      <c r="J248" s="2">
         <v>45863</v>
       </c>
-      <c r="K248" s="4">
+      <c r="K248" s="2">
         <v>45875</v>
       </c>
+      <c r="L248" s="2"/>
       <c r="M248">
         <v>9</v>
       </c>
@@ -10569,16 +10571,16 @@
       <c r="G249" t="s">
         <v>29</v>
       </c>
-      <c r="I249" s="4">
+      <c r="I249" s="2">
         <v>45813</v>
       </c>
-      <c r="J249" s="4">
+      <c r="J249" s="2">
         <v>45826</v>
       </c>
-      <c r="K249" s="4">
+      <c r="K249" s="2">
         <v>45839</v>
       </c>
-      <c r="L249" s="4">
+      <c r="L249" s="2">
         <v>45882</v>
       </c>
       <c r="M249">
@@ -10607,16 +10609,16 @@
       <c r="G250" t="s">
         <v>29</v>
       </c>
-      <c r="I250" s="4">
+      <c r="I250" s="2">
         <v>45713</v>
       </c>
-      <c r="J250" s="4">
+      <c r="J250" s="2">
         <v>45734</v>
       </c>
-      <c r="K250" s="4">
+      <c r="K250" s="2">
         <v>45768</v>
       </c>
-      <c r="L250" s="4">
+      <c r="L250" s="2">
         <v>45890</v>
       </c>
     </row>
@@ -10639,22 +10641,22 @@
       <c r="G251" t="s">
         <v>29</v>
       </c>
-      <c r="I251" s="4">
+      <c r="I251" s="2">
         <v>45811</v>
       </c>
-      <c r="J251" s="4">
+      <c r="J251" s="2">
         <v>45846</v>
       </c>
-      <c r="K251" s="4">
+      <c r="K251" s="2">
         <v>45875</v>
       </c>
-      <c r="L251" s="4">
+      <c r="L251" s="2">
         <v>45896</v>
       </c>
-      <c r="M251" s="4">
+      <c r="M251">
         <v>15</v>
       </c>
-      <c r="N251" s="4">
+      <c r="N251">
         <v>5.92</v>
       </c>
     </row>
@@ -10677,16 +10679,16 @@
       <c r="G252" t="s">
         <v>29</v>
       </c>
-      <c r="I252" s="4">
+      <c r="I252" s="2">
         <v>45645</v>
       </c>
-      <c r="J252" s="4">
+      <c r="J252" s="2">
         <v>45667</v>
       </c>
-      <c r="K252" s="4">
+      <c r="K252" s="2">
         <v>45673</v>
       </c>
-      <c r="L252" s="4">
+      <c r="L252" s="2">
         <v>45894</v>
       </c>
     </row>
@@ -10709,16 +10711,16 @@
       <c r="G253" t="s">
         <v>29</v>
       </c>
-      <c r="I253" s="4">
+      <c r="I253" s="2">
         <v>45813</v>
       </c>
-      <c r="J253" s="4">
+      <c r="J253" s="2">
         <v>45833</v>
       </c>
-      <c r="K253" s="4">
+      <c r="K253" s="2">
         <v>45897</v>
       </c>
-      <c r="L253" s="4">
+      <c r="L253" s="2">
         <v>45918</v>
       </c>
     </row>
